--- a/STOCK V.O 2026.xlsx
+++ b/STOCK V.O 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TR-COMERCIAL-6\Desktop\INFORMES V.O\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9137FD-4F47-4268-A44B-BFD23599088F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D52E02-59D0-4816-BB52-2CAF0E805117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="662" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="662" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="2" state="hidden" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="425">
   <si>
     <t>AUTOMATRICULADOS SEAT</t>
   </si>
@@ -1319,6 +1319,9 @@
   </si>
   <si>
     <t>WB1 PF4 Z9A YW8</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
   </si>
 </sst>
 </file>
@@ -2757,13 +2760,13 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4426,8 +4429,8 @@
     <row r="10" spans="1:53" customFormat="1" ht="10.050000000000001" customHeight="1">
       <c r="A10" s="21"/>
       <c r="B10" s="29"/>
-      <c r="C10" s="250"/>
-      <c r="D10" s="250"/>
+      <c r="C10" s="249"/>
+      <c r="D10" s="249"/>
       <c r="E10" s="28"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -9764,10 +9767,10 @@
       <c r="O3" s="16"/>
       <c r="P3" s="16"/>
       <c r="Q3" s="16"/>
-      <c r="R3" s="251">
+      <c r="R3" s="250">
         <v>46227</v>
       </c>
-      <c r="S3" s="251"/>
+      <c r="S3" s="250"/>
       <c r="T3" s="19"/>
       <c r="U3" s="131"/>
     </row>
@@ -13645,8 +13648,8 @@
       <c r="P50" s="191">
         <v>36900</v>
       </c>
-      <c r="Q50" s="189" t="s">
-        <v>338</v>
+      <c r="Q50" s="208" t="s">
+        <v>424</v>
       </c>
       <c r="R50" s="189" t="s">
         <v>22</v>
@@ -22761,10 +22764,10 @@
       <c r="P2" s="160"/>
       <c r="Q2" s="160"/>
       <c r="R2" s="160"/>
-      <c r="S2" s="249">
+      <c r="S2" s="251">
         <v>46188</v>
       </c>
-      <c r="T2" s="249"/>
+      <c r="T2" s="251"/>
       <c r="U2" s="161"/>
     </row>
     <row r="3" spans="1:60" s="28" customFormat="1" ht="16.5" customHeight="1">

--- a/STOCK V.O 2026.xlsx
+++ b/STOCK V.O 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TR-COMERCIAL-6\Desktop\INFORMES V.O\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D52E02-59D0-4816-BB52-2CAF0E805117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{763C350F-BD09-4286-AA29-F08FF4852936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="662" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,10 +21,10 @@
     <sheet name="REMA-OCASIÓN" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'AUTOMATRICULADOS CUPRA'!$B$2:$P$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'AUTOMATRICULADOS SEAT'!$B$2:$S$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'AUTOMATRICULADOS CUPRA'!$B$2:$P$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'AUTOMATRICULADOS SEAT'!$B$2:$S$30</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'REMA-OCASIÓN'!$C$2:$Q$18</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">SEMINUEVOS!$B$2:$U$52</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">SEMINUEVOS!$B$2:$U$48</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="405">
   <si>
     <t>AUTOMATRICULADOS SEAT</t>
   </si>
@@ -433,12 +433,6 @@
     <t>VO</t>
   </si>
   <si>
-    <t>2753 LDK</t>
-  </si>
-  <si>
-    <t>KJZLR087144</t>
-  </si>
-  <si>
     <t>MAGNETIC-NEGRO</t>
   </si>
   <si>
@@ -793,15 +787,6 @@
     <t>KP3T1031008</t>
   </si>
   <si>
-    <t>2434 NLX</t>
-  </si>
-  <si>
-    <t>KP5T1031656</t>
-  </si>
-  <si>
-    <t>Z0B YW8</t>
-  </si>
-  <si>
     <t>FORMENTOR 1.5 e-HYBRID 204 DSG</t>
   </si>
   <si>
@@ -1084,30 +1069,9 @@
     <t>9656 NCK</t>
   </si>
   <si>
-    <t>BLANCON-NEGRO</t>
-  </si>
-  <si>
     <t>KJ7SR612832</t>
   </si>
   <si>
-    <t>0125 NCL</t>
-  </si>
-  <si>
-    <t>KJ7SR611745</t>
-  </si>
-  <si>
-    <t>P7P PTA PUR</t>
-  </si>
-  <si>
-    <t>4387 MRF</t>
-  </si>
-  <si>
-    <t>GRIS DOLPHIN</t>
-  </si>
-  <si>
-    <t>KN8RW011363</t>
-  </si>
-  <si>
     <t>3718 NBD</t>
   </si>
   <si>
@@ -1171,24 +1135,6 @@
     <t>KJ3VR025497</t>
   </si>
   <si>
-    <t>1327 NPT</t>
-  </si>
-  <si>
-    <t>FIORD</t>
-  </si>
-  <si>
-    <t>KL0TR085722</t>
-  </si>
-  <si>
-    <t>8397 NPR</t>
-  </si>
-  <si>
-    <t>1847 NPT</t>
-  </si>
-  <si>
-    <t>KL6TR073302</t>
-  </si>
-  <si>
     <t>1749 NPT</t>
   </si>
   <si>
@@ -1228,21 +1174,6 @@
     <t>KP3T1056300</t>
   </si>
   <si>
-    <t>PUK YW8</t>
-  </si>
-  <si>
-    <t>1875 MGZ</t>
-  </si>
-  <si>
-    <t>KL4PR048985</t>
-  </si>
-  <si>
-    <t>KL2TR094342</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
     <t>LA SALLE</t>
   </si>
   <si>
@@ -1261,9 +1192,6 @@
     <t>WB1 PF4 YW8</t>
   </si>
   <si>
-    <t>NICOLAS</t>
-  </si>
-  <si>
     <t>7429 NCK</t>
   </si>
   <si>
@@ -1276,52 +1204,64 @@
     <t>KJXSR612825</t>
   </si>
   <si>
-    <t>LEON 1.5 TSI 130 FR XL</t>
-  </si>
-  <si>
     <t>NAVE COVEY</t>
   </si>
   <si>
-    <t>COVEY</t>
+    <t>TERRAMAR VZ 1.5 E-HYBRID 272</t>
+  </si>
+  <si>
+    <t>4719 NHM</t>
+  </si>
+  <si>
+    <t>KP4S1008609</t>
+  </si>
+  <si>
+    <t>8273 NBR</t>
+  </si>
+  <si>
+    <t>GRIS MAGNETIC</t>
+  </si>
+  <si>
+    <t>KS8VR001057</t>
+  </si>
+  <si>
+    <t>RAVAL 211cv 51,5kwh ENDURANDE D.L.E</t>
+  </si>
+  <si>
+    <t>9755 NRG</t>
+  </si>
+  <si>
+    <t>KM1TR041849</t>
+  </si>
+  <si>
+    <t>WB1 PF4 Z9A YW8</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>SINIESTRO</t>
   </si>
   <si>
     <t>SABARIEGO</t>
   </si>
   <si>
-    <t>TERRAMAR VZ 1.5 E-HYBRID 272</t>
-  </si>
-  <si>
-    <t>4719 NHM</t>
-  </si>
-  <si>
-    <t>KP4S1008609</t>
-  </si>
-  <si>
-    <t>8273 NBR</t>
-  </si>
-  <si>
-    <t>GRIS MAGNETIC</t>
-  </si>
-  <si>
-    <t>KS8VR001057</t>
-  </si>
-  <si>
-    <t>RAVAL 211cv 51,5kwh ENDURANDE D.L.E</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
-  </si>
-  <si>
-    <t>9755 NRG</t>
-  </si>
-  <si>
-    <t>KM1TR041849</t>
-  </si>
-  <si>
-    <t>WB1 PF4 Z9A YW8</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
+    <t>8164 NDC</t>
+  </si>
+  <si>
+    <t>KJ8SR619840</t>
+  </si>
+  <si>
+    <t>7664 NDC</t>
+  </si>
+  <si>
+    <t>KJ4SR620791</t>
+  </si>
+  <si>
+    <t>7223 NDC</t>
+  </si>
+  <si>
+    <t>KJ3SR620832</t>
   </si>
 </sst>
 </file>
@@ -1333,7 +1273,7 @@
     <numFmt numFmtId="165" formatCode="dd\-mm\-yy;@"/>
     <numFmt numFmtId="166" formatCode="#,##0\ [$€-1]"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="37">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1599,8 +1539,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1652,12 +1600,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2094,7 +2036,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="252">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2667,9 +2609,6 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2694,9 +2633,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="26" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2730,9 +2666,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="23" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2748,9 +2681,6 @@
     <xf numFmtId="1" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2760,14 +2690,17 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3886,7 +3819,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BA219"/>
+  <dimension ref="A1:BA215"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1" style="2" customWidth="1"/>
@@ -3967,8 +3900,8 @@
       <c r="N3" s="17"/>
       <c r="O3" s="17"/>
       <c r="P3" s="18"/>
-      <c r="Q3" s="225">
-        <v>46227</v>
+      <c r="Q3" s="224">
+        <v>46232</v>
       </c>
       <c r="R3" s="19"/>
       <c r="S3" s="20"/>
@@ -4108,7 +4041,7 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="36" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>17</v>
@@ -4117,7 +4050,7 @@
         <v>18</v>
       </c>
       <c r="H6" s="37">
-        <v>2900</v>
+        <v>2600</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>19</v>
@@ -4138,14 +4071,12 @@
         <v>19900</v>
       </c>
       <c r="O6" s="37" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="P6" s="40"/>
-      <c r="Q6" s="40" t="s">
-        <v>398</v>
-      </c>
-      <c r="R6" s="217" t="s">
-        <v>325</v>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="S6" s="41"/>
       <c r="T6" s="42"/>
@@ -4191,13 +4122,13 @@
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="36" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="H7" s="37">
         <v>99</v>
@@ -4209,7 +4140,7 @@
         <v>46203</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="L7" s="38">
         <v>46296</v>
@@ -4221,12 +4152,12 @@
         <v>20900</v>
       </c>
       <c r="O7" s="37" t="s">
-        <v>338</v>
+        <v>375</v>
       </c>
       <c r="P7" s="40"/>
       <c r="Q7" s="40"/>
-      <c r="R7" s="228" t="s">
-        <v>325</v>
+      <c r="R7" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="S7" s="41"/>
       <c r="T7" s="42"/>
@@ -4272,25 +4203,25 @@
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="36" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="H8" s="37">
         <v>99</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J8" s="38">
         <v>46203</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="L8" s="38">
         <v>46296</v>
@@ -4302,12 +4233,14 @@
         <v>20900</v>
       </c>
       <c r="O8" s="37" t="s">
-        <v>338</v>
+        <v>396</v>
       </c>
       <c r="P8" s="40"/>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="228" t="s">
-        <v>325</v>
+      <c r="Q8" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="R8" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="S8" s="41"/>
       <c r="T8" s="42"/>
@@ -4349,17 +4282,17 @@
       <c r="A9" s="34"/>
       <c r="B9" s="35"/>
       <c r="C9" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="36" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="H9" s="37">
         <v>99</v>
@@ -4371,7 +4304,7 @@
         <v>46203</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="L9" s="38" t="s">
         <v>27</v>
@@ -4383,12 +4316,12 @@
         <v>20600</v>
       </c>
       <c r="O9" s="37" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="P9" s="40"/>
       <c r="Q9" s="40"/>
-      <c r="R9" s="220" t="s">
-        <v>325</v>
+      <c r="R9" s="219" t="s">
+        <v>320</v>
       </c>
       <c r="S9" s="41"/>
       <c r="T9" s="42"/>
@@ -4429,8 +4362,8 @@
     <row r="10" spans="1:53" customFormat="1" ht="10.050000000000001" customHeight="1">
       <c r="A10" s="21"/>
       <c r="B10" s="29"/>
-      <c r="C10" s="249"/>
-      <c r="D10" s="249"/>
+      <c r="C10" s="246"/>
+      <c r="D10" s="246"/>
       <c r="E10" s="28"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -4444,7 +4377,7 @@
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
-      <c r="R10" s="220"/>
+      <c r="R10" s="219"/>
       <c r="S10" s="41"/>
       <c r="T10" s="21"/>
       <c r="U10" s="21"/>
@@ -4485,7 +4418,7 @@
       <c r="A11" s="34"/>
       <c r="B11" s="35"/>
       <c r="C11" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="36" t="s">
@@ -4495,7 +4428,7 @@
         <v>23</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="H11" s="37">
         <v>99</v>
@@ -4507,7 +4440,7 @@
         <v>46142</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="L11" s="38" t="s">
         <v>27</v>
@@ -4519,14 +4452,14 @@
         <v>19900</v>
       </c>
       <c r="O11" s="37" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="P11" s="40" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="Q11" s="40"/>
-      <c r="R11" s="220" t="s">
-        <v>325</v>
+      <c r="R11" s="219" t="s">
+        <v>320</v>
       </c>
       <c r="S11" s="41"/>
       <c r="T11" s="42"/>
@@ -4582,7 +4515,7 @@
       <c r="O12" s="37"/>
       <c r="P12" s="40"/>
       <c r="Q12" s="40"/>
-      <c r="R12" s="220"/>
+      <c r="R12" s="219"/>
       <c r="S12" s="41"/>
       <c r="T12" s="42"/>
       <c r="U12" s="43"/>
@@ -4661,8 +4594,8 @@
       </c>
       <c r="P13" s="40"/>
       <c r="Q13" s="40"/>
-      <c r="R13" s="217" t="s">
-        <v>325</v>
+      <c r="R13" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="S13" s="47"/>
       <c r="T13" s="42"/>
@@ -4718,7 +4651,7 @@
       <c r="O14" s="37"/>
       <c r="P14" s="40"/>
       <c r="Q14" s="40"/>
-      <c r="R14" s="228"/>
+      <c r="R14" s="226"/>
       <c r="S14" s="47"/>
       <c r="T14" s="42"/>
       <c r="U14" s="43"/>
@@ -4763,25 +4696,25 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="36" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="H15" s="37">
         <v>99</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="J15" s="38">
         <v>46203</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="L15" s="38">
         <v>46296</v>
@@ -4793,12 +4726,12 @@
         <v>22500</v>
       </c>
       <c r="O15" s="37" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="P15" s="40"/>
       <c r="Q15" s="40"/>
-      <c r="R15" s="217" t="s">
-        <v>325</v>
+      <c r="R15" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="S15" s="47"/>
       <c r="T15" s="42"/>
@@ -4854,7 +4787,7 @@
       <c r="O16" s="37"/>
       <c r="P16" s="40"/>
       <c r="Q16" s="40"/>
-      <c r="R16" s="228"/>
+      <c r="R16" s="226"/>
       <c r="S16" s="47"/>
       <c r="T16" s="42"/>
       <c r="U16" s="43"/>
@@ -4899,25 +4832,25 @@
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="36" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="H17" s="37">
         <v>99</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J17" s="38">
         <v>46203</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="L17" s="38">
         <v>46296</v>
@@ -4929,12 +4862,14 @@
         <v>23500</v>
       </c>
       <c r="O17" s="37" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="P17" s="40"/>
-      <c r="Q17" s="40"/>
-      <c r="R17" s="228" t="s">
-        <v>325</v>
+      <c r="Q17" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="R17" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="S17" s="47"/>
       <c r="T17" s="42"/>
@@ -4990,7 +4925,7 @@
       <c r="O18" s="37"/>
       <c r="P18" s="40"/>
       <c r="Q18" s="40"/>
-      <c r="R18" s="217"/>
+      <c r="R18" s="216"/>
       <c r="S18" s="47"/>
       <c r="T18" s="42"/>
       <c r="U18" s="43"/>
@@ -5035,44 +4970,46 @@
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="36" t="s">
-        <v>134</v>
+        <v>302</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>374</v>
+        <v>303</v>
       </c>
       <c r="H19" s="37">
-        <v>99</v>
+        <v>999</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>375</v>
+        <v>19</v>
       </c>
       <c r="J19" s="38">
-        <v>46203</v>
+        <v>46168</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>376</v>
+        <v>323</v>
       </c>
       <c r="L19" s="38">
-        <v>46296</v>
+        <v>46261</v>
       </c>
       <c r="M19" s="37">
-        <v>22822</v>
+        <v>31752</v>
       </c>
       <c r="N19" s="39">
-        <v>23900</v>
+        <v>33500</v>
       </c>
       <c r="O19" s="37" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="P19" s="40"/>
-      <c r="Q19" s="40"/>
-      <c r="R19" s="217" t="s">
-        <v>325</v>
-      </c>
-      <c r="S19" s="47"/>
+      <c r="Q19" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="R19" s="216" t="s">
+        <v>320</v>
+      </c>
+      <c r="S19" s="41"/>
       <c r="T19" s="42"/>
       <c r="U19" s="43"/>
       <c r="V19" s="43"/>
@@ -5108,52 +5045,26 @@
       <c r="AZ19" s="44"/>
       <c r="BA19" s="44"/>
     </row>
-    <row r="20" spans="1:53" s="45" customFormat="1" ht="18" customHeight="1">
+    <row r="20" spans="1:53" s="45" customFormat="1" ht="14.4" customHeight="1">
       <c r="A20" s="34"/>
       <c r="B20" s="35"/>
-      <c r="C20" s="1" t="s">
-        <v>263</v>
-      </c>
+      <c r="C20" s="1"/>
       <c r="D20" s="1"/>
-      <c r="E20" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="H20" s="37">
-        <v>99</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="J20" s="38">
-        <v>46203</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="L20" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="M20" s="37">
-        <v>22821</v>
-      </c>
-      <c r="N20" s="39">
-        <v>23900</v>
-      </c>
-      <c r="O20" s="37" t="s">
-        <v>338</v>
-      </c>
+      <c r="E20" s="36"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="38"/>
+      <c r="M20" s="37"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="37"/>
       <c r="P20" s="40"/>
       <c r="Q20" s="40"/>
-      <c r="R20" s="217" t="s">
-        <v>325</v>
-      </c>
-      <c r="S20" s="47"/>
+      <c r="R20" s="219"/>
+      <c r="S20" s="41"/>
       <c r="T20" s="42"/>
       <c r="U20" s="43"/>
       <c r="V20" s="43"/>
@@ -5192,49 +5103,47 @@
     <row r="21" spans="1:53" s="45" customFormat="1" ht="18" customHeight="1">
       <c r="A21" s="34"/>
       <c r="B21" s="35"/>
-      <c r="C21" s="240" t="s">
-        <v>263</v>
-      </c>
-      <c r="D21" s="240"/>
-      <c r="E21" s="241" t="s">
-        <v>134</v>
-      </c>
-      <c r="F21" s="240" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="240" t="s">
-        <v>378</v>
-      </c>
-      <c r="H21" s="242">
+      <c r="C21" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="36" t="s">
+        <v>198</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="H21" s="37">
         <v>99</v>
       </c>
-      <c r="I21" s="240" t="s">
-        <v>19</v>
-      </c>
-      <c r="J21" s="243">
+      <c r="I21" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="J21" s="38">
         <v>46203</v>
       </c>
-      <c r="K21" s="240" t="s">
-        <v>379</v>
-      </c>
-      <c r="L21" s="243" t="s">
+      <c r="K21" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="L21" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="M21" s="242">
-        <v>23364</v>
-      </c>
-      <c r="N21" s="245">
-        <v>24200</v>
-      </c>
-      <c r="O21" s="242" t="s">
-        <v>338</v>
-      </c>
-      <c r="P21" s="244"/>
-      <c r="Q21" s="244" t="s">
-        <v>412</v>
-      </c>
-      <c r="R21" s="218" t="s">
-        <v>325</v>
+      <c r="M21" s="37">
+        <v>23788</v>
+      </c>
+      <c r="N21" s="39">
+        <v>24900</v>
+      </c>
+      <c r="O21" s="37" t="s">
+        <v>333</v>
+      </c>
+      <c r="P21" s="40"/>
+      <c r="Q21" s="40"/>
+      <c r="R21" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="S21" s="47"/>
       <c r="T21" s="42"/>
@@ -5272,7 +5181,7 @@
       <c r="AZ21" s="44"/>
       <c r="BA21" s="44"/>
     </row>
-    <row r="22" spans="1:53" s="45" customFormat="1" ht="10.050000000000001" customHeight="1">
+    <row r="22" spans="1:53" s="45" customFormat="1" ht="4.8" customHeight="1">
       <c r="A22" s="34"/>
       <c r="B22" s="35"/>
       <c r="C22" s="1"/>
@@ -5290,7 +5199,7 @@
       <c r="O22" s="37"/>
       <c r="P22" s="40"/>
       <c r="Q22" s="40"/>
-      <c r="R22" s="217"/>
+      <c r="R22" s="216"/>
       <c r="S22" s="47"/>
       <c r="T22" s="42"/>
       <c r="U22" s="43"/>
@@ -5331,48 +5240,46 @@
       <c r="A23" s="34"/>
       <c r="B23" s="35"/>
       <c r="C23" s="1" t="s">
-        <v>16</v>
+        <v>258</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="36" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="H23" s="37">
-        <v>999</v>
+        <v>99</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>19</v>
+        <v>306</v>
       </c>
       <c r="J23" s="38">
         <v>46168</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="L23" s="38">
-        <v>46261</v>
+        <v>307</v>
+      </c>
+      <c r="L23" s="38" t="s">
+        <v>27</v>
       </c>
       <c r="M23" s="37">
-        <v>31752</v>
+        <v>29582</v>
       </c>
       <c r="N23" s="39">
-        <v>33500</v>
+        <v>30900</v>
       </c>
       <c r="O23" s="37" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="P23" s="40"/>
-      <c r="Q23" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="R23" s="217" t="s">
-        <v>325</v>
+      <c r="Q23" s="40"/>
+      <c r="R23" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="S23" s="41"/>
       <c r="T23" s="42"/>
@@ -5410,7 +5317,7 @@
       <c r="AZ23" s="44"/>
       <c r="BA23" s="44"/>
     </row>
-    <row r="24" spans="1:53" s="45" customFormat="1" ht="14.4" customHeight="1">
+    <row r="24" spans="1:53" s="45" customFormat="1" ht="4.95" customHeight="1">
       <c r="A24" s="34"/>
       <c r="B24" s="35"/>
       <c r="C24" s="1"/>
@@ -5428,7 +5335,7 @@
       <c r="O24" s="37"/>
       <c r="P24" s="40"/>
       <c r="Q24" s="40"/>
-      <c r="R24" s="220"/>
+      <c r="R24" s="219"/>
       <c r="S24" s="41"/>
       <c r="T24" s="42"/>
       <c r="U24" s="43"/>
@@ -5465,50 +5372,50 @@
       <c r="AZ24" s="44"/>
       <c r="BA24" s="44"/>
     </row>
-    <row r="25" spans="1:53" s="45" customFormat="1" ht="18" customHeight="1">
+    <row r="25" spans="1:53" s="2" customFormat="1" ht="18" customHeight="1">
       <c r="A25" s="34"/>
       <c r="B25" s="35"/>
       <c r="C25" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="36" t="s">
-        <v>200</v>
+        <v>261</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>201</v>
+        <v>23</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>380</v>
+        <v>262</v>
       </c>
       <c r="H25" s="37">
         <v>99</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>381</v>
+        <v>19</v>
       </c>
       <c r="J25" s="38">
-        <v>46203</v>
+        <v>46142</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>382</v>
+        <v>263</v>
       </c>
       <c r="L25" s="38" t="s">
         <v>27</v>
       </c>
       <c r="M25" s="37">
-        <v>23788</v>
+        <v>30730</v>
       </c>
       <c r="N25" s="39">
-        <v>24900</v>
+        <v>31500</v>
       </c>
       <c r="O25" s="37" t="s">
-        <v>338</v>
+        <v>35</v>
       </c>
       <c r="P25" s="40"/>
       <c r="Q25" s="40"/>
-      <c r="R25" s="217" t="s">
-        <v>325</v>
+      <c r="R25" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="S25" s="47"/>
       <c r="T25" s="42"/>
@@ -5546,25 +5453,51 @@
       <c r="AZ25" s="44"/>
       <c r="BA25" s="44"/>
     </row>
-    <row r="26" spans="1:53" s="45" customFormat="1" ht="4.8" customHeight="1">
+    <row r="26" spans="1:53" s="2" customFormat="1" ht="18" customHeight="1">
       <c r="A26" s="34"/>
       <c r="B26" s="35"/>
-      <c r="C26" s="1"/>
+      <c r="C26" s="1" t="s">
+        <v>258</v>
+      </c>
       <c r="D26" s="1"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="37"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="38"/>
-      <c r="M26" s="37"/>
-      <c r="N26" s="39"/>
-      <c r="O26" s="37"/>
+      <c r="E26" s="36" t="s">
+        <v>261</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="H26" s="37">
+        <v>99</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J26" s="38">
+        <v>46142</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="L26" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="M26" s="37">
+        <v>30730</v>
+      </c>
+      <c r="N26" s="39">
+        <v>31900</v>
+      </c>
+      <c r="O26" s="132" t="s">
+        <v>268</v>
+      </c>
       <c r="P26" s="40"/>
       <c r="Q26" s="40"/>
-      <c r="R26" s="217"/>
+      <c r="R26" s="216" t="s">
+        <v>320</v>
+      </c>
       <c r="S26" s="47"/>
       <c r="T26" s="42"/>
       <c r="U26" s="43"/>
@@ -5601,52 +5534,52 @@
       <c r="AZ26" s="44"/>
       <c r="BA26" s="44"/>
     </row>
-    <row r="27" spans="1:53" s="45" customFormat="1" ht="18" customHeight="1">
+    <row r="27" spans="1:53" s="2" customFormat="1" ht="18" customHeight="1">
       <c r="A27" s="34"/>
       <c r="B27" s="35"/>
       <c r="C27" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="36" t="s">
-        <v>309</v>
+        <v>261</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>310</v>
+        <v>266</v>
       </c>
       <c r="H27" s="37">
-        <v>99</v>
+        <v>4500</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>311</v>
+        <v>19</v>
       </c>
       <c r="J27" s="38">
-        <v>46168</v>
+        <v>46142</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>312</v>
+        <v>267</v>
       </c>
       <c r="L27" s="38" t="s">
         <v>27</v>
       </c>
       <c r="M27" s="37">
-        <v>29582</v>
+        <v>30730</v>
       </c>
       <c r="N27" s="39">
         <v>30900</v>
       </c>
       <c r="O27" s="37" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="P27" s="40"/>
       <c r="Q27" s="40"/>
-      <c r="R27" s="217" t="s">
-        <v>325</v>
-      </c>
-      <c r="S27" s="41"/>
+      <c r="R27" s="216" t="s">
+        <v>320</v>
+      </c>
+      <c r="S27" s="47"/>
       <c r="T27" s="42"/>
       <c r="U27" s="43"/>
       <c r="V27" s="43"/>
@@ -5682,25 +5615,51 @@
       <c r="AZ27" s="44"/>
       <c r="BA27" s="44"/>
     </row>
-    <row r="28" spans="1:53" s="45" customFormat="1" ht="4.95" customHeight="1">
+    <row r="28" spans="1:53" s="45" customFormat="1" ht="18" customHeight="1">
       <c r="A28" s="34"/>
       <c r="B28" s="35"/>
-      <c r="C28" s="1"/>
+      <c r="C28" s="1" t="s">
+        <v>258</v>
+      </c>
       <c r="D28" s="1"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="38"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="37"/>
-      <c r="N28" s="39"/>
-      <c r="O28" s="37"/>
+      <c r="E28" s="36" t="s">
+        <v>308</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="H28" s="37">
+        <v>99</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J28" s="38">
+        <v>46168</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="L28" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="M28" s="37">
+        <v>31324</v>
+      </c>
+      <c r="N28" s="39">
+        <v>32500</v>
+      </c>
+      <c r="O28" s="132" t="s">
+        <v>299</v>
+      </c>
       <c r="P28" s="40"/>
       <c r="Q28" s="40"/>
-      <c r="R28" s="220"/>
+      <c r="R28" s="216" t="s">
+        <v>320</v>
+      </c>
       <c r="S28" s="41"/>
       <c r="T28" s="42"/>
       <c r="U28" s="43"/>
@@ -5737,52 +5696,52 @@
       <c r="AZ28" s="44"/>
       <c r="BA28" s="44"/>
     </row>
-    <row r="29" spans="1:53" s="2" customFormat="1" ht="18" customHeight="1">
+    <row r="29" spans="1:53" s="45" customFormat="1" ht="18" customHeight="1">
       <c r="A29" s="34"/>
       <c r="B29" s="35"/>
       <c r="C29" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="36" t="s">
-        <v>266</v>
+        <v>308</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>267</v>
+        <v>311</v>
       </c>
       <c r="H29" s="37">
         <v>99</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>19</v>
+        <v>125</v>
       </c>
       <c r="J29" s="38">
-        <v>46142</v>
+        <v>46168</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>268</v>
+        <v>312</v>
       </c>
       <c r="L29" s="38" t="s">
         <v>27</v>
       </c>
       <c r="M29" s="37">
-        <v>30730</v>
+        <v>31324</v>
       </c>
       <c r="N29" s="39">
-        <v>31500</v>
-      </c>
-      <c r="O29" s="37" t="s">
-        <v>35</v>
+        <v>32500</v>
+      </c>
+      <c r="O29" s="132" t="s">
+        <v>334</v>
       </c>
       <c r="P29" s="40"/>
       <c r="Q29" s="40"/>
-      <c r="R29" s="217" t="s">
-        <v>325</v>
-      </c>
-      <c r="S29" s="47"/>
+      <c r="R29" s="216" t="s">
+        <v>320</v>
+      </c>
+      <c r="S29" s="41"/>
       <c r="T29" s="42"/>
       <c r="U29" s="43"/>
       <c r="V29" s="43"/>
@@ -5818,351 +5777,87 @@
       <c r="AZ29" s="44"/>
       <c r="BA29" s="44"/>
     </row>
-    <row r="30" spans="1:53" s="2" customFormat="1" ht="18" customHeight="1">
-      <c r="A30" s="34"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="D30" s="1"/>
-      <c r="E30" s="36" t="s">
-        <v>266</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="H30" s="37">
-        <v>99</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J30" s="38">
-        <v>46142</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="L30" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="M30" s="37">
-        <v>30730</v>
-      </c>
-      <c r="N30" s="39">
-        <v>31900</v>
-      </c>
-      <c r="O30" s="37" t="s">
-        <v>338</v>
-      </c>
-      <c r="P30" s="40"/>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="217" t="s">
-        <v>325</v>
-      </c>
-      <c r="S30" s="47"/>
-      <c r="T30" s="42"/>
-      <c r="U30" s="43"/>
-      <c r="V30" s="43"/>
-      <c r="W30" s="43"/>
-      <c r="X30" s="43"/>
-      <c r="Y30" s="43"/>
-      <c r="Z30" s="43"/>
-      <c r="AA30" s="43"/>
-      <c r="AB30" s="43"/>
-      <c r="AC30" s="43"/>
-      <c r="AD30" s="43"/>
-      <c r="AE30" s="43"/>
-      <c r="AF30" s="43"/>
-      <c r="AG30" s="43"/>
-      <c r="AH30" s="43"/>
-      <c r="AI30" s="43"/>
-      <c r="AJ30" s="43"/>
-      <c r="AK30" s="43"/>
-      <c r="AL30" s="43"/>
-      <c r="AM30" s="43"/>
-      <c r="AN30" s="43"/>
-      <c r="AO30" s="43"/>
-      <c r="AP30" s="43"/>
-      <c r="AQ30" s="43"/>
-      <c r="AR30" s="43"/>
-      <c r="AS30" s="43"/>
-      <c r="AT30" s="43"/>
-      <c r="AU30" s="43"/>
-      <c r="AV30" s="43"/>
-      <c r="AW30" s="43"/>
-      <c r="AX30" s="43"/>
-      <c r="AY30" s="43"/>
-      <c r="AZ30" s="44"/>
-      <c r="BA30" s="44"/>
-    </row>
-    <row r="31" spans="1:53" s="2" customFormat="1" ht="18" customHeight="1">
-      <c r="A31" s="34"/>
-      <c r="B31" s="35"/>
-      <c r="C31" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="D31" s="1"/>
-      <c r="E31" s="36" t="s">
-        <v>266</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="H31" s="37">
-        <v>4500</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J31" s="38">
-        <v>46142</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="L31" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="M31" s="37">
-        <v>30730</v>
-      </c>
-      <c r="N31" s="39">
-        <v>30900</v>
-      </c>
-      <c r="O31" s="37" t="s">
-        <v>338</v>
-      </c>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="217" t="s">
-        <v>325</v>
-      </c>
-      <c r="S31" s="47"/>
-      <c r="T31" s="42"/>
-      <c r="U31" s="43"/>
-      <c r="V31" s="43"/>
-      <c r="W31" s="43"/>
-      <c r="X31" s="43"/>
-      <c r="Y31" s="43"/>
-      <c r="Z31" s="43"/>
-      <c r="AA31" s="43"/>
-      <c r="AB31" s="43"/>
-      <c r="AC31" s="43"/>
-      <c r="AD31" s="43"/>
-      <c r="AE31" s="43"/>
-      <c r="AF31" s="43"/>
-      <c r="AG31" s="43"/>
-      <c r="AH31" s="43"/>
-      <c r="AI31" s="43"/>
-      <c r="AJ31" s="43"/>
-      <c r="AK31" s="43"/>
-      <c r="AL31" s="43"/>
-      <c r="AM31" s="43"/>
-      <c r="AN31" s="43"/>
-      <c r="AO31" s="43"/>
-      <c r="AP31" s="43"/>
-      <c r="AQ31" s="43"/>
-      <c r="AR31" s="43"/>
-      <c r="AS31" s="43"/>
-      <c r="AT31" s="43"/>
-      <c r="AU31" s="43"/>
-      <c r="AV31" s="43"/>
-      <c r="AW31" s="43"/>
-      <c r="AX31" s="43"/>
-      <c r="AY31" s="43"/>
-      <c r="AZ31" s="44"/>
-      <c r="BA31" s="44"/>
-    </row>
-    <row r="32" spans="1:53" s="45" customFormat="1" ht="18" customHeight="1">
-      <c r="A32" s="34"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="D32" s="1"/>
-      <c r="E32" s="36" t="s">
-        <v>313</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="H32" s="37">
-        <v>99</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J32" s="38">
-        <v>46168</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="L32" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="M32" s="37">
-        <v>31324</v>
-      </c>
-      <c r="N32" s="39">
-        <v>32500</v>
-      </c>
-      <c r="O32" s="132" t="s">
-        <v>304</v>
-      </c>
-      <c r="P32" s="40"/>
-      <c r="Q32" s="40"/>
-      <c r="R32" s="217" t="s">
-        <v>325</v>
-      </c>
-      <c r="S32" s="41"/>
-      <c r="T32" s="42"/>
-      <c r="U32" s="43"/>
-      <c r="V32" s="43"/>
-      <c r="W32" s="43"/>
-      <c r="X32" s="43"/>
-      <c r="Y32" s="43"/>
-      <c r="Z32" s="43"/>
-      <c r="AA32" s="43"/>
-      <c r="AB32" s="43"/>
-      <c r="AC32" s="43"/>
-      <c r="AD32" s="43"/>
-      <c r="AE32" s="43"/>
-      <c r="AF32" s="43"/>
-      <c r="AG32" s="43"/>
-      <c r="AH32" s="43"/>
-      <c r="AI32" s="43"/>
-      <c r="AJ32" s="43"/>
-      <c r="AK32" s="43"/>
-      <c r="AL32" s="43"/>
-      <c r="AM32" s="43"/>
-      <c r="AN32" s="43"/>
-      <c r="AO32" s="43"/>
-      <c r="AP32" s="43"/>
-      <c r="AQ32" s="43"/>
-      <c r="AR32" s="43"/>
-      <c r="AS32" s="43"/>
-      <c r="AT32" s="43"/>
-      <c r="AU32" s="43"/>
-      <c r="AV32" s="43"/>
-      <c r="AW32" s="43"/>
-      <c r="AX32" s="43"/>
-      <c r="AY32" s="43"/>
-      <c r="AZ32" s="44"/>
-      <c r="BA32" s="44"/>
-    </row>
-    <row r="33" spans="1:53" s="45" customFormat="1" ht="18" customHeight="1">
-      <c r="A33" s="34"/>
-      <c r="B33" s="35"/>
-      <c r="C33" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="D33" s="1"/>
-      <c r="E33" s="36" t="s">
-        <v>313</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="H33" s="37">
-        <v>99</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="J33" s="38">
-        <v>46168</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="L33" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="M33" s="37">
-        <v>31324</v>
-      </c>
-      <c r="N33" s="39">
-        <v>32500</v>
-      </c>
-      <c r="O33" s="132" t="s">
-        <v>339</v>
-      </c>
-      <c r="P33" s="40"/>
-      <c r="Q33" s="40"/>
-      <c r="R33" s="217" t="s">
-        <v>325</v>
-      </c>
-      <c r="S33" s="41"/>
-      <c r="T33" s="42"/>
-      <c r="U33" s="43"/>
-      <c r="V33" s="43"/>
-      <c r="W33" s="43"/>
-      <c r="X33" s="43"/>
-      <c r="Y33" s="43"/>
-      <c r="Z33" s="43"/>
-      <c r="AA33" s="43"/>
-      <c r="AB33" s="43"/>
-      <c r="AC33" s="43"/>
-      <c r="AD33" s="43"/>
-      <c r="AE33" s="43"/>
-      <c r="AF33" s="43"/>
-      <c r="AG33" s="43"/>
-      <c r="AH33" s="43"/>
-      <c r="AI33" s="43"/>
-      <c r="AJ33" s="43"/>
-      <c r="AK33" s="43"/>
-      <c r="AL33" s="43"/>
-      <c r="AM33" s="43"/>
-      <c r="AN33" s="43"/>
-      <c r="AO33" s="43"/>
-      <c r="AP33" s="43"/>
-      <c r="AQ33" s="43"/>
-      <c r="AR33" s="43"/>
-      <c r="AS33" s="43"/>
-      <c r="AT33" s="43"/>
-      <c r="AU33" s="43"/>
-      <c r="AV33" s="43"/>
-      <c r="AW33" s="43"/>
-      <c r="AX33" s="43"/>
-      <c r="AY33" s="43"/>
-      <c r="AZ33" s="44"/>
-      <c r="BA33" s="44"/>
-    </row>
-    <row r="34" spans="1:53" s="2" customFormat="1" ht="4.5" customHeight="1">
-      <c r="B34" s="48"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="50"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="50"/>
-      <c r="I34" s="50"/>
-      <c r="J34" s="51"/>
-      <c r="K34" s="50"/>
-      <c r="L34" s="51"/>
-      <c r="M34" s="50"/>
-      <c r="N34" s="50"/>
-      <c r="O34" s="50"/>
-      <c r="P34" s="50"/>
-      <c r="Q34" s="50"/>
-      <c r="R34" s="49"/>
-      <c r="S34" s="52"/>
-    </row>
-    <row r="35" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="30" spans="1:53" s="2" customFormat="1" ht="4.5" customHeight="1">
+      <c r="B30" s="48"/>
+      <c r="C30" s="49"/>
+      <c r="D30" s="49"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="50"/>
+      <c r="G30" s="50"/>
+      <c r="H30" s="50"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="51"/>
+      <c r="K30" s="50"/>
+      <c r="L30" s="51"/>
+      <c r="M30" s="50"/>
+      <c r="N30" s="50"/>
+      <c r="O30" s="50"/>
+      <c r="P30" s="50"/>
+      <c r="Q30" s="50"/>
+      <c r="R30" s="49"/>
+      <c r="S30" s="52"/>
+    </row>
+    <row r="31" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7"/>
+    </row>
+    <row r="32" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="7"/>
+    </row>
+    <row r="33" spans="5:17" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+    </row>
+    <row r="34" spans="5:17" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="7"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7"/>
+      <c r="Q34" s="7"/>
+    </row>
+    <row r="35" spans="5:17" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
@@ -6177,7 +5872,7 @@
       <c r="P35" s="7"/>
       <c r="Q35" s="7"/>
     </row>
-    <row r="36" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="36" spans="5:17" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
@@ -6192,7 +5887,7 @@
       <c r="P36" s="7"/>
       <c r="Q36" s="7"/>
     </row>
-    <row r="37" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="37" spans="5:17" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
@@ -6207,7 +5902,7 @@
       <c r="P37" s="7"/>
       <c r="Q37" s="7"/>
     </row>
-    <row r="38" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="38" spans="5:17" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
@@ -6222,7 +5917,7 @@
       <c r="P38" s="7"/>
       <c r="Q38" s="7"/>
     </row>
-    <row r="39" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="39" spans="5:17" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
@@ -6237,7 +5932,7 @@
       <c r="P39" s="7"/>
       <c r="Q39" s="7"/>
     </row>
-    <row r="40" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="40" spans="5:17" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
@@ -6252,7 +5947,7 @@
       <c r="P40" s="7"/>
       <c r="Q40" s="7"/>
     </row>
-    <row r="41" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="41" spans="5:17" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
@@ -6267,7 +5962,7 @@
       <c r="P41" s="7"/>
       <c r="Q41" s="7"/>
     </row>
-    <row r="42" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="42" spans="5:17" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
@@ -6282,7 +5977,7 @@
       <c r="P42" s="7"/>
       <c r="Q42" s="7"/>
     </row>
-    <row r="43" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="43" spans="5:17" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
@@ -6297,7 +5992,7 @@
       <c r="P43" s="7"/>
       <c r="Q43" s="7"/>
     </row>
-    <row r="44" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="44" spans="5:17" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
@@ -6312,7 +6007,7 @@
       <c r="P44" s="7"/>
       <c r="Q44" s="7"/>
     </row>
-    <row r="45" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="45" spans="5:17" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
@@ -6327,7 +6022,7 @@
       <c r="P45" s="7"/>
       <c r="Q45" s="7"/>
     </row>
-    <row r="46" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="46" spans="5:17" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
@@ -6342,7 +6037,7 @@
       <c r="P46" s="7"/>
       <c r="Q46" s="7"/>
     </row>
-    <row r="47" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="47" spans="5:17" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
@@ -6357,7 +6052,7 @@
       <c r="P47" s="7"/>
       <c r="Q47" s="7"/>
     </row>
-    <row r="48" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="48" spans="5:17" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
@@ -8382,7 +8077,11 @@
       <c r="P182" s="7"/>
       <c r="Q182" s="7"/>
     </row>
-    <row r="183" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="183" spans="1:53" s="6" customFormat="1" ht="15" customHeight="1">
+      <c r="A183" s="2"/>
+      <c r="B183" s="2"/>
+      <c r="C183" s="2"/>
+      <c r="D183" s="2"/>
       <c r="E183" s="7"/>
       <c r="F183" s="7"/>
       <c r="G183" s="7"/>
@@ -8396,8 +8095,48 @@
       <c r="O183" s="7"/>
       <c r="P183" s="7"/>
       <c r="Q183" s="7"/>
-    </row>
-    <row r="184" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="R183" s="2"/>
+      <c r="S183" s="2"/>
+      <c r="T183" s="2"/>
+      <c r="U183" s="2"/>
+      <c r="V183" s="2"/>
+      <c r="W183" s="2"/>
+      <c r="X183" s="2"/>
+      <c r="Y183" s="2"/>
+      <c r="Z183" s="2"/>
+      <c r="AA183" s="2"/>
+      <c r="AB183" s="2"/>
+      <c r="AC183" s="2"/>
+      <c r="AD183" s="2"/>
+      <c r="AE183" s="2"/>
+      <c r="AF183" s="2"/>
+      <c r="AG183" s="2"/>
+      <c r="AH183" s="2"/>
+      <c r="AI183" s="2"/>
+      <c r="AJ183" s="2"/>
+      <c r="AK183" s="2"/>
+      <c r="AL183" s="2"/>
+      <c r="AM183" s="2"/>
+      <c r="AN183" s="2"/>
+      <c r="AO183" s="2"/>
+      <c r="AP183" s="2"/>
+      <c r="AQ183" s="2"/>
+      <c r="AR183" s="2"/>
+      <c r="AS183" s="2"/>
+      <c r="AT183" s="2"/>
+      <c r="AU183" s="2"/>
+      <c r="AV183" s="2"/>
+      <c r="AW183" s="2"/>
+      <c r="AX183" s="2"/>
+      <c r="AY183" s="2"/>
+      <c r="AZ183" s="2"/>
+      <c r="BA183" s="2"/>
+    </row>
+    <row r="184" spans="1:53" s="6" customFormat="1" ht="15" customHeight="1">
+      <c r="A184" s="2"/>
+      <c r="B184" s="2"/>
+      <c r="C184" s="2"/>
+      <c r="D184" s="2"/>
       <c r="E184" s="7"/>
       <c r="F184" s="7"/>
       <c r="G184" s="7"/>
@@ -8411,8 +8150,48 @@
       <c r="O184" s="7"/>
       <c r="P184" s="7"/>
       <c r="Q184" s="7"/>
-    </row>
-    <row r="185" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="R184" s="2"/>
+      <c r="S184" s="2"/>
+      <c r="T184" s="2"/>
+      <c r="U184" s="2"/>
+      <c r="V184" s="2"/>
+      <c r="W184" s="2"/>
+      <c r="X184" s="2"/>
+      <c r="Y184" s="2"/>
+      <c r="Z184" s="2"/>
+      <c r="AA184" s="2"/>
+      <c r="AB184" s="2"/>
+      <c r="AC184" s="2"/>
+      <c r="AD184" s="2"/>
+      <c r="AE184" s="2"/>
+      <c r="AF184" s="2"/>
+      <c r="AG184" s="2"/>
+      <c r="AH184" s="2"/>
+      <c r="AI184" s="2"/>
+      <c r="AJ184" s="2"/>
+      <c r="AK184" s="2"/>
+      <c r="AL184" s="2"/>
+      <c r="AM184" s="2"/>
+      <c r="AN184" s="2"/>
+      <c r="AO184" s="2"/>
+      <c r="AP184" s="2"/>
+      <c r="AQ184" s="2"/>
+      <c r="AR184" s="2"/>
+      <c r="AS184" s="2"/>
+      <c r="AT184" s="2"/>
+      <c r="AU184" s="2"/>
+      <c r="AV184" s="2"/>
+      <c r="AW184" s="2"/>
+      <c r="AX184" s="2"/>
+      <c r="AY184" s="2"/>
+      <c r="AZ184" s="2"/>
+      <c r="BA184" s="2"/>
+    </row>
+    <row r="185" spans="1:53" s="6" customFormat="1" ht="15" customHeight="1">
+      <c r="A185" s="2"/>
+      <c r="B185" s="2"/>
+      <c r="C185" s="2"/>
+      <c r="D185" s="2"/>
       <c r="E185" s="7"/>
       <c r="F185" s="7"/>
       <c r="G185" s="7"/>
@@ -8426,8 +8205,48 @@
       <c r="O185" s="7"/>
       <c r="P185" s="7"/>
       <c r="Q185" s="7"/>
-    </row>
-    <row r="186" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="R185" s="2"/>
+      <c r="S185" s="2"/>
+      <c r="T185" s="2"/>
+      <c r="U185" s="2"/>
+      <c r="V185" s="2"/>
+      <c r="W185" s="2"/>
+      <c r="X185" s="2"/>
+      <c r="Y185" s="2"/>
+      <c r="Z185" s="2"/>
+      <c r="AA185" s="2"/>
+      <c r="AB185" s="2"/>
+      <c r="AC185" s="2"/>
+      <c r="AD185" s="2"/>
+      <c r="AE185" s="2"/>
+      <c r="AF185" s="2"/>
+      <c r="AG185" s="2"/>
+      <c r="AH185" s="2"/>
+      <c r="AI185" s="2"/>
+      <c r="AJ185" s="2"/>
+      <c r="AK185" s="2"/>
+      <c r="AL185" s="2"/>
+      <c r="AM185" s="2"/>
+      <c r="AN185" s="2"/>
+      <c r="AO185" s="2"/>
+      <c r="AP185" s="2"/>
+      <c r="AQ185" s="2"/>
+      <c r="AR185" s="2"/>
+      <c r="AS185" s="2"/>
+      <c r="AT185" s="2"/>
+      <c r="AU185" s="2"/>
+      <c r="AV185" s="2"/>
+      <c r="AW185" s="2"/>
+      <c r="AX185" s="2"/>
+      <c r="AY185" s="2"/>
+      <c r="AZ185" s="2"/>
+      <c r="BA185" s="2"/>
+    </row>
+    <row r="186" spans="1:53" s="6" customFormat="1" ht="15" customHeight="1">
+      <c r="A186" s="2"/>
+      <c r="B186" s="2"/>
+      <c r="C186" s="2"/>
+      <c r="D186" s="2"/>
       <c r="E186" s="7"/>
       <c r="F186" s="7"/>
       <c r="G186" s="7"/>
@@ -8441,6 +8260,42 @@
       <c r="O186" s="7"/>
       <c r="P186" s="7"/>
       <c r="Q186" s="7"/>
+      <c r="R186" s="2"/>
+      <c r="S186" s="2"/>
+      <c r="T186" s="2"/>
+      <c r="U186" s="2"/>
+      <c r="V186" s="2"/>
+      <c r="W186" s="2"/>
+      <c r="X186" s="2"/>
+      <c r="Y186" s="2"/>
+      <c r="Z186" s="2"/>
+      <c r="AA186" s="2"/>
+      <c r="AB186" s="2"/>
+      <c r="AC186" s="2"/>
+      <c r="AD186" s="2"/>
+      <c r="AE186" s="2"/>
+      <c r="AF186" s="2"/>
+      <c r="AG186" s="2"/>
+      <c r="AH186" s="2"/>
+      <c r="AI186" s="2"/>
+      <c r="AJ186" s="2"/>
+      <c r="AK186" s="2"/>
+      <c r="AL186" s="2"/>
+      <c r="AM186" s="2"/>
+      <c r="AN186" s="2"/>
+      <c r="AO186" s="2"/>
+      <c r="AP186" s="2"/>
+      <c r="AQ186" s="2"/>
+      <c r="AR186" s="2"/>
+      <c r="AS186" s="2"/>
+      <c r="AT186" s="2"/>
+      <c r="AU186" s="2"/>
+      <c r="AV186" s="2"/>
+      <c r="AW186" s="2"/>
+      <c r="AX186" s="2"/>
+      <c r="AY186" s="2"/>
+      <c r="AZ186" s="2"/>
+      <c r="BA186" s="2"/>
     </row>
     <row r="187" spans="1:53" s="6" customFormat="1" ht="15" customHeight="1">
       <c r="A187" s="2"/>
@@ -8610,23 +8465,19 @@
     <row r="190" spans="1:53" s="6" customFormat="1" ht="15" customHeight="1">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
-      <c r="C190" s="2"/>
-      <c r="D190" s="2"/>
-      <c r="E190" s="7"/>
-      <c r="F190" s="7"/>
-      <c r="G190" s="7"/>
-      <c r="H190" s="7"/>
-      <c r="I190" s="7"/>
-      <c r="J190" s="8"/>
-      <c r="K190" s="7"/>
-      <c r="L190" s="8"/>
-      <c r="M190" s="7"/>
-      <c r="N190" s="7"/>
-      <c r="O190" s="7"/>
-      <c r="P190" s="7"/>
-      <c r="Q190" s="7"/>
-      <c r="R190" s="2"/>
-      <c r="S190" s="2"/>
+      <c r="E190" s="53"/>
+      <c r="F190" s="53"/>
+      <c r="G190" s="53"/>
+      <c r="H190" s="53"/>
+      <c r="I190" s="53"/>
+      <c r="J190" s="54"/>
+      <c r="K190" s="53"/>
+      <c r="L190" s="54"/>
+      <c r="M190" s="53"/>
+      <c r="N190" s="53"/>
+      <c r="O190" s="53"/>
+      <c r="P190" s="53"/>
+      <c r="Q190" s="53"/>
       <c r="T190" s="2"/>
       <c r="U190" s="2"/>
       <c r="V190" s="2"/>
@@ -8659,29 +8510,23 @@
       <c r="AW190" s="2"/>
       <c r="AX190" s="2"/>
       <c r="AY190" s="2"/>
-      <c r="AZ190" s="2"/>
-      <c r="BA190" s="2"/>
     </row>
     <row r="191" spans="1:53" s="6" customFormat="1" ht="15" customHeight="1">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
-      <c r="C191" s="2"/>
-      <c r="D191" s="2"/>
-      <c r="E191" s="7"/>
-      <c r="F191" s="7"/>
-      <c r="G191" s="7"/>
-      <c r="H191" s="7"/>
-      <c r="I191" s="7"/>
-      <c r="J191" s="8"/>
-      <c r="K191" s="7"/>
-      <c r="L191" s="8"/>
-      <c r="M191" s="7"/>
-      <c r="N191" s="7"/>
-      <c r="O191" s="7"/>
-      <c r="P191" s="7"/>
-      <c r="Q191" s="7"/>
-      <c r="R191" s="2"/>
-      <c r="S191" s="2"/>
+      <c r="E191" s="53"/>
+      <c r="F191" s="53"/>
+      <c r="G191" s="53"/>
+      <c r="H191" s="53"/>
+      <c r="I191" s="53"/>
+      <c r="J191" s="54"/>
+      <c r="K191" s="53"/>
+      <c r="L191" s="54"/>
+      <c r="M191" s="53"/>
+      <c r="N191" s="53"/>
+      <c r="O191" s="53"/>
+      <c r="P191" s="53"/>
+      <c r="Q191" s="53"/>
       <c r="T191" s="2"/>
       <c r="U191" s="2"/>
       <c r="V191" s="2"/>
@@ -8714,29 +8559,23 @@
       <c r="AW191" s="2"/>
       <c r="AX191" s="2"/>
       <c r="AY191" s="2"/>
-      <c r="AZ191" s="2"/>
-      <c r="BA191" s="2"/>
     </row>
     <row r="192" spans="1:53" s="6" customFormat="1" ht="15" customHeight="1">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
-      <c r="C192" s="2"/>
-      <c r="D192" s="2"/>
-      <c r="E192" s="7"/>
-      <c r="F192" s="7"/>
-      <c r="G192" s="7"/>
-      <c r="H192" s="7"/>
-      <c r="I192" s="7"/>
-      <c r="J192" s="8"/>
-      <c r="K192" s="7"/>
-      <c r="L192" s="8"/>
-      <c r="M192" s="7"/>
-      <c r="N192" s="7"/>
-      <c r="O192" s="7"/>
-      <c r="P192" s="7"/>
-      <c r="Q192" s="7"/>
-      <c r="R192" s="2"/>
-      <c r="S192" s="2"/>
+      <c r="E192" s="53"/>
+      <c r="F192" s="53"/>
+      <c r="G192" s="53"/>
+      <c r="H192" s="53"/>
+      <c r="I192" s="53"/>
+      <c r="J192" s="54"/>
+      <c r="K192" s="53"/>
+      <c r="L192" s="54"/>
+      <c r="M192" s="53"/>
+      <c r="N192" s="53"/>
+      <c r="O192" s="53"/>
+      <c r="P192" s="53"/>
+      <c r="Q192" s="53"/>
       <c r="T192" s="2"/>
       <c r="U192" s="2"/>
       <c r="V192" s="2"/>
@@ -8769,29 +8608,23 @@
       <c r="AW192" s="2"/>
       <c r="AX192" s="2"/>
       <c r="AY192" s="2"/>
-      <c r="AZ192" s="2"/>
-      <c r="BA192" s="2"/>
     </row>
     <row r="193" spans="1:53" s="6" customFormat="1" ht="15" customHeight="1">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
-      <c r="C193" s="2"/>
-      <c r="D193" s="2"/>
-      <c r="E193" s="7"/>
-      <c r="F193" s="7"/>
-      <c r="G193" s="7"/>
-      <c r="H193" s="7"/>
-      <c r="I193" s="7"/>
-      <c r="J193" s="8"/>
-      <c r="K193" s="7"/>
-      <c r="L193" s="8"/>
-      <c r="M193" s="7"/>
-      <c r="N193" s="7"/>
-      <c r="O193" s="7"/>
-      <c r="P193" s="7"/>
-      <c r="Q193" s="7"/>
-      <c r="R193" s="2"/>
-      <c r="S193" s="2"/>
+      <c r="E193" s="53"/>
+      <c r="F193" s="53"/>
+      <c r="G193" s="53"/>
+      <c r="H193" s="53"/>
+      <c r="I193" s="53"/>
+      <c r="J193" s="54"/>
+      <c r="K193" s="53"/>
+      <c r="L193" s="54"/>
+      <c r="M193" s="53"/>
+      <c r="N193" s="53"/>
+      <c r="O193" s="53"/>
+      <c r="P193" s="53"/>
+      <c r="Q193" s="53"/>
       <c r="T193" s="2"/>
       <c r="U193" s="2"/>
       <c r="V193" s="2"/>
@@ -8824,8 +8657,6 @@
       <c r="AW193" s="2"/>
       <c r="AX193" s="2"/>
       <c r="AY193" s="2"/>
-      <c r="AZ193" s="2"/>
-      <c r="BA193" s="2"/>
     </row>
     <row r="194" spans="1:53" s="6" customFormat="1" ht="15" customHeight="1">
       <c r="A194" s="2"/>
@@ -9170,9 +9001,9 @@
       <c r="AX200" s="2"/>
       <c r="AY200" s="2"/>
     </row>
-    <row r="201" spans="1:53" s="6" customFormat="1" ht="15" customHeight="1">
-      <c r="A201" s="2"/>
-      <c r="B201" s="2"/>
+    <row r="201" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="C201" s="6"/>
+      <c r="D201" s="6"/>
       <c r="E201" s="53"/>
       <c r="F201" s="53"/>
       <c r="G201" s="53"/>
@@ -9186,42 +9017,14 @@
       <c r="O201" s="53"/>
       <c r="P201" s="53"/>
       <c r="Q201" s="53"/>
-      <c r="T201" s="2"/>
-      <c r="U201" s="2"/>
-      <c r="V201" s="2"/>
-      <c r="W201" s="2"/>
-      <c r="X201" s="2"/>
-      <c r="Y201" s="2"/>
-      <c r="Z201" s="2"/>
-      <c r="AA201" s="2"/>
-      <c r="AB201" s="2"/>
-      <c r="AC201" s="2"/>
-      <c r="AD201" s="2"/>
-      <c r="AE201" s="2"/>
-      <c r="AF201" s="2"/>
-      <c r="AG201" s="2"/>
-      <c r="AH201" s="2"/>
-      <c r="AI201" s="2"/>
-      <c r="AJ201" s="2"/>
-      <c r="AK201" s="2"/>
-      <c r="AL201" s="2"/>
-      <c r="AM201" s="2"/>
-      <c r="AN201" s="2"/>
-      <c r="AO201" s="2"/>
-      <c r="AP201" s="2"/>
-      <c r="AQ201" s="2"/>
-      <c r="AR201" s="2"/>
-      <c r="AS201" s="2"/>
-      <c r="AT201" s="2"/>
-      <c r="AU201" s="2"/>
-      <c r="AV201" s="2"/>
-      <c r="AW201" s="2"/>
-      <c r="AX201" s="2"/>
-      <c r="AY201" s="2"/>
-    </row>
-    <row r="202" spans="1:53" s="6" customFormat="1" ht="15" customHeight="1">
-      <c r="A202" s="2"/>
-      <c r="B202" s="2"/>
+      <c r="R201" s="6"/>
+      <c r="S201" s="6"/>
+      <c r="AZ201" s="6"/>
+      <c r="BA201" s="6"/>
+    </row>
+    <row r="202" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="C202" s="6"/>
+      <c r="D202" s="6"/>
       <c r="E202" s="53"/>
       <c r="F202" s="53"/>
       <c r="G202" s="53"/>
@@ -9235,42 +9038,14 @@
       <c r="O202" s="53"/>
       <c r="P202" s="53"/>
       <c r="Q202" s="53"/>
-      <c r="T202" s="2"/>
-      <c r="U202" s="2"/>
-      <c r="V202" s="2"/>
-      <c r="W202" s="2"/>
-      <c r="X202" s="2"/>
-      <c r="Y202" s="2"/>
-      <c r="Z202" s="2"/>
-      <c r="AA202" s="2"/>
-      <c r="AB202" s="2"/>
-      <c r="AC202" s="2"/>
-      <c r="AD202" s="2"/>
-      <c r="AE202" s="2"/>
-      <c r="AF202" s="2"/>
-      <c r="AG202" s="2"/>
-      <c r="AH202" s="2"/>
-      <c r="AI202" s="2"/>
-      <c r="AJ202" s="2"/>
-      <c r="AK202" s="2"/>
-      <c r="AL202" s="2"/>
-      <c r="AM202" s="2"/>
-      <c r="AN202" s="2"/>
-      <c r="AO202" s="2"/>
-      <c r="AP202" s="2"/>
-      <c r="AQ202" s="2"/>
-      <c r="AR202" s="2"/>
-      <c r="AS202" s="2"/>
-      <c r="AT202" s="2"/>
-      <c r="AU202" s="2"/>
-      <c r="AV202" s="2"/>
-      <c r="AW202" s="2"/>
-      <c r="AX202" s="2"/>
-      <c r="AY202" s="2"/>
-    </row>
-    <row r="203" spans="1:53" s="6" customFormat="1" ht="15" customHeight="1">
-      <c r="A203" s="2"/>
-      <c r="B203" s="2"/>
+      <c r="R202" s="6"/>
+      <c r="S202" s="6"/>
+      <c r="AZ202" s="6"/>
+      <c r="BA202" s="6"/>
+    </row>
+    <row r="203" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="C203" s="6"/>
+      <c r="D203" s="6"/>
       <c r="E203" s="53"/>
       <c r="F203" s="53"/>
       <c r="G203" s="53"/>
@@ -9284,42 +9059,14 @@
       <c r="O203" s="53"/>
       <c r="P203" s="53"/>
       <c r="Q203" s="53"/>
-      <c r="T203" s="2"/>
-      <c r="U203" s="2"/>
-      <c r="V203" s="2"/>
-      <c r="W203" s="2"/>
-      <c r="X203" s="2"/>
-      <c r="Y203" s="2"/>
-      <c r="Z203" s="2"/>
-      <c r="AA203" s="2"/>
-      <c r="AB203" s="2"/>
-      <c r="AC203" s="2"/>
-      <c r="AD203" s="2"/>
-      <c r="AE203" s="2"/>
-      <c r="AF203" s="2"/>
-      <c r="AG203" s="2"/>
-      <c r="AH203" s="2"/>
-      <c r="AI203" s="2"/>
-      <c r="AJ203" s="2"/>
-      <c r="AK203" s="2"/>
-      <c r="AL203" s="2"/>
-      <c r="AM203" s="2"/>
-      <c r="AN203" s="2"/>
-      <c r="AO203" s="2"/>
-      <c r="AP203" s="2"/>
-      <c r="AQ203" s="2"/>
-      <c r="AR203" s="2"/>
-      <c r="AS203" s="2"/>
-      <c r="AT203" s="2"/>
-      <c r="AU203" s="2"/>
-      <c r="AV203" s="2"/>
-      <c r="AW203" s="2"/>
-      <c r="AX203" s="2"/>
-      <c r="AY203" s="2"/>
-    </row>
-    <row r="204" spans="1:53" s="6" customFormat="1" ht="15" customHeight="1">
-      <c r="A204" s="2"/>
-      <c r="B204" s="2"/>
+      <c r="R203" s="6"/>
+      <c r="S203" s="6"/>
+      <c r="AZ203" s="6"/>
+      <c r="BA203" s="6"/>
+    </row>
+    <row r="204" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
+      <c r="C204" s="6"/>
+      <c r="D204" s="6"/>
       <c r="E204" s="53"/>
       <c r="F204" s="53"/>
       <c r="G204" s="53"/>
@@ -9333,38 +9080,10 @@
       <c r="O204" s="53"/>
       <c r="P204" s="53"/>
       <c r="Q204" s="53"/>
-      <c r="T204" s="2"/>
-      <c r="U204" s="2"/>
-      <c r="V204" s="2"/>
-      <c r="W204" s="2"/>
-      <c r="X204" s="2"/>
-      <c r="Y204" s="2"/>
-      <c r="Z204" s="2"/>
-      <c r="AA204" s="2"/>
-      <c r="AB204" s="2"/>
-      <c r="AC204" s="2"/>
-      <c r="AD204" s="2"/>
-      <c r="AE204" s="2"/>
-      <c r="AF204" s="2"/>
-      <c r="AG204" s="2"/>
-      <c r="AH204" s="2"/>
-      <c r="AI204" s="2"/>
-      <c r="AJ204" s="2"/>
-      <c r="AK204" s="2"/>
-      <c r="AL204" s="2"/>
-      <c r="AM204" s="2"/>
-      <c r="AN204" s="2"/>
-      <c r="AO204" s="2"/>
-      <c r="AP204" s="2"/>
-      <c r="AQ204" s="2"/>
-      <c r="AR204" s="2"/>
-      <c r="AS204" s="2"/>
-      <c r="AT204" s="2"/>
-      <c r="AU204" s="2"/>
-      <c r="AV204" s="2"/>
-      <c r="AW204" s="2"/>
-      <c r="AX204" s="2"/>
-      <c r="AY204" s="2"/>
+      <c r="R204" s="6"/>
+      <c r="S204" s="6"/>
+      <c r="AZ204" s="6"/>
+      <c r="BA204" s="6"/>
     </row>
     <row r="205" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="C205" s="6"/>
@@ -9430,90 +9149,82 @@
       <c r="BA207" s="6"/>
     </row>
     <row r="208" spans="1:53" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="C208" s="6"/>
-      <c r="D208" s="6"/>
-      <c r="E208" s="53"/>
-      <c r="F208" s="53"/>
-      <c r="G208" s="53"/>
-      <c r="H208" s="53"/>
-      <c r="I208" s="53"/>
-      <c r="J208" s="54"/>
-      <c r="K208" s="53"/>
-      <c r="L208" s="54"/>
-      <c r="M208" s="53"/>
-      <c r="N208" s="53"/>
-      <c r="O208" s="53"/>
-      <c r="P208" s="53"/>
-      <c r="Q208" s="53"/>
-      <c r="R208" s="6"/>
-      <c r="S208" s="6"/>
+      <c r="E208" s="7"/>
+      <c r="F208" s="7"/>
+      <c r="G208" s="7"/>
+      <c r="H208" s="7"/>
+      <c r="I208" s="7"/>
+      <c r="J208" s="8"/>
+      <c r="K208" s="7"/>
+      <c r="L208" s="8"/>
+      <c r="M208" s="7"/>
+      <c r="N208" s="7"/>
+      <c r="O208" s="7"/>
+      <c r="P208" s="7"/>
+      <c r="Q208" s="7"/>
       <c r="AZ208" s="6"/>
       <c r="BA208" s="6"/>
     </row>
-    <row r="209" spans="3:53" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="C209" s="6"/>
-      <c r="D209" s="6"/>
-      <c r="E209" s="53"/>
-      <c r="F209" s="53"/>
-      <c r="G209" s="53"/>
-      <c r="H209" s="53"/>
-      <c r="I209" s="53"/>
-      <c r="J209" s="54"/>
-      <c r="K209" s="53"/>
-      <c r="L209" s="54"/>
-      <c r="M209" s="53"/>
-      <c r="N209" s="53"/>
-      <c r="O209" s="53"/>
-      <c r="P209" s="53"/>
-      <c r="Q209" s="53"/>
-      <c r="R209" s="6"/>
-      <c r="S209" s="6"/>
-      <c r="AZ209" s="6"/>
-      <c r="BA209" s="6"/>
-    </row>
-    <row r="210" spans="3:53" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="C210" s="6"/>
-      <c r="D210" s="6"/>
-      <c r="E210" s="53"/>
-      <c r="F210" s="53"/>
-      <c r="G210" s="53"/>
-      <c r="H210" s="53"/>
-      <c r="I210" s="53"/>
-      <c r="J210" s="54"/>
-      <c r="K210" s="53"/>
-      <c r="L210" s="54"/>
-      <c r="M210" s="53"/>
-      <c r="N210" s="53"/>
-      <c r="O210" s="53"/>
-      <c r="P210" s="53"/>
-      <c r="Q210" s="53"/>
-      <c r="R210" s="6"/>
-      <c r="S210" s="6"/>
-      <c r="AZ210" s="6"/>
-      <c r="BA210" s="6"/>
-    </row>
-    <row r="211" spans="3:53" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="C211" s="6"/>
-      <c r="D211" s="6"/>
-      <c r="E211" s="53"/>
-      <c r="F211" s="53"/>
-      <c r="G211" s="53"/>
-      <c r="H211" s="53"/>
-      <c r="I211" s="53"/>
-      <c r="J211" s="54"/>
-      <c r="K211" s="53"/>
-      <c r="L211" s="54"/>
-      <c r="M211" s="53"/>
-      <c r="N211" s="53"/>
-      <c r="O211" s="53"/>
-      <c r="P211" s="53"/>
-      <c r="Q211" s="53"/>
-      <c r="R211" s="6"/>
-      <c r="S211" s="6"/>
-      <c r="AZ211" s="6"/>
-      <c r="BA211" s="6"/>
-    </row>
-    <row r="212" spans="3:53" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="209" spans="3:19" ht="15" customHeight="1">
+      <c r="C209" s="2"/>
+      <c r="D209" s="2"/>
+      <c r="E209" s="7"/>
+      <c r="F209" s="7"/>
+      <c r="G209" s="7"/>
+      <c r="H209" s="7"/>
+      <c r="I209" s="7"/>
+      <c r="J209" s="8"/>
+      <c r="K209" s="7"/>
+      <c r="L209" s="8"/>
+      <c r="M209" s="7"/>
+      <c r="N209" s="7"/>
+      <c r="O209" s="7"/>
+      <c r="P209" s="7"/>
+      <c r="Q209" s="7"/>
+      <c r="R209" s="2"/>
+      <c r="S209" s="2"/>
+    </row>
+    <row r="210" spans="3:19" ht="15" customHeight="1">
+      <c r="C210" s="2"/>
+      <c r="D210" s="2"/>
+      <c r="E210" s="7"/>
+      <c r="F210" s="7"/>
+      <c r="G210" s="7"/>
+      <c r="H210" s="7"/>
+      <c r="I210" s="7"/>
+      <c r="J210" s="8"/>
+      <c r="K210" s="7"/>
+      <c r="L210" s="8"/>
+      <c r="M210" s="7"/>
+      <c r="N210" s="7"/>
+      <c r="O210" s="7"/>
+      <c r="P210" s="7"/>
+      <c r="Q210" s="7"/>
+      <c r="R210" s="2"/>
+      <c r="S210" s="2"/>
+    </row>
+    <row r="211" spans="3:19" ht="15" customHeight="1">
+      <c r="C211" s="2"/>
+      <c r="D211" s="2"/>
+      <c r="E211" s="7"/>
+      <c r="F211" s="7"/>
+      <c r="G211" s="7"/>
+      <c r="H211" s="7"/>
+      <c r="I211" s="7"/>
+      <c r="J211" s="8"/>
+      <c r="K211" s="7"/>
+      <c r="L211" s="8"/>
+      <c r="M211" s="7"/>
+      <c r="N211" s="7"/>
+      <c r="O211" s="7"/>
+      <c r="P211" s="7"/>
+      <c r="Q211" s="7"/>
+      <c r="R211" s="2"/>
+      <c r="S211" s="2"/>
+    </row>
+    <row r="212" spans="3:19" ht="15" customHeight="1">
+      <c r="C212" s="2"/>
+      <c r="D212" s="2"/>
       <c r="E212" s="7"/>
       <c r="F212" s="7"/>
       <c r="G212" s="7"/>
@@ -9527,10 +9238,10 @@
       <c r="O212" s="7"/>
       <c r="P212" s="7"/>
       <c r="Q212" s="7"/>
-      <c r="AZ212" s="6"/>
-      <c r="BA212" s="6"/>
-    </row>
-    <row r="213" spans="3:53" ht="15" customHeight="1">
+      <c r="R212" s="2"/>
+      <c r="S212" s="2"/>
+    </row>
+    <row r="213" spans="3:19" ht="15" customHeight="1">
       <c r="C213" s="2"/>
       <c r="D213" s="2"/>
       <c r="E213" s="7"/>
@@ -9549,7 +9260,7 @@
       <c r="R213" s="2"/>
       <c r="S213" s="2"/>
     </row>
-    <row r="214" spans="3:53" ht="15" customHeight="1">
+    <row r="214" spans="3:19" ht="15" customHeight="1">
       <c r="C214" s="2"/>
       <c r="D214" s="2"/>
       <c r="E214" s="7"/>
@@ -9568,7 +9279,7 @@
       <c r="R214" s="2"/>
       <c r="S214" s="2"/>
     </row>
-    <row r="215" spans="3:53" ht="15" customHeight="1">
+    <row r="215" spans="3:19" ht="15" customHeight="1">
       <c r="C215" s="2"/>
       <c r="D215" s="2"/>
       <c r="E215" s="7"/>
@@ -9587,82 +9298,6 @@
       <c r="R215" s="2"/>
       <c r="S215" s="2"/>
     </row>
-    <row r="216" spans="3:53" ht="15" customHeight="1">
-      <c r="C216" s="2"/>
-      <c r="D216" s="2"/>
-      <c r="E216" s="7"/>
-      <c r="F216" s="7"/>
-      <c r="G216" s="7"/>
-      <c r="H216" s="7"/>
-      <c r="I216" s="7"/>
-      <c r="J216" s="8"/>
-      <c r="K216" s="7"/>
-      <c r="L216" s="8"/>
-      <c r="M216" s="7"/>
-      <c r="N216" s="7"/>
-      <c r="O216" s="7"/>
-      <c r="P216" s="7"/>
-      <c r="Q216" s="7"/>
-      <c r="R216" s="2"/>
-      <c r="S216" s="2"/>
-    </row>
-    <row r="217" spans="3:53" ht="15" customHeight="1">
-      <c r="C217" s="2"/>
-      <c r="D217" s="2"/>
-      <c r="E217" s="7"/>
-      <c r="F217" s="7"/>
-      <c r="G217" s="7"/>
-      <c r="H217" s="7"/>
-      <c r="I217" s="7"/>
-      <c r="J217" s="8"/>
-      <c r="K217" s="7"/>
-      <c r="L217" s="8"/>
-      <c r="M217" s="7"/>
-      <c r="N217" s="7"/>
-      <c r="O217" s="7"/>
-      <c r="P217" s="7"/>
-      <c r="Q217" s="7"/>
-      <c r="R217" s="2"/>
-      <c r="S217" s="2"/>
-    </row>
-    <row r="218" spans="3:53" ht="15" customHeight="1">
-      <c r="C218" s="2"/>
-      <c r="D218" s="2"/>
-      <c r="E218" s="7"/>
-      <c r="F218" s="7"/>
-      <c r="G218" s="7"/>
-      <c r="H218" s="7"/>
-      <c r="I218" s="7"/>
-      <c r="J218" s="8"/>
-      <c r="K218" s="7"/>
-      <c r="L218" s="8"/>
-      <c r="M218" s="7"/>
-      <c r="N218" s="7"/>
-      <c r="O218" s="7"/>
-      <c r="P218" s="7"/>
-      <c r="Q218" s="7"/>
-      <c r="R218" s="2"/>
-      <c r="S218" s="2"/>
-    </row>
-    <row r="219" spans="3:53" ht="15" customHeight="1">
-      <c r="C219" s="2"/>
-      <c r="D219" s="2"/>
-      <c r="E219" s="7"/>
-      <c r="F219" s="7"/>
-      <c r="G219" s="7"/>
-      <c r="H219" s="7"/>
-      <c r="I219" s="7"/>
-      <c r="J219" s="8"/>
-      <c r="K219" s="7"/>
-      <c r="L219" s="8"/>
-      <c r="M219" s="7"/>
-      <c r="N219" s="7"/>
-      <c r="O219" s="7"/>
-      <c r="P219" s="7"/>
-      <c r="Q219" s="7"/>
-      <c r="R219" s="2"/>
-      <c r="S219" s="2"/>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C10:D10"/>
@@ -9677,7 +9312,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BH1048549"/>
+  <dimension ref="A1:BH1048545"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="0.77734375" style="104" customWidth="1"/>
@@ -9767,10 +9402,10 @@
       <c r="O3" s="16"/>
       <c r="P3" s="16"/>
       <c r="Q3" s="16"/>
-      <c r="R3" s="250">
-        <v>46227</v>
-      </c>
-      <c r="S3" s="250"/>
+      <c r="R3" s="245">
+        <v>46232</v>
+      </c>
+      <c r="S3" s="245"/>
       <c r="T3" s="19"/>
       <c r="U3" s="131"/>
     </row>
@@ -9947,13 +9582,13 @@
         <v>23</v>
       </c>
       <c r="F6" s="188" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="G6" s="188" t="s">
         <v>24</v>
       </c>
       <c r="H6" s="188" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="I6" s="189">
         <v>20270</v>
@@ -9981,12 +9616,12 @@
         <v>17900</v>
       </c>
       <c r="Q6" s="189" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="R6" s="189"/>
       <c r="S6" s="189"/>
-      <c r="T6" s="217" t="s">
-        <v>325</v>
+      <c r="T6" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="U6" s="192"/>
       <c r="V6" s="193"/>
@@ -10042,13 +9677,13 @@
         <v>23</v>
       </c>
       <c r="F7" s="188" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="G7" s="188" t="s">
         <v>29</v>
       </c>
       <c r="H7" s="188" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="I7" s="189">
         <v>13018</v>
@@ -10076,12 +9711,12 @@
         <v>18200</v>
       </c>
       <c r="Q7" s="189" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="R7" s="189"/>
       <c r="S7" s="189"/>
-      <c r="T7" s="217" t="s">
-        <v>325</v>
+      <c r="T7" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="U7" s="192"/>
       <c r="V7" s="193"/>
@@ -10124,28 +9759,61 @@
       <c r="BG7" s="193"/>
       <c r="BH7" s="193"/>
     </row>
-    <row r="8" spans="1:60" s="194" customFormat="1" ht="4.5" customHeight="1">
+    <row r="8" spans="1:60" s="194" customFormat="1" ht="19.5" customHeight="1">
       <c r="A8" s="185"/>
       <c r="B8" s="186"/>
-      <c r="C8" s="187"/>
-      <c r="D8" s="188"/>
-      <c r="E8" s="188"/>
-      <c r="F8" s="188"/>
-      <c r="G8" s="188"/>
-      <c r="H8" s="188"/>
-      <c r="I8" s="189"/>
-      <c r="J8" s="190"/>
-      <c r="K8" s="190"/>
-      <c r="L8" s="189"/>
-      <c r="M8" s="189"/>
-      <c r="N8" s="189"/>
-      <c r="O8" s="189"/>
-      <c r="P8" s="191"/>
-      <c r="Q8" s="189"/>
+      <c r="C8" s="187" t="s">
+        <v>124</v>
+      </c>
+      <c r="D8" s="188" t="s">
+        <v>123</v>
+      </c>
+      <c r="E8" s="188" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="188" t="s">
+        <v>401</v>
+      </c>
+      <c r="G8" s="188" t="s">
+        <v>125</v>
+      </c>
+      <c r="H8" s="188" t="s">
+        <v>402</v>
+      </c>
+      <c r="I8" s="189">
+        <v>14620</v>
+      </c>
+      <c r="J8" s="190">
+        <v>46200</v>
+      </c>
+      <c r="K8" s="190">
+        <v>46232</v>
+      </c>
+      <c r="L8" s="189">
+        <v>16461</v>
+      </c>
+      <c r="M8" s="189">
+        <v>347</v>
+      </c>
+      <c r="N8" s="189">
+        <v>200</v>
+      </c>
+      <c r="O8" s="189">
+        <f>P8-L8-M8-N8</f>
+        <v>1192</v>
+      </c>
+      <c r="P8" s="191">
+        <v>18200</v>
+      </c>
+      <c r="Q8" s="189" t="s">
+        <v>337</v>
+      </c>
       <c r="R8" s="189"/>
       <c r="S8" s="189"/>
-      <c r="T8" s="217"/>
-      <c r="U8" s="202"/>
+      <c r="T8" s="219" t="s">
+        <v>320</v>
+      </c>
+      <c r="U8" s="192"/>
       <c r="V8" s="193"/>
       <c r="W8" s="193"/>
       <c r="X8" s="193"/>
@@ -10190,57 +9858,55 @@
       <c r="A9" s="185"/>
       <c r="B9" s="186"/>
       <c r="C9" s="187" t="s">
-        <v>287</v>
+        <v>124</v>
       </c>
       <c r="D9" s="188" t="s">
         <v>123</v>
       </c>
       <c r="E9" s="188" t="s">
-        <v>290</v>
+        <v>23</v>
       </c>
       <c r="F9" s="188" t="s">
-        <v>288</v>
+        <v>403</v>
       </c>
       <c r="G9" s="188" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H9" s="188" t="s">
-        <v>289</v>
+        <v>404</v>
       </c>
       <c r="I9" s="189">
-        <v>714</v>
+        <v>14864</v>
       </c>
       <c r="J9" s="190">
-        <v>45044</v>
+        <v>46200</v>
       </c>
       <c r="K9" s="190">
-        <v>46141</v>
+        <v>46232</v>
       </c>
       <c r="L9" s="189">
-        <v>21308</v>
+        <v>16487</v>
       </c>
       <c r="M9" s="189">
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="N9" s="189">
         <v>200</v>
       </c>
       <c r="O9" s="189">
         <f>P9-L9-M9-N9</f>
-        <v>392</v>
+        <v>1201</v>
       </c>
       <c r="P9" s="191">
-        <v>21900</v>
+        <v>18200</v>
       </c>
       <c r="Q9" s="189" t="s">
-        <v>338</v>
-      </c>
-      <c r="R9" s="189" t="s">
-        <v>22</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="R9" s="189"/>
       <c r="S9" s="189"/>
-      <c r="T9" s="217" t="s">
-        <v>325</v>
+      <c r="T9" s="219" t="s">
+        <v>320</v>
       </c>
       <c r="U9" s="192"/>
       <c r="V9" s="193"/>
@@ -10283,61 +9949,28 @@
       <c r="BG9" s="193"/>
       <c r="BH9" s="193"/>
     </row>
-    <row r="10" spans="1:60" s="194" customFormat="1" ht="19.5" customHeight="1">
+    <row r="10" spans="1:60" s="194" customFormat="1" ht="4.5" customHeight="1">
       <c r="A10" s="185"/>
       <c r="B10" s="186"/>
-      <c r="C10" s="187" t="s">
-        <v>294</v>
-      </c>
-      <c r="D10" s="188" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" s="188" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="188" t="s">
-        <v>295</v>
-      </c>
-      <c r="G10" s="188" t="s">
-        <v>126</v>
-      </c>
-      <c r="H10" s="188" t="s">
-        <v>297</v>
-      </c>
-      <c r="I10" s="189">
-        <v>17297</v>
-      </c>
-      <c r="J10" s="190">
-        <v>45673</v>
-      </c>
-      <c r="K10" s="190">
-        <v>46162</v>
-      </c>
-      <c r="L10" s="189">
-        <v>20777</v>
-      </c>
-      <c r="M10" s="189">
-        <v>0</v>
-      </c>
-      <c r="N10" s="189">
-        <v>200</v>
-      </c>
-      <c r="O10" s="189">
-        <f t="shared" ref="O10:O11" si="0">P10-L10-M10-N10</f>
-        <v>1923</v>
-      </c>
-      <c r="P10" s="191">
-        <v>22900</v>
-      </c>
-      <c r="Q10" s="208" t="s">
-        <v>339</v>
-      </c>
+      <c r="C10" s="187"/>
+      <c r="D10" s="188"/>
+      <c r="E10" s="188"/>
+      <c r="F10" s="188"/>
+      <c r="G10" s="188"/>
+      <c r="H10" s="188"/>
+      <c r="I10" s="189"/>
+      <c r="J10" s="190"/>
+      <c r="K10" s="190"/>
+      <c r="L10" s="189"/>
+      <c r="M10" s="189"/>
+      <c r="N10" s="189"/>
+      <c r="O10" s="189"/>
+      <c r="P10" s="191"/>
+      <c r="Q10" s="189"/>
       <c r="R10" s="189"/>
       <c r="S10" s="189"/>
-      <c r="T10" s="217" t="s">
-        <v>325</v>
-      </c>
-      <c r="U10" s="192"/>
+      <c r="T10" s="216"/>
+      <c r="U10" s="202"/>
       <c r="V10" s="193"/>
       <c r="W10" s="193"/>
       <c r="X10" s="193"/>
@@ -10381,58 +10014,60 @@
     <row r="11" spans="1:60" s="194" customFormat="1" ht="19.5" customHeight="1">
       <c r="A11" s="185"/>
       <c r="B11" s="186"/>
-      <c r="C11" s="187" t="s">
-        <v>294</v>
-      </c>
-      <c r="D11" s="188" t="s">
+      <c r="C11" s="203" t="s">
+        <v>282</v>
+      </c>
+      <c r="D11" s="204" t="s">
         <v>123</v>
       </c>
-      <c r="E11" s="188" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="188" t="s">
-        <v>296</v>
-      </c>
-      <c r="G11" s="188" t="s">
-        <v>293</v>
-      </c>
-      <c r="H11" s="188" t="s">
-        <v>298</v>
-      </c>
-      <c r="I11" s="189">
-        <v>11991</v>
-      </c>
-      <c r="J11" s="190">
-        <v>45814</v>
-      </c>
-      <c r="K11" s="190">
-        <v>46162</v>
-      </c>
-      <c r="L11" s="189">
-        <v>21203</v>
-      </c>
-      <c r="M11" s="189">
+      <c r="E11" s="204" t="s">
+        <v>285</v>
+      </c>
+      <c r="F11" s="204" t="s">
+        <v>283</v>
+      </c>
+      <c r="G11" s="204" t="s">
+        <v>126</v>
+      </c>
+      <c r="H11" s="204" t="s">
+        <v>284</v>
+      </c>
+      <c r="I11" s="205">
+        <v>714</v>
+      </c>
+      <c r="J11" s="206">
+        <v>45044</v>
+      </c>
+      <c r="K11" s="206">
+        <v>46141</v>
+      </c>
+      <c r="L11" s="205">
+        <v>21308</v>
+      </c>
+      <c r="M11" s="205">
         <v>0</v>
       </c>
-      <c r="N11" s="189">
+      <c r="N11" s="205">
         <v>200</v>
       </c>
-      <c r="O11" s="189">
-        <f t="shared" si="0"/>
-        <v>1497</v>
-      </c>
-      <c r="P11" s="191">
-        <v>22900</v>
-      </c>
-      <c r="Q11" s="189" t="s">
-        <v>338</v>
-      </c>
-      <c r="R11" s="189" t="s">
-        <v>410</v>
-      </c>
-      <c r="S11" s="189"/>
+      <c r="O11" s="205">
+        <f>P11-L11-M11-N11</f>
+        <v>392</v>
+      </c>
+      <c r="P11" s="207">
+        <v>21900</v>
+      </c>
+      <c r="Q11" s="205" t="s">
+        <v>333</v>
+      </c>
+      <c r="R11" s="205" t="s">
+        <v>22</v>
+      </c>
+      <c r="S11" s="205" t="s">
+        <v>398</v>
+      </c>
       <c r="T11" s="217" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="U11" s="192"/>
       <c r="V11" s="193"/>
@@ -10478,58 +10113,56 @@
     <row r="12" spans="1:60" s="194" customFormat="1" ht="19.5" customHeight="1">
       <c r="A12" s="185"/>
       <c r="B12" s="186"/>
-      <c r="C12" s="203" t="s">
-        <v>294</v>
-      </c>
-      <c r="D12" s="204" t="s">
+      <c r="C12" s="187" t="s">
+        <v>289</v>
+      </c>
+      <c r="D12" s="188" t="s">
         <v>123</v>
       </c>
-      <c r="E12" s="204" t="s">
+      <c r="E12" s="188" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="204" t="s">
-        <v>353</v>
-      </c>
-      <c r="G12" s="204" t="s">
+      <c r="F12" s="188" t="s">
+        <v>290</v>
+      </c>
+      <c r="G12" s="188" t="s">
+        <v>126</v>
+      </c>
+      <c r="H12" s="188" t="s">
+        <v>292</v>
+      </c>
+      <c r="I12" s="189">
+        <v>17297</v>
+      </c>
+      <c r="J12" s="190">
+        <v>45673</v>
+      </c>
+      <c r="K12" s="190">
+        <v>46162</v>
+      </c>
+      <c r="L12" s="189">
+        <v>20777</v>
+      </c>
+      <c r="M12" s="189">
+        <v>0</v>
+      </c>
+      <c r="N12" s="189">
+        <v>200</v>
+      </c>
+      <c r="O12" s="189">
+        <f t="shared" ref="O12:O13" si="0">P12-L12-M12-N12</f>
+        <v>1923</v>
+      </c>
+      <c r="P12" s="191">
+        <v>22900</v>
+      </c>
+      <c r="Q12" s="208" t="s">
         <v>334</v>
       </c>
-      <c r="H12" s="204" t="s">
-        <v>354</v>
-      </c>
-      <c r="I12" s="205">
-        <v>8835</v>
-      </c>
-      <c r="J12" s="206">
-        <v>45769</v>
-      </c>
-      <c r="K12" s="206">
-        <v>46202</v>
-      </c>
-      <c r="L12" s="205">
-        <v>21295</v>
-      </c>
-      <c r="M12" s="205">
-        <v>0</v>
-      </c>
-      <c r="N12" s="205">
-        <v>200</v>
-      </c>
-      <c r="O12" s="205">
-        <f t="shared" ref="O12" si="1">P12-L12-M12-N12</f>
-        <v>1405</v>
-      </c>
-      <c r="P12" s="207">
-        <v>22900</v>
-      </c>
-      <c r="Q12" s="205" t="s">
-        <v>35</v>
-      </c>
-      <c r="R12" s="205"/>
-      <c r="S12" s="205" t="s">
-        <v>404</v>
-      </c>
-      <c r="T12" s="218" t="s">
-        <v>325</v>
+      <c r="R12" s="189"/>
+      <c r="S12" s="189"/>
+      <c r="T12" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="U12" s="192"/>
       <c r="V12" s="193"/>
@@ -10572,27 +10205,60 @@
       <c r="BG12" s="193"/>
       <c r="BH12" s="193"/>
     </row>
-    <row r="13" spans="1:60" s="194" customFormat="1" ht="15" customHeight="1">
+    <row r="13" spans="1:60" s="194" customFormat="1" ht="19.5" customHeight="1">
       <c r="A13" s="185"/>
       <c r="B13" s="186"/>
-      <c r="C13" s="187"/>
-      <c r="D13" s="188"/>
-      <c r="E13" s="188"/>
-      <c r="F13" s="188"/>
-      <c r="G13" s="188"/>
-      <c r="H13" s="188"/>
-      <c r="I13" s="189"/>
-      <c r="J13" s="190"/>
-      <c r="K13" s="190"/>
-      <c r="L13" s="189"/>
-      <c r="M13" s="189"/>
-      <c r="N13" s="189"/>
-      <c r="O13" s="189"/>
-      <c r="P13" s="191"/>
-      <c r="Q13" s="189"/>
+      <c r="C13" s="187" t="s">
+        <v>289</v>
+      </c>
+      <c r="D13" s="188" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" s="188" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="188" t="s">
+        <v>291</v>
+      </c>
+      <c r="G13" s="188" t="s">
+        <v>288</v>
+      </c>
+      <c r="H13" s="188" t="s">
+        <v>293</v>
+      </c>
+      <c r="I13" s="189">
+        <v>11991</v>
+      </c>
+      <c r="J13" s="190">
+        <v>45814</v>
+      </c>
+      <c r="K13" s="190">
+        <v>46162</v>
+      </c>
+      <c r="L13" s="189">
+        <v>21203</v>
+      </c>
+      <c r="M13" s="189">
+        <v>0</v>
+      </c>
+      <c r="N13" s="189">
+        <v>200</v>
+      </c>
+      <c r="O13" s="189">
+        <f t="shared" si="0"/>
+        <v>1497</v>
+      </c>
+      <c r="P13" s="191">
+        <v>22900</v>
+      </c>
+      <c r="Q13" s="189" t="s">
+        <v>333</v>
+      </c>
       <c r="R13" s="189"/>
       <c r="S13" s="189"/>
-      <c r="T13" s="219"/>
+      <c r="T13" s="216" t="s">
+        <v>320</v>
+      </c>
       <c r="U13" s="192"/>
       <c r="V13" s="193"/>
       <c r="W13" s="193"/>
@@ -10637,54 +10303,56 @@
     <row r="14" spans="1:60" s="194" customFormat="1" ht="19.5" customHeight="1">
       <c r="A14" s="185"/>
       <c r="B14" s="186"/>
-      <c r="C14" s="203" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" s="204" t="s">
-        <v>127</v>
-      </c>
-      <c r="E14" s="204"/>
-      <c r="F14" s="204" t="s">
-        <v>128</v>
-      </c>
-      <c r="G14" s="204" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" s="204" t="s">
-        <v>129</v>
-      </c>
-      <c r="I14" s="205">
-        <v>73752</v>
-      </c>
-      <c r="J14" s="206">
-        <v>43822</v>
-      </c>
-      <c r="K14" s="206">
-        <v>46105</v>
-      </c>
-      <c r="L14" s="205">
-        <v>10375</v>
-      </c>
-      <c r="M14" s="205">
+      <c r="C14" s="187" t="s">
+        <v>289</v>
+      </c>
+      <c r="D14" s="188" t="s">
+        <v>123</v>
+      </c>
+      <c r="E14" s="188" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="188" t="s">
+        <v>341</v>
+      </c>
+      <c r="G14" s="188" t="s">
+        <v>329</v>
+      </c>
+      <c r="H14" s="188" t="s">
+        <v>342</v>
+      </c>
+      <c r="I14" s="189">
+        <v>8835</v>
+      </c>
+      <c r="J14" s="190">
+        <v>45769</v>
+      </c>
+      <c r="K14" s="190">
+        <v>46202</v>
+      </c>
+      <c r="L14" s="189">
+        <v>21295</v>
+      </c>
+      <c r="M14" s="189">
         <v>0</v>
       </c>
-      <c r="N14" s="205">
-        <v>600</v>
-      </c>
-      <c r="O14" s="205">
-        <f>P14-L14-M14-N14</f>
-        <v>2825</v>
-      </c>
-      <c r="P14" s="207">
-        <v>13800</v>
-      </c>
-      <c r="Q14" s="227" t="s">
-        <v>339</v>
-      </c>
-      <c r="R14" s="205"/>
-      <c r="S14" s="205"/>
-      <c r="T14" s="218" t="s">
-        <v>325</v>
+      <c r="N14" s="189">
+        <v>200</v>
+      </c>
+      <c r="O14" s="189">
+        <f t="shared" ref="O14" si="1">P14-L14-M14-N14</f>
+        <v>1405</v>
+      </c>
+      <c r="P14" s="191">
+        <v>22900</v>
+      </c>
+      <c r="Q14" s="189" t="s">
+        <v>35</v>
+      </c>
+      <c r="R14" s="189"/>
+      <c r="S14" s="189"/>
+      <c r="T14" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="U14" s="192"/>
       <c r="V14" s="193"/>
@@ -10727,7 +10395,7 @@
       <c r="BG14" s="193"/>
       <c r="BH14" s="193"/>
     </row>
-    <row r="15" spans="1:60" s="194" customFormat="1" ht="4.5" customHeight="1">
+    <row r="15" spans="1:60" s="194" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="185"/>
       <c r="B15" s="186"/>
       <c r="C15" s="187"/>
@@ -10736,7 +10404,7 @@
       <c r="F15" s="188"/>
       <c r="G15" s="188"/>
       <c r="H15" s="188"/>
-      <c r="I15" s="209"/>
+      <c r="I15" s="189"/>
       <c r="J15" s="190"/>
       <c r="K15" s="190"/>
       <c r="L15" s="189"/>
@@ -10747,7 +10415,7 @@
       <c r="Q15" s="189"/>
       <c r="R15" s="189"/>
       <c r="S15" s="189"/>
-      <c r="T15" s="217"/>
+      <c r="T15" s="218"/>
       <c r="U15" s="192"/>
       <c r="V15" s="193"/>
       <c r="W15" s="193"/>
@@ -10793,7 +10461,7 @@
       <c r="A16" s="185"/>
       <c r="B16" s="186"/>
       <c r="C16" s="187" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D16" s="188" t="s">
         <v>123</v>
@@ -10802,13 +10470,13 @@
         <v>23</v>
       </c>
       <c r="F16" s="188" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="G16" s="188" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H16" s="188" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="I16" s="189">
         <v>19619</v>
@@ -10836,14 +10504,12 @@
         <v>18600</v>
       </c>
       <c r="Q16" s="189" t="s">
-        <v>338</v>
-      </c>
-      <c r="R16" s="189" t="s">
-        <v>22</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="R16" s="189"/>
       <c r="S16" s="189"/>
-      <c r="T16" s="216" t="s">
-        <v>325</v>
+      <c r="T16" s="226" t="s">
+        <v>320</v>
       </c>
       <c r="U16" s="192"/>
       <c r="V16" s="193"/>
@@ -10890,7 +10556,7 @@
       <c r="A17" s="185"/>
       <c r="B17" s="186"/>
       <c r="C17" s="187" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D17" s="188" t="s">
         <v>123</v>
@@ -10899,13 +10565,13 @@
         <v>23</v>
       </c>
       <c r="F17" s="188" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="G17" s="188" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H17" s="188" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="I17" s="189">
         <v>23996</v>
@@ -10933,12 +10599,12 @@
         <v>18400</v>
       </c>
       <c r="Q17" s="208" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="R17" s="189"/>
       <c r="S17" s="189"/>
-      <c r="T17" s="217" t="s">
-        <v>325</v>
+      <c r="T17" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="U17" s="192"/>
       <c r="V17" s="193"/>
@@ -10985,7 +10651,7 @@
       <c r="A18" s="185"/>
       <c r="B18" s="186"/>
       <c r="C18" s="187" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D18" s="188" t="s">
         <v>123</v>
@@ -10994,13 +10660,13 @@
         <v>23</v>
       </c>
       <c r="F18" s="188" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="G18" s="188" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H18" s="188" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="I18" s="189">
         <v>18801</v>
@@ -11028,12 +10694,12 @@
         <v>18300</v>
       </c>
       <c r="Q18" s="189" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="R18" s="189"/>
       <c r="S18" s="189"/>
-      <c r="T18" s="220" t="s">
-        <v>325</v>
+      <c r="T18" s="219" t="s">
+        <v>320</v>
       </c>
       <c r="U18" s="192"/>
       <c r="V18" s="193"/>
@@ -11080,7 +10746,7 @@
       <c r="A19" s="185"/>
       <c r="B19" s="186"/>
       <c r="C19" s="187" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D19" s="188" t="s">
         <v>123</v>
@@ -11089,13 +10755,13 @@
         <v>23</v>
       </c>
       <c r="F19" s="188" t="s">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="G19" s="188" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H19" s="188" t="s">
-        <v>406</v>
+        <v>382</v>
       </c>
       <c r="I19" s="189">
         <v>13517</v>
@@ -11123,12 +10789,12 @@
         <v>18800</v>
       </c>
       <c r="Q19" s="189" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="R19" s="189"/>
       <c r="S19" s="189"/>
-      <c r="T19" s="220" t="s">
-        <v>325</v>
+      <c r="T19" s="219" t="s">
+        <v>320</v>
       </c>
       <c r="U19" s="192"/>
       <c r="V19" s="193"/>
@@ -11175,7 +10841,7 @@
       <c r="A20" s="185"/>
       <c r="B20" s="186"/>
       <c r="C20" s="187" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D20" s="188" t="s">
         <v>123</v>
@@ -11184,13 +10850,13 @@
         <v>23</v>
       </c>
       <c r="F20" s="188" t="s">
-        <v>407</v>
+        <v>383</v>
       </c>
       <c r="G20" s="188" t="s">
         <v>30</v>
       </c>
       <c r="H20" s="188" t="s">
-        <v>408</v>
+        <v>384</v>
       </c>
       <c r="I20" s="189">
         <v>16591</v>
@@ -11218,12 +10884,12 @@
         <v>18300</v>
       </c>
       <c r="Q20" s="189" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="R20" s="189"/>
       <c r="S20" s="189"/>
-      <c r="T20" s="220" t="s">
-        <v>325</v>
+      <c r="T20" s="226" t="s">
+        <v>320</v>
       </c>
       <c r="U20" s="192"/>
       <c r="V20" s="193"/>
@@ -11286,7 +10952,7 @@
       <c r="Q21" s="189"/>
       <c r="R21" s="189"/>
       <c r="S21" s="189"/>
-      <c r="T21" s="217"/>
+      <c r="T21" s="216"/>
       <c r="U21" s="192"/>
       <c r="V21" s="193"/>
       <c r="W21" s="193"/>
@@ -11332,7 +10998,7 @@
       <c r="A22" s="185"/>
       <c r="B22" s="186"/>
       <c r="C22" s="187" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D22" s="188" t="s">
         <v>123</v>
@@ -11341,13 +11007,13 @@
         <v>23</v>
       </c>
       <c r="F22" s="188" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G22" s="188" t="s">
         <v>30</v>
       </c>
       <c r="H22" s="188" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I22" s="189">
         <v>14033</v>
@@ -11375,14 +11041,14 @@
         <v>20200</v>
       </c>
       <c r="Q22" s="189" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="R22" s="189" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="S22" s="189"/>
-      <c r="T22" s="217" t="s">
-        <v>325</v>
+      <c r="T22" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="U22" s="192"/>
       <c r="V22" s="193"/>
@@ -11445,7 +11111,7 @@
       <c r="Q23" s="189"/>
       <c r="R23" s="189"/>
       <c r="S23" s="189"/>
-      <c r="T23" s="217"/>
+      <c r="T23" s="216"/>
       <c r="U23" s="192"/>
       <c r="V23" s="193"/>
       <c r="W23" s="193"/>
@@ -11491,7 +11157,7 @@
       <c r="A24" s="185"/>
       <c r="B24" s="186"/>
       <c r="C24" s="187" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="D24" s="188" t="s">
         <v>123</v>
@@ -11500,13 +11166,13 @@
         <v>23</v>
       </c>
       <c r="F24" s="188" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="G24" s="188" t="s">
-        <v>345</v>
+        <v>184</v>
       </c>
       <c r="H24" s="188" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="I24" s="189">
         <v>16925</v>
@@ -11534,14 +11200,12 @@
         <v>19500</v>
       </c>
       <c r="Q24" s="189" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="R24" s="189"/>
-      <c r="S24" s="189" t="s">
-        <v>397</v>
-      </c>
-      <c r="T24" s="217" t="s">
-        <v>325</v>
+      <c r="S24" s="189"/>
+      <c r="T24" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="U24" s="192"/>
       <c r="V24" s="193"/>
@@ -11587,58 +11251,56 @@
     <row r="25" spans="1:60" s="194" customFormat="1" ht="19.5" customHeight="1">
       <c r="A25" s="185"/>
       <c r="B25" s="186"/>
-      <c r="C25" s="203" t="s">
-        <v>343</v>
-      </c>
-      <c r="D25" s="204" t="s">
+      <c r="C25" s="187" t="s">
+        <v>338</v>
+      </c>
+      <c r="D25" s="188" t="s">
         <v>123</v>
       </c>
-      <c r="E25" s="204" t="s">
+      <c r="E25" s="188" t="s">
         <v>23</v>
       </c>
-      <c r="F25" s="204" t="s">
-        <v>347</v>
-      </c>
-      <c r="G25" s="204" t="s">
-        <v>345</v>
-      </c>
-      <c r="H25" s="204" t="s">
-        <v>348</v>
-      </c>
-      <c r="I25" s="205">
-        <v>17818</v>
-      </c>
-      <c r="J25" s="206">
-        <v>45812</v>
-      </c>
-      <c r="K25" s="206">
-        <v>46198</v>
-      </c>
-      <c r="L25" s="205">
-        <v>17100</v>
-      </c>
-      <c r="M25" s="205">
-        <v>881</v>
-      </c>
-      <c r="N25" s="205">
+      <c r="F25" s="188" t="s">
+        <v>399</v>
+      </c>
+      <c r="G25" s="188" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25" s="188" t="s">
+        <v>400</v>
+      </c>
+      <c r="I25" s="189">
+        <v>11444</v>
+      </c>
+      <c r="J25" s="190">
+        <v>45835</v>
+      </c>
+      <c r="K25" s="190">
+        <v>46231</v>
+      </c>
+      <c r="L25" s="189">
+        <v>18297</v>
+      </c>
+      <c r="M25" s="189">
+        <v>218</v>
+      </c>
+      <c r="N25" s="189">
         <v>200</v>
       </c>
-      <c r="O25" s="205">
+      <c r="O25" s="189">
         <f>P25-L25-M25-N25</f>
-        <v>1319</v>
-      </c>
-      <c r="P25" s="207">
+        <v>785</v>
+      </c>
+      <c r="P25" s="191">
         <v>19500</v>
       </c>
-      <c r="Q25" s="227" t="s">
-        <v>326</v>
-      </c>
-      <c r="R25" s="205"/>
-      <c r="S25" s="205" t="s">
-        <v>326</v>
-      </c>
-      <c r="T25" s="218" t="s">
-        <v>325</v>
+      <c r="Q25" s="189" t="s">
+        <v>337</v>
+      </c>
+      <c r="R25" s="189"/>
+      <c r="S25" s="189"/>
+      <c r="T25" s="226" t="s">
+        <v>320</v>
       </c>
       <c r="U25" s="192"/>
       <c r="V25" s="193"/>
@@ -11701,7 +11363,7 @@
       <c r="Q26" s="189"/>
       <c r="R26" s="189"/>
       <c r="S26" s="189"/>
-      <c r="T26" s="217"/>
+      <c r="T26" s="216"/>
       <c r="U26" s="192"/>
       <c r="V26" s="193"/>
       <c r="W26" s="193"/>
@@ -11747,7 +11409,7 @@
       <c r="A27" s="185"/>
       <c r="B27" s="186"/>
       <c r="C27" s="187" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="D27" s="188" t="s">
         <v>123</v>
@@ -11756,13 +11418,13 @@
         <v>23</v>
       </c>
       <c r="F27" s="188" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="G27" s="188" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H27" s="188" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="I27" s="189">
         <v>14102</v>
@@ -11790,12 +11452,12 @@
         <v>20800</v>
       </c>
       <c r="Q27" s="208" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="R27" s="189"/>
       <c r="S27" s="189"/>
-      <c r="T27" s="220" t="s">
-        <v>325</v>
+      <c r="T27" s="219" t="s">
+        <v>320</v>
       </c>
       <c r="U27" s="192"/>
       <c r="V27" s="193"/>
@@ -11858,7 +11520,7 @@
       <c r="Q28" s="189"/>
       <c r="R28" s="189"/>
       <c r="S28" s="189"/>
-      <c r="T28" s="217"/>
+      <c r="T28" s="216"/>
       <c r="U28" s="192"/>
       <c r="V28" s="193"/>
       <c r="W28" s="193"/>
@@ -11903,54 +11565,54 @@
     <row r="29" spans="1:60" s="194" customFormat="1" ht="19.5" customHeight="1">
       <c r="A29" s="185"/>
       <c r="B29" s="186"/>
-      <c r="C29" s="187" t="s">
-        <v>400</v>
-      </c>
-      <c r="D29" s="188" t="s">
+      <c r="C29" s="203" t="s">
+        <v>377</v>
+      </c>
+      <c r="D29" s="204" t="s">
         <v>127</v>
       </c>
-      <c r="E29" s="188"/>
-      <c r="F29" s="188" t="s">
-        <v>401</v>
-      </c>
-      <c r="G29" s="188" t="s">
+      <c r="E29" s="204"/>
+      <c r="F29" s="204" t="s">
+        <v>378</v>
+      </c>
+      <c r="G29" s="204" t="s">
         <v>24</v>
       </c>
-      <c r="H29" s="188" t="s">
-        <v>402</v>
-      </c>
-      <c r="I29" s="189">
+      <c r="H29" s="204" t="s">
+        <v>379</v>
+      </c>
+      <c r="I29" s="205">
         <v>101464</v>
       </c>
-      <c r="J29" s="190">
+      <c r="J29" s="206">
         <v>43615</v>
       </c>
-      <c r="K29" s="190">
+      <c r="K29" s="206">
         <v>46204</v>
       </c>
-      <c r="L29" s="189">
+      <c r="L29" s="205">
         <v>10500</v>
       </c>
-      <c r="M29" s="189">
+      <c r="M29" s="205">
         <v>1000</v>
       </c>
-      <c r="N29" s="189">
+      <c r="N29" s="205">
         <v>200</v>
       </c>
-      <c r="O29" s="189">
+      <c r="O29" s="205">
         <f>P29-L29-M29-N29</f>
         <v>2100</v>
       </c>
-      <c r="P29" s="191">
+      <c r="P29" s="207">
         <v>13800</v>
       </c>
-      <c r="Q29" s="189" t="s">
-        <v>338</v>
-      </c>
-      <c r="R29" s="189"/>
-      <c r="S29" s="189"/>
-      <c r="T29" s="228" t="s">
-        <v>325</v>
+      <c r="Q29" s="205" t="s">
+        <v>333</v>
+      </c>
+      <c r="R29" s="205"/>
+      <c r="S29" s="205"/>
+      <c r="T29" s="248" t="s">
+        <v>320</v>
       </c>
       <c r="U29" s="192"/>
       <c r="V29" s="193"/>
@@ -12013,7 +11675,7 @@
       <c r="Q30" s="189"/>
       <c r="R30" s="189"/>
       <c r="S30" s="189"/>
-      <c r="T30" s="217"/>
+      <c r="T30" s="216"/>
       <c r="U30" s="192"/>
       <c r="V30" s="193"/>
       <c r="W30" s="193"/>
@@ -12058,58 +11720,58 @@
     <row r="31" spans="1:60" s="194" customFormat="1" ht="19.5" customHeight="1">
       <c r="A31" s="185"/>
       <c r="B31" s="186"/>
-      <c r="C31" s="203" t="s">
-        <v>409</v>
-      </c>
-      <c r="D31" s="204" t="s">
-        <v>127</v>
-      </c>
-      <c r="E31" s="204" t="s">
-        <v>393</v>
-      </c>
-      <c r="F31" s="204" t="s">
-        <v>394</v>
-      </c>
-      <c r="G31" s="204" t="s">
-        <v>24</v>
-      </c>
-      <c r="H31" s="204" t="s">
-        <v>395</v>
-      </c>
-      <c r="I31" s="205">
-        <v>37626</v>
-      </c>
-      <c r="J31" s="206">
-        <v>45070</v>
-      </c>
-      <c r="K31" s="206">
-        <v>46204</v>
-      </c>
-      <c r="L31" s="205">
-        <v>18500</v>
-      </c>
-      <c r="M31" s="205">
-        <v>0</v>
-      </c>
-      <c r="N31" s="205">
+      <c r="C31" s="187" t="s">
+        <v>255</v>
+      </c>
+      <c r="D31" s="188" t="s">
+        <v>123</v>
+      </c>
+      <c r="E31" s="188" t="s">
+        <v>23</v>
+      </c>
+      <c r="F31" s="188" t="s">
+        <v>248</v>
+      </c>
+      <c r="G31" s="188" t="s">
+        <v>56</v>
+      </c>
+      <c r="H31" s="188" t="s">
+        <v>249</v>
+      </c>
+      <c r="I31" s="189">
+        <v>27790</v>
+      </c>
+      <c r="J31" s="190">
+        <v>45855</v>
+      </c>
+      <c r="K31" s="190">
+        <v>46129</v>
+      </c>
+      <c r="L31" s="189">
+        <v>19190</v>
+      </c>
+      <c r="M31" s="189">
+        <v>535</v>
+      </c>
+      <c r="N31" s="189">
         <v>200</v>
       </c>
-      <c r="O31" s="205">
+      <c r="O31" s="189">
         <f>P31-L31-M31-N31</f>
-        <v>2100</v>
-      </c>
-      <c r="P31" s="207">
-        <v>20800</v>
-      </c>
-      <c r="Q31" s="205" t="s">
-        <v>35</v>
-      </c>
-      <c r="R31" s="205"/>
-      <c r="S31" s="205" t="s">
-        <v>411</v>
-      </c>
-      <c r="T31" s="218" t="s">
-        <v>325</v>
+        <v>2675</v>
+      </c>
+      <c r="P31" s="191">
+        <v>22600</v>
+      </c>
+      <c r="Q31" s="189" t="s">
+        <v>333</v>
+      </c>
+      <c r="R31" s="189" t="s">
+        <v>22</v>
+      </c>
+      <c r="S31" s="189"/>
+      <c r="T31" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="U31" s="192"/>
       <c r="V31" s="193"/>
@@ -12152,7 +11814,7 @@
       <c r="BG31" s="193"/>
       <c r="BH31" s="193"/>
     </row>
-    <row r="32" spans="1:60" s="194" customFormat="1" ht="5.4" customHeight="1">
+    <row r="32" spans="1:60" s="194" customFormat="1" ht="4.5" customHeight="1">
       <c r="A32" s="185"/>
       <c r="B32" s="186"/>
       <c r="C32" s="187"/>
@@ -12172,7 +11834,7 @@
       <c r="Q32" s="189"/>
       <c r="R32" s="189"/>
       <c r="S32" s="189"/>
-      <c r="T32" s="217"/>
+      <c r="T32" s="216"/>
       <c r="U32" s="192"/>
       <c r="V32" s="193"/>
       <c r="W32" s="193"/>
@@ -12218,57 +11880,55 @@
       <c r="A33" s="185"/>
       <c r="B33" s="186"/>
       <c r="C33" s="187" t="s">
-        <v>260</v>
+        <v>132</v>
       </c>
       <c r="D33" s="188" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E33" s="188" t="s">
         <v>23</v>
       </c>
       <c r="F33" s="188" t="s">
-        <v>253</v>
+        <v>286</v>
       </c>
       <c r="G33" s="188" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="H33" s="188" t="s">
-        <v>254</v>
+        <v>287</v>
       </c>
       <c r="I33" s="189">
-        <v>27790</v>
+        <v>21890</v>
       </c>
       <c r="J33" s="190">
-        <v>45855</v>
+        <v>45719</v>
       </c>
       <c r="K33" s="190">
-        <v>46129</v>
+        <v>46155</v>
       </c>
       <c r="L33" s="189">
-        <v>19190</v>
+        <v>23300</v>
       </c>
       <c r="M33" s="189">
-        <v>535</v>
+        <v>0</v>
       </c>
       <c r="N33" s="189">
         <v>200</v>
       </c>
       <c r="O33" s="189">
         <f>P33-L33-M33-N33</f>
-        <v>2675</v>
+        <v>-200</v>
       </c>
       <c r="P33" s="191">
-        <v>22600</v>
-      </c>
-      <c r="Q33" s="189" t="s">
-        <v>338</v>
-      </c>
-      <c r="R33" s="189" t="s">
-        <v>22</v>
-      </c>
+        <v>23300</v>
+      </c>
+      <c r="Q33" s="208" t="s">
+        <v>334</v>
+      </c>
+      <c r="R33" s="189"/>
       <c r="S33" s="189"/>
-      <c r="T33" s="217" t="s">
-        <v>325</v>
+      <c r="T33" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="U33" s="192"/>
       <c r="V33" s="193"/>
@@ -12311,27 +11971,60 @@
       <c r="BG33" s="193"/>
       <c r="BH33" s="193"/>
     </row>
-    <row r="34" spans="1:60" s="194" customFormat="1" ht="4.5" customHeight="1">
+    <row r="34" spans="1:60" s="194" customFormat="1" ht="19.5" customHeight="1">
       <c r="A34" s="185"/>
       <c r="B34" s="186"/>
-      <c r="C34" s="187"/>
-      <c r="D34" s="188"/>
-      <c r="E34" s="188"/>
-      <c r="F34" s="188"/>
-      <c r="G34" s="188"/>
-      <c r="H34" s="188"/>
-      <c r="I34" s="189"/>
-      <c r="J34" s="190"/>
-      <c r="K34" s="190"/>
-      <c r="L34" s="189"/>
-      <c r="M34" s="189"/>
-      <c r="N34" s="189"/>
-      <c r="O34" s="189"/>
-      <c r="P34" s="191"/>
-      <c r="Q34" s="189"/>
+      <c r="C34" s="187" t="s">
+        <v>132</v>
+      </c>
+      <c r="D34" s="188" t="s">
+        <v>123</v>
+      </c>
+      <c r="E34" s="188" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34" s="188" t="s">
+        <v>133</v>
+      </c>
+      <c r="G34" s="188" t="s">
+        <v>28</v>
+      </c>
+      <c r="H34" s="188" t="s">
+        <v>134</v>
+      </c>
+      <c r="I34" s="189">
+        <v>14459</v>
+      </c>
+      <c r="J34" s="190">
+        <v>45744</v>
+      </c>
+      <c r="K34" s="190">
+        <v>46094</v>
+      </c>
+      <c r="L34" s="189">
+        <v>20422</v>
+      </c>
+      <c r="M34" s="189">
+        <v>841</v>
+      </c>
+      <c r="N34" s="189">
+        <v>200</v>
+      </c>
+      <c r="O34" s="189">
+        <f>P34-L34-M34-N34</f>
+        <v>1437</v>
+      </c>
+      <c r="P34" s="191">
+        <v>22900</v>
+      </c>
+      <c r="Q34" s="208" t="s">
+        <v>268</v>
+      </c>
       <c r="R34" s="189"/>
       <c r="S34" s="189"/>
-      <c r="T34" s="217"/>
+      <c r="T34" s="216" t="s">
+        <v>320</v>
+      </c>
       <c r="U34" s="192"/>
       <c r="V34" s="193"/>
       <c r="W34" s="193"/>
@@ -12376,56 +12069,60 @@
     <row r="35" spans="1:60" s="194" customFormat="1" ht="19.5" customHeight="1">
       <c r="A35" s="185"/>
       <c r="B35" s="186"/>
-      <c r="C35" s="187" t="s">
-        <v>134</v>
-      </c>
-      <c r="D35" s="188" t="s">
-        <v>127</v>
-      </c>
-      <c r="E35" s="188" t="s">
+      <c r="C35" s="203" t="s">
+        <v>132</v>
+      </c>
+      <c r="D35" s="204" t="s">
+        <v>123</v>
+      </c>
+      <c r="E35" s="204" t="s">
         <v>23</v>
       </c>
-      <c r="F35" s="188" t="s">
-        <v>291</v>
-      </c>
-      <c r="G35" s="188" t="s">
-        <v>24</v>
-      </c>
-      <c r="H35" s="188" t="s">
-        <v>292</v>
-      </c>
-      <c r="I35" s="189">
-        <v>21890</v>
-      </c>
-      <c r="J35" s="190">
-        <v>45719</v>
-      </c>
-      <c r="K35" s="190">
-        <v>46155</v>
-      </c>
-      <c r="L35" s="189">
+      <c r="F35" s="204" t="s">
+        <v>135</v>
+      </c>
+      <c r="G35" s="204" t="s">
+        <v>29</v>
+      </c>
+      <c r="H35" s="204" t="s">
+        <v>136</v>
+      </c>
+      <c r="I35" s="205">
+        <v>14388</v>
+      </c>
+      <c r="J35" s="206">
+        <v>45744</v>
+      </c>
+      <c r="K35" s="206">
+        <v>46094</v>
+      </c>
+      <c r="L35" s="205">
+        <v>21227</v>
+      </c>
+      <c r="M35" s="205">
+        <v>497</v>
+      </c>
+      <c r="N35" s="205">
+        <v>200</v>
+      </c>
+      <c r="O35" s="205">
+        <f>P35-L35-M35-N35</f>
+        <v>1376</v>
+      </c>
+      <c r="P35" s="207">
         <v>23300</v>
       </c>
-      <c r="M35" s="189">
-        <v>0</v>
-      </c>
-      <c r="N35" s="189">
-        <v>200</v>
-      </c>
-      <c r="O35" s="189">
-        <f>P35-L35-M35-N35</f>
-        <v>-200</v>
-      </c>
-      <c r="P35" s="191">
-        <v>23300</v>
-      </c>
-      <c r="Q35" s="208" t="s">
-        <v>339</v>
-      </c>
-      <c r="R35" s="189"/>
-      <c r="S35" s="189"/>
-      <c r="T35" s="217" t="s">
-        <v>325</v>
+      <c r="Q35" s="205" t="s">
+        <v>333</v>
+      </c>
+      <c r="R35" s="205" t="s">
+        <v>22</v>
+      </c>
+      <c r="S35" s="205" t="s">
+        <v>397</v>
+      </c>
+      <c r="T35" s="243" t="s">
+        <v>320</v>
       </c>
       <c r="U35" s="192"/>
       <c r="V35" s="193"/>
@@ -12468,60 +12165,27 @@
       <c r="BG35" s="193"/>
       <c r="BH35" s="193"/>
     </row>
-    <row r="36" spans="1:60" s="194" customFormat="1" ht="19.5" customHeight="1">
+    <row r="36" spans="1:60" s="194" customFormat="1" ht="15" customHeight="1">
       <c r="A36" s="185"/>
       <c r="B36" s="186"/>
-      <c r="C36" s="187" t="s">
-        <v>134</v>
-      </c>
-      <c r="D36" s="188" t="s">
-        <v>123</v>
-      </c>
-      <c r="E36" s="188" t="s">
-        <v>23</v>
-      </c>
-      <c r="F36" s="188" t="s">
-        <v>135</v>
-      </c>
-      <c r="G36" s="188" t="s">
-        <v>28</v>
-      </c>
-      <c r="H36" s="188" t="s">
-        <v>136</v>
-      </c>
-      <c r="I36" s="189">
-        <v>14459</v>
-      </c>
-      <c r="J36" s="190">
-        <v>45744</v>
-      </c>
-      <c r="K36" s="190">
-        <v>46094</v>
-      </c>
-      <c r="L36" s="189">
-        <v>20422</v>
-      </c>
-      <c r="M36" s="189">
-        <v>841</v>
-      </c>
-      <c r="N36" s="189">
-        <v>200</v>
-      </c>
-      <c r="O36" s="189">
-        <f>P36-L36-M36-N36</f>
-        <v>1437</v>
-      </c>
-      <c r="P36" s="191">
-        <v>22900</v>
-      </c>
-      <c r="Q36" s="208" t="s">
-        <v>273</v>
-      </c>
+      <c r="C36" s="187"/>
+      <c r="D36" s="188"/>
+      <c r="E36" s="188"/>
+      <c r="F36" s="188"/>
+      <c r="G36" s="188"/>
+      <c r="H36" s="188"/>
+      <c r="I36" s="189"/>
+      <c r="J36" s="190"/>
+      <c r="K36" s="190"/>
+      <c r="L36" s="189"/>
+      <c r="M36" s="189"/>
+      <c r="N36" s="189"/>
+      <c r="O36" s="189"/>
+      <c r="P36" s="191"/>
+      <c r="Q36" s="208"/>
       <c r="R36" s="189"/>
       <c r="S36" s="189"/>
-      <c r="T36" s="217" t="s">
-        <v>325</v>
-      </c>
+      <c r="T36" s="216"/>
       <c r="U36" s="192"/>
       <c r="V36" s="193"/>
       <c r="W36" s="193"/>
@@ -12567,7 +12231,7 @@
       <c r="A37" s="185"/>
       <c r="B37" s="186"/>
       <c r="C37" s="187" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D37" s="188" t="s">
         <v>123</v>
@@ -12576,48 +12240,46 @@
         <v>23</v>
       </c>
       <c r="F37" s="188" t="s">
-        <v>137</v>
+        <v>256</v>
       </c>
       <c r="G37" s="188" t="s">
         <v>29</v>
       </c>
       <c r="H37" s="188" t="s">
-        <v>138</v>
-      </c>
-      <c r="I37" s="189">
-        <v>14388</v>
+        <v>257</v>
+      </c>
+      <c r="I37" s="209">
+        <v>12432</v>
       </c>
       <c r="J37" s="190">
-        <v>45744</v>
+        <v>45789</v>
       </c>
       <c r="K37" s="190">
-        <v>46094</v>
+        <v>46136</v>
       </c>
       <c r="L37" s="189">
-        <v>21227</v>
+        <v>22224</v>
       </c>
       <c r="M37" s="189">
-        <v>497</v>
+        <v>246</v>
       </c>
       <c r="N37" s="189">
         <v>200</v>
       </c>
       <c r="O37" s="189">
         <f>P37-L37-M37-N37</f>
-        <v>1376</v>
+        <v>1230</v>
       </c>
       <c r="P37" s="191">
-        <v>23300</v>
+        <v>23900</v>
       </c>
       <c r="Q37" s="189" t="s">
-        <v>338</v>
-      </c>
-      <c r="R37" s="189" t="s">
-        <v>22</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="R37" s="189"/>
       <c r="S37" s="189"/>
       <c r="T37" s="216" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="U37" s="192"/>
       <c r="V37" s="193"/>
@@ -12680,7 +12342,7 @@
       <c r="Q38" s="208"/>
       <c r="R38" s="189"/>
       <c r="S38" s="189"/>
-      <c r="T38" s="217"/>
+      <c r="T38" s="218"/>
       <c r="U38" s="192"/>
       <c r="V38" s="193"/>
       <c r="W38" s="193"/>
@@ -12726,55 +12388,57 @@
       <c r="A39" s="185"/>
       <c r="B39" s="186"/>
       <c r="C39" s="187" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D39" s="188" t="s">
         <v>123</v>
       </c>
       <c r="E39" s="188" t="s">
-        <v>23</v>
+        <v>141</v>
       </c>
       <c r="F39" s="188" t="s">
-        <v>261</v>
+        <v>142</v>
       </c>
       <c r="G39" s="188" t="s">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="H39" s="188" t="s">
-        <v>262</v>
-      </c>
-      <c r="I39" s="209">
-        <v>12432</v>
+        <v>144</v>
+      </c>
+      <c r="I39" s="189">
+        <v>22478</v>
       </c>
       <c r="J39" s="190">
-        <v>45789</v>
-      </c>
-      <c r="K39" s="190">
-        <v>46136</v>
+        <v>45721</v>
+      </c>
+      <c r="K39" s="223">
+        <v>45982</v>
       </c>
       <c r="L39" s="189">
-        <v>22224</v>
+        <v>27917</v>
       </c>
       <c r="M39" s="189">
-        <v>246</v>
+        <v>832</v>
       </c>
       <c r="N39" s="189">
         <v>200</v>
       </c>
       <c r="O39" s="189">
         <f>P39-L39-M39-N39</f>
-        <v>1230</v>
+        <v>-1049</v>
       </c>
       <c r="P39" s="191">
-        <v>23900</v>
+        <v>27900</v>
       </c>
       <c r="Q39" s="189" t="s">
-        <v>338</v>
-      </c>
-      <c r="R39" s="189"/>
+        <v>35</v>
+      </c>
+      <c r="R39" s="189" t="s">
+        <v>322</v>
+      </c>
       <c r="S39" s="189"/>
-      <c r="T39" s="217" t="s">
-        <v>325</v>
+      <c r="T39" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="U39" s="192"/>
       <c r="V39" s="193"/>
@@ -12817,85 +12481,122 @@
       <c r="BG39" s="193"/>
       <c r="BH39" s="193"/>
     </row>
-    <row r="40" spans="1:60" s="194" customFormat="1" ht="15" customHeight="1">
-      <c r="A40" s="239"/>
+    <row r="40" spans="1:60" s="194" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A40" s="185"/>
       <c r="B40" s="186"/>
-      <c r="C40" s="187"/>
-      <c r="D40" s="188"/>
-      <c r="E40" s="188"/>
-      <c r="F40" s="188"/>
-      <c r="G40" s="188"/>
-      <c r="H40" s="188"/>
-      <c r="I40" s="189"/>
-      <c r="J40" s="190"/>
-      <c r="K40" s="190"/>
-      <c r="L40" s="189"/>
-      <c r="M40" s="189"/>
-      <c r="N40" s="189"/>
-      <c r="O40" s="189"/>
-      <c r="P40" s="191"/>
-      <c r="Q40" s="208"/>
+      <c r="C40" s="187" t="s">
+        <v>140</v>
+      </c>
+      <c r="D40" s="188" t="s">
+        <v>123</v>
+      </c>
+      <c r="E40" s="188" t="s">
+        <v>279</v>
+      </c>
+      <c r="F40" s="188" t="s">
+        <v>280</v>
+      </c>
+      <c r="G40" s="188" t="s">
+        <v>29</v>
+      </c>
+      <c r="H40" s="188" t="s">
+        <v>281</v>
+      </c>
+      <c r="I40" s="189">
+        <v>18550</v>
+      </c>
+      <c r="J40" s="190">
+        <v>45688</v>
+      </c>
+      <c r="K40" s="190">
+        <v>46141</v>
+      </c>
+      <c r="L40" s="189">
+        <v>28943</v>
+      </c>
+      <c r="M40" s="189">
+        <v>0</v>
+      </c>
+      <c r="N40" s="189">
+        <v>200</v>
+      </c>
+      <c r="O40" s="189">
+        <f>P40-L40-M40-N40</f>
+        <v>1357</v>
+      </c>
+      <c r="P40" s="191">
+        <v>30500</v>
+      </c>
+      <c r="Q40" s="189" t="s">
+        <v>333</v>
+      </c>
       <c r="R40" s="189"/>
       <c r="S40" s="189"/>
-      <c r="T40" s="217"/>
+      <c r="T40" s="216" t="s">
+        <v>320</v>
+      </c>
       <c r="U40" s="192"/>
-    </row>
-    <row r="41" spans="1:60" s="194" customFormat="1" ht="19.5" customHeight="1">
+      <c r="V40" s="193"/>
+      <c r="W40" s="193"/>
+      <c r="X40" s="193"/>
+      <c r="Y40" s="193"/>
+      <c r="Z40" s="193"/>
+      <c r="AA40" s="193"/>
+      <c r="AB40" s="193"/>
+      <c r="AC40" s="193"/>
+      <c r="AD40" s="193"/>
+      <c r="AE40" s="193"/>
+      <c r="AF40" s="193"/>
+      <c r="AG40" s="193"/>
+      <c r="AH40" s="193"/>
+      <c r="AI40" s="193"/>
+      <c r="AJ40" s="193"/>
+      <c r="AK40" s="193"/>
+      <c r="AL40" s="193"/>
+      <c r="AM40" s="193"/>
+      <c r="AN40" s="193"/>
+      <c r="AO40" s="193"/>
+      <c r="AP40" s="193"/>
+      <c r="AQ40" s="193"/>
+      <c r="AR40" s="193"/>
+      <c r="AS40" s="193"/>
+      <c r="AT40" s="193"/>
+      <c r="AU40" s="193"/>
+      <c r="AV40" s="193"/>
+      <c r="AW40" s="193"/>
+      <c r="AX40" s="193"/>
+      <c r="AY40" s="193"/>
+      <c r="AZ40" s="193"/>
+      <c r="BA40" s="193"/>
+      <c r="BB40" s="193"/>
+      <c r="BC40" s="193"/>
+      <c r="BD40" s="193"/>
+      <c r="BE40" s="193"/>
+      <c r="BF40" s="193"/>
+      <c r="BG40" s="193"/>
+      <c r="BH40" s="193"/>
+    </row>
+    <row r="41" spans="1:60" s="194" customFormat="1" ht="15" customHeight="1">
       <c r="A41" s="185"/>
       <c r="B41" s="186"/>
-      <c r="C41" s="203" t="s">
-        <v>107</v>
-      </c>
-      <c r="D41" s="204" t="s">
-        <v>123</v>
-      </c>
-      <c r="E41" s="204" t="s">
-        <v>349</v>
-      </c>
-      <c r="F41" s="204" t="s">
-        <v>350</v>
-      </c>
-      <c r="G41" s="204" t="s">
-        <v>351</v>
-      </c>
-      <c r="H41" s="204" t="s">
-        <v>352</v>
-      </c>
-      <c r="I41" s="205">
-        <v>16837</v>
-      </c>
-      <c r="J41" s="206">
-        <v>45415</v>
-      </c>
-      <c r="K41" s="206">
-        <v>46202</v>
-      </c>
-      <c r="L41" s="205">
-        <v>27150</v>
-      </c>
-      <c r="M41" s="205">
-        <v>0</v>
-      </c>
-      <c r="N41" s="205">
-        <v>200</v>
-      </c>
-      <c r="O41" s="205">
-        <f>P41-L41-M41-N41</f>
-        <v>5150</v>
-      </c>
-      <c r="P41" s="207">
-        <v>32500</v>
-      </c>
-      <c r="Q41" s="205" t="s">
-        <v>35</v>
-      </c>
-      <c r="R41" s="205"/>
-      <c r="S41" s="205" t="s">
-        <v>412</v>
-      </c>
-      <c r="T41" s="218" t="s">
-        <v>325</v>
-      </c>
+      <c r="C41" s="187"/>
+      <c r="D41" s="188"/>
+      <c r="E41" s="188"/>
+      <c r="F41" s="188"/>
+      <c r="G41" s="188"/>
+      <c r="H41" s="188"/>
+      <c r="I41" s="189"/>
+      <c r="J41" s="190"/>
+      <c r="K41" s="190"/>
+      <c r="L41" s="189"/>
+      <c r="M41" s="189"/>
+      <c r="N41" s="189"/>
+      <c r="O41" s="189"/>
+      <c r="P41" s="191"/>
+      <c r="Q41" s="189"/>
+      <c r="R41" s="189"/>
+      <c r="S41" s="189"/>
+      <c r="T41" s="218"/>
       <c r="U41" s="192"/>
       <c r="V41" s="193"/>
       <c r="W41" s="193"/>
@@ -12937,27 +12638,58 @@
       <c r="BG41" s="193"/>
       <c r="BH41" s="193"/>
     </row>
-    <row r="42" spans="1:60" s="194" customFormat="1" ht="15" customHeight="1">
+    <row r="42" spans="1:60" s="210" customFormat="1" ht="19.5" customHeight="1">
       <c r="A42" s="185"/>
       <c r="B42" s="186"/>
-      <c r="C42" s="187"/>
-      <c r="D42" s="188"/>
+      <c r="C42" s="187" t="s">
+        <v>250</v>
+      </c>
+      <c r="D42" s="188" t="s">
+        <v>127</v>
+      </c>
       <c r="E42" s="188"/>
-      <c r="F42" s="188"/>
-      <c r="G42" s="188"/>
-      <c r="H42" s="188"/>
-      <c r="I42" s="189"/>
-      <c r="J42" s="190"/>
-      <c r="K42" s="190"/>
-      <c r="L42" s="189"/>
-      <c r="M42" s="189"/>
-      <c r="N42" s="189"/>
-      <c r="O42" s="189"/>
-      <c r="P42" s="191"/>
-      <c r="Q42" s="208"/>
+      <c r="F42" s="188" t="s">
+        <v>251</v>
+      </c>
+      <c r="G42" s="188" t="s">
+        <v>24</v>
+      </c>
+      <c r="H42" s="188" t="s">
+        <v>252</v>
+      </c>
+      <c r="I42" s="189">
+        <v>24519</v>
+      </c>
+      <c r="J42" s="190">
+        <v>45312</v>
+      </c>
+      <c r="K42" s="190">
+        <v>46132</v>
+      </c>
+      <c r="L42" s="189">
+        <v>25000</v>
+      </c>
+      <c r="M42" s="189">
+        <v>0</v>
+      </c>
+      <c r="N42" s="189">
+        <v>200</v>
+      </c>
+      <c r="O42" s="189">
+        <f>P42-L42-M42-N42</f>
+        <v>1700</v>
+      </c>
+      <c r="P42" s="191">
+        <v>26900</v>
+      </c>
+      <c r="Q42" s="189" t="s">
+        <v>35</v>
+      </c>
       <c r="R42" s="189"/>
       <c r="S42" s="189"/>
-      <c r="T42" s="219"/>
+      <c r="T42" s="216" t="s">
+        <v>320</v>
+      </c>
       <c r="U42" s="192"/>
       <c r="V42" s="193"/>
       <c r="W42" s="193"/>
@@ -12999,62 +12731,27 @@
       <c r="BG42" s="193"/>
       <c r="BH42" s="193"/>
     </row>
-    <row r="43" spans="1:60" s="194" customFormat="1" ht="19.5" customHeight="1">
+    <row r="43" spans="1:60" s="194" customFormat="1" ht="4.5" customHeight="1">
       <c r="A43" s="185"/>
       <c r="B43" s="186"/>
-      <c r="C43" s="187" t="s">
-        <v>142</v>
-      </c>
-      <c r="D43" s="188" t="s">
-        <v>123</v>
-      </c>
-      <c r="E43" s="188" t="s">
-        <v>143</v>
-      </c>
-      <c r="F43" s="188" t="s">
-        <v>144</v>
-      </c>
-      <c r="G43" s="188" t="s">
-        <v>145</v>
-      </c>
-      <c r="H43" s="188" t="s">
-        <v>146</v>
-      </c>
-      <c r="I43" s="189">
-        <v>22478</v>
-      </c>
-      <c r="J43" s="190">
-        <v>45721</v>
-      </c>
-      <c r="K43" s="224">
-        <v>45982</v>
-      </c>
-      <c r="L43" s="189">
-        <v>27917</v>
-      </c>
-      <c r="M43" s="189">
-        <v>832</v>
-      </c>
-      <c r="N43" s="189">
-        <v>200</v>
-      </c>
-      <c r="O43" s="189">
-        <f>P43-L43-M43-N43</f>
-        <v>-1049</v>
-      </c>
-      <c r="P43" s="191">
-        <v>27900</v>
-      </c>
-      <c r="Q43" s="189" t="s">
-        <v>35</v>
-      </c>
-      <c r="R43" s="189" t="s">
-        <v>327</v>
-      </c>
+      <c r="C43" s="187"/>
+      <c r="D43" s="188"/>
+      <c r="E43" s="188"/>
+      <c r="F43" s="188"/>
+      <c r="G43" s="188"/>
+      <c r="H43" s="188"/>
+      <c r="I43" s="189"/>
+      <c r="J43" s="190"/>
+      <c r="K43" s="190"/>
+      <c r="L43" s="189"/>
+      <c r="M43" s="189"/>
+      <c r="N43" s="189"/>
+      <c r="O43" s="189"/>
+      <c r="P43" s="191"/>
+      <c r="Q43" s="189"/>
+      <c r="R43" s="189"/>
       <c r="S43" s="189"/>
-      <c r="T43" s="217" t="s">
-        <v>325</v>
-      </c>
+      <c r="T43" s="216"/>
       <c r="U43" s="192"/>
       <c r="V43" s="193"/>
       <c r="W43" s="193"/>
@@ -13096,59 +12793,61 @@
       <c r="BG43" s="193"/>
       <c r="BH43" s="193"/>
     </row>
-    <row r="44" spans="1:60" s="194" customFormat="1" ht="19.5" customHeight="1">
+    <row r="44" spans="1:60" s="210" customFormat="1" ht="19.5" customHeight="1">
       <c r="A44" s="185"/>
       <c r="B44" s="186"/>
       <c r="C44" s="187" t="s">
-        <v>142</v>
+        <v>246</v>
       </c>
       <c r="D44" s="188" t="s">
         <v>123</v>
       </c>
       <c r="E44" s="188" t="s">
-        <v>284</v>
+        <v>247</v>
       </c>
       <c r="F44" s="188" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="G44" s="188" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H44" s="188" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="I44" s="189">
-        <v>18550</v>
+        <v>27900</v>
       </c>
       <c r="J44" s="190">
-        <v>45688</v>
+        <v>45849</v>
       </c>
       <c r="K44" s="190">
-        <v>46141</v>
+        <v>46169</v>
       </c>
       <c r="L44" s="189">
-        <v>28943</v>
+        <v>30557</v>
       </c>
       <c r="M44" s="189">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="N44" s="189">
         <v>200</v>
       </c>
       <c r="O44" s="189">
         <f>P44-L44-M44-N44</f>
-        <v>1357</v>
+        <v>1422</v>
       </c>
       <c r="P44" s="191">
-        <v>30500</v>
+        <v>32500</v>
       </c>
       <c r="Q44" s="189" t="s">
-        <v>338</v>
-      </c>
-      <c r="R44" s="189"/>
+        <v>35</v>
+      </c>
+      <c r="R44" s="189" t="s">
+        <v>22</v>
+      </c>
       <c r="S44" s="189"/>
-      <c r="T44" s="217" t="s">
-        <v>325</v>
+      <c r="T44" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="U44" s="192"/>
       <c r="V44" s="193"/>
@@ -13191,27 +12890,62 @@
       <c r="BG44" s="193"/>
       <c r="BH44" s="193"/>
     </row>
-    <row r="45" spans="1:60" s="194" customFormat="1" ht="15" customHeight="1">
+    <row r="45" spans="1:60" s="210" customFormat="1" ht="19.5" customHeight="1">
       <c r="A45" s="185"/>
       <c r="B45" s="186"/>
-      <c r="C45" s="187"/>
-      <c r="D45" s="188"/>
-      <c r="E45" s="188"/>
-      <c r="F45" s="188"/>
-      <c r="G45" s="188"/>
-      <c r="H45" s="188"/>
-      <c r="I45" s="189"/>
-      <c r="J45" s="190"/>
-      <c r="K45" s="190"/>
-      <c r="L45" s="189"/>
-      <c r="M45" s="189"/>
-      <c r="N45" s="189"/>
-      <c r="O45" s="189"/>
-      <c r="P45" s="191"/>
-      <c r="Q45" s="189"/>
-      <c r="R45" s="189"/>
+      <c r="C45" s="187" t="s">
+        <v>246</v>
+      </c>
+      <c r="D45" s="188" t="s">
+        <v>123</v>
+      </c>
+      <c r="E45" s="188" t="s">
+        <v>324</v>
+      </c>
+      <c r="F45" s="188" t="s">
+        <v>325</v>
+      </c>
+      <c r="G45" s="188" t="s">
+        <v>326</v>
+      </c>
+      <c r="H45" s="188" t="s">
+        <v>327</v>
+      </c>
+      <c r="I45" s="189">
+        <v>9253</v>
+      </c>
+      <c r="J45" s="190">
+        <v>45992</v>
+      </c>
+      <c r="K45" s="190">
+        <v>46183</v>
+      </c>
+      <c r="L45" s="189">
+        <v>33036</v>
+      </c>
+      <c r="M45" s="189">
+        <v>391</v>
+      </c>
+      <c r="N45" s="189">
+        <v>200</v>
+      </c>
+      <c r="O45" s="189">
+        <f>P45-L45-M45-N45</f>
+        <v>1273</v>
+      </c>
+      <c r="P45" s="191">
+        <v>34900</v>
+      </c>
+      <c r="Q45" s="189" t="s">
+        <v>333</v>
+      </c>
+      <c r="R45" s="189" t="s">
+        <v>22</v>
+      </c>
       <c r="S45" s="189"/>
-      <c r="T45" s="219"/>
+      <c r="T45" s="216" t="s">
+        <v>320</v>
+      </c>
       <c r="U45" s="192"/>
       <c r="V45" s="193"/>
       <c r="W45" s="193"/>
@@ -13257,53 +12991,57 @@
       <c r="A46" s="185"/>
       <c r="B46" s="186"/>
       <c r="C46" s="187" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="D46" s="188" t="s">
-        <v>127</v>
-      </c>
-      <c r="E46" s="188"/>
+        <v>123</v>
+      </c>
+      <c r="E46" s="188" t="s">
+        <v>332</v>
+      </c>
       <c r="F46" s="188" t="s">
-        <v>256</v>
+        <v>328</v>
       </c>
       <c r="G46" s="188" t="s">
-        <v>24</v>
+        <v>329</v>
       </c>
       <c r="H46" s="188" t="s">
-        <v>257</v>
+        <v>330</v>
       </c>
       <c r="I46" s="189">
-        <v>24519</v>
+        <v>6900</v>
       </c>
       <c r="J46" s="190">
-        <v>45312</v>
+        <v>46077</v>
       </c>
       <c r="K46" s="190">
-        <v>46132</v>
+        <v>46183</v>
       </c>
       <c r="L46" s="189">
-        <v>25000</v>
+        <v>34630</v>
       </c>
       <c r="M46" s="189">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="N46" s="189">
         <v>200</v>
       </c>
       <c r="O46" s="189">
         <f>P46-L46-M46-N46</f>
-        <v>3700</v>
+        <v>1765</v>
       </c>
       <c r="P46" s="191">
-        <v>28900</v>
-      </c>
-      <c r="Q46" s="189" t="s">
-        <v>35</v>
-      </c>
-      <c r="R46" s="189"/>
+        <v>36900</v>
+      </c>
+      <c r="Q46" s="208" t="s">
+        <v>396</v>
+      </c>
+      <c r="R46" s="189" t="s">
+        <v>22</v>
+      </c>
       <c r="S46" s="189"/>
-      <c r="T46" s="217" t="s">
-        <v>325</v>
+      <c r="T46" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="U46" s="192"/>
       <c r="V46" s="193"/>
@@ -13346,7 +13084,7 @@
       <c r="BG46" s="193"/>
       <c r="BH46" s="193"/>
     </row>
-    <row r="47" spans="1:60" s="194" customFormat="1" ht="4.5" customHeight="1">
+    <row r="47" spans="1:60" s="210" customFormat="1" ht="4.95" customHeight="1">
       <c r="A47" s="185"/>
       <c r="B47" s="186"/>
       <c r="C47" s="187"/>
@@ -13366,7 +13104,7 @@
       <c r="Q47" s="189"/>
       <c r="R47" s="189"/>
       <c r="S47" s="189"/>
-      <c r="T47" s="217"/>
+      <c r="T47" s="216"/>
       <c r="U47" s="192"/>
       <c r="V47" s="193"/>
       <c r="W47" s="193"/>
@@ -13408,61 +13146,57 @@
       <c r="BG47" s="193"/>
       <c r="BH47" s="193"/>
     </row>
-    <row r="48" spans="1:60" s="210" customFormat="1" ht="19.5" customHeight="1">
+    <row r="48" spans="1:60" s="210" customFormat="1" ht="19.2" customHeight="1">
       <c r="A48" s="185"/>
       <c r="B48" s="186"/>
       <c r="C48" s="187" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="D48" s="188" t="s">
-        <v>123</v>
-      </c>
-      <c r="E48" s="188" t="s">
-        <v>252</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="E48" s="188"/>
       <c r="F48" s="188" t="s">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="G48" s="188" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H48" s="188" t="s">
-        <v>306</v>
+        <v>276</v>
       </c>
       <c r="I48" s="189">
-        <v>27900</v>
+        <v>41703</v>
       </c>
       <c r="J48" s="190">
-        <v>45849</v>
+        <v>44824</v>
       </c>
       <c r="K48" s="190">
-        <v>46169</v>
+        <v>46147</v>
       </c>
       <c r="L48" s="189">
-        <v>30557</v>
+        <v>24000</v>
       </c>
       <c r="M48" s="189">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="N48" s="189">
         <v>200</v>
       </c>
       <c r="O48" s="189">
         <f>P48-L48-M48-N48</f>
-        <v>1422</v>
+        <v>1700</v>
       </c>
       <c r="P48" s="191">
-        <v>32500</v>
+        <v>25900</v>
       </c>
       <c r="Q48" s="189" t="s">
         <v>35</v>
       </c>
-      <c r="R48" s="189" t="s">
-        <v>22</v>
-      </c>
+      <c r="R48" s="189"/>
       <c r="S48" s="189"/>
-      <c r="T48" s="228" t="s">
-        <v>325</v>
+      <c r="T48" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="U48" s="192"/>
       <c r="V48" s="193"/>
@@ -13505,62 +13239,27 @@
       <c r="BG48" s="193"/>
       <c r="BH48" s="193"/>
     </row>
-    <row r="49" spans="1:60" s="210" customFormat="1" ht="19.5" customHeight="1">
+    <row r="49" spans="1:60" s="210" customFormat="1" ht="5.4" customHeight="1">
       <c r="A49" s="185"/>
       <c r="B49" s="186"/>
-      <c r="C49" s="187" t="s">
-        <v>251</v>
-      </c>
-      <c r="D49" s="188" t="s">
-        <v>123</v>
-      </c>
-      <c r="E49" s="188" t="s">
-        <v>329</v>
-      </c>
-      <c r="F49" s="188" t="s">
-        <v>330</v>
-      </c>
-      <c r="G49" s="188" t="s">
-        <v>331</v>
-      </c>
-      <c r="H49" s="188" t="s">
-        <v>332</v>
-      </c>
-      <c r="I49" s="189">
-        <v>9253</v>
-      </c>
-      <c r="J49" s="190">
-        <v>45992</v>
-      </c>
-      <c r="K49" s="190">
-        <v>46183</v>
-      </c>
-      <c r="L49" s="189">
-        <v>33036</v>
-      </c>
-      <c r="M49" s="189">
-        <v>391</v>
-      </c>
-      <c r="N49" s="189">
-        <v>200</v>
-      </c>
-      <c r="O49" s="189">
-        <f>P49-L49-M49-N49</f>
-        <v>1273</v>
-      </c>
-      <c r="P49" s="191">
-        <v>34900</v>
-      </c>
-      <c r="Q49" s="189" t="s">
-        <v>338</v>
-      </c>
-      <c r="R49" s="189" t="s">
-        <v>22</v>
-      </c>
+      <c r="C49" s="187"/>
+      <c r="D49" s="188"/>
+      <c r="E49" s="188"/>
+      <c r="F49" s="188"/>
+      <c r="G49" s="188"/>
+      <c r="H49" s="188"/>
+      <c r="I49" s="189"/>
+      <c r="J49" s="190"/>
+      <c r="K49" s="190"/>
+      <c r="L49" s="189"/>
+      <c r="M49" s="189"/>
+      <c r="N49" s="189"/>
+      <c r="O49" s="189"/>
+      <c r="P49" s="191"/>
+      <c r="Q49" s="189"/>
+      <c r="R49" s="189"/>
       <c r="S49" s="189"/>
-      <c r="T49" s="217" t="s">
-        <v>325</v>
-      </c>
+      <c r="T49" s="216"/>
       <c r="U49" s="192"/>
       <c r="V49" s="193"/>
       <c r="W49" s="193"/>
@@ -13606,57 +13305,53 @@
       <c r="A50" s="185"/>
       <c r="B50" s="186"/>
       <c r="C50" s="187" t="s">
-        <v>251</v>
+        <v>386</v>
       </c>
       <c r="D50" s="188" t="s">
         <v>123</v>
       </c>
-      <c r="E50" s="188" t="s">
-        <v>337</v>
-      </c>
+      <c r="E50" s="188"/>
       <c r="F50" s="188" t="s">
-        <v>333</v>
+        <v>387</v>
       </c>
       <c r="G50" s="188" t="s">
-        <v>334</v>
+        <v>28</v>
       </c>
       <c r="H50" s="188" t="s">
-        <v>335</v>
+        <v>388</v>
       </c>
       <c r="I50" s="189">
-        <v>6900</v>
+        <v>22201</v>
       </c>
       <c r="J50" s="190">
-        <v>46077</v>
+        <v>45980</v>
       </c>
       <c r="K50" s="190">
-        <v>46183</v>
+        <v>46220</v>
       </c>
       <c r="L50" s="189">
-        <v>34630</v>
+        <v>34989</v>
       </c>
       <c r="M50" s="189">
-        <v>305</v>
+        <v>0</v>
       </c>
       <c r="N50" s="189">
         <v>200</v>
       </c>
       <c r="O50" s="189">
         <f>P50-L50-M50-N50</f>
-        <v>1765</v>
+        <v>4311</v>
       </c>
       <c r="P50" s="191">
-        <v>36900</v>
-      </c>
-      <c r="Q50" s="208" t="s">
-        <v>424</v>
-      </c>
-      <c r="R50" s="189" t="s">
-        <v>22</v>
-      </c>
+        <v>39500</v>
+      </c>
+      <c r="Q50" s="189" t="s">
+        <v>337</v>
+      </c>
+      <c r="R50" s="189"/>
       <c r="S50" s="189"/>
-      <c r="T50" s="217" t="s">
-        <v>325</v>
+      <c r="T50" s="219" t="s">
+        <v>320</v>
       </c>
       <c r="U50" s="192"/>
       <c r="V50" s="193"/>
@@ -13699,339 +13394,111 @@
       <c r="BG50" s="193"/>
       <c r="BH50" s="193"/>
     </row>
-    <row r="51" spans="1:60" s="210" customFormat="1" ht="4.95" customHeight="1">
-      <c r="A51" s="185"/>
-      <c r="B51" s="186"/>
-      <c r="C51" s="187"/>
-      <c r="D51" s="188"/>
-      <c r="E51" s="188"/>
-      <c r="F51" s="188"/>
-      <c r="G51" s="188"/>
-      <c r="H51" s="188"/>
-      <c r="I51" s="189"/>
-      <c r="J51" s="190"/>
-      <c r="K51" s="190"/>
-      <c r="L51" s="189"/>
-      <c r="M51" s="189"/>
-      <c r="N51" s="189"/>
-      <c r="O51" s="189"/>
-      <c r="P51" s="191"/>
-      <c r="Q51" s="189"/>
-      <c r="R51" s="189"/>
-      <c r="S51" s="189"/>
-      <c r="T51" s="217"/>
-      <c r="U51" s="192"/>
-      <c r="V51" s="193"/>
-      <c r="W51" s="193"/>
-      <c r="X51" s="193"/>
-      <c r="Y51" s="193"/>
-      <c r="Z51" s="193"/>
-      <c r="AA51" s="193"/>
-      <c r="AB51" s="193"/>
-      <c r="AC51" s="193"/>
-      <c r="AD51" s="193"/>
-      <c r="AE51" s="193"/>
-      <c r="AF51" s="193"/>
-      <c r="AG51" s="193"/>
-      <c r="AH51" s="193"/>
-      <c r="AI51" s="193"/>
-      <c r="AJ51" s="193"/>
-      <c r="AK51" s="193"/>
-      <c r="AL51" s="193"/>
-      <c r="AM51" s="193"/>
-      <c r="AN51" s="193"/>
-      <c r="AO51" s="193"/>
-      <c r="AP51" s="193"/>
-      <c r="AQ51" s="193"/>
-      <c r="AR51" s="193"/>
-      <c r="AS51" s="193"/>
-      <c r="AT51" s="193"/>
-      <c r="AU51" s="193"/>
-      <c r="AV51" s="193"/>
-      <c r="AW51" s="193"/>
-      <c r="AX51" s="193"/>
-      <c r="AY51" s="193"/>
-      <c r="AZ51" s="193"/>
-      <c r="BA51" s="193"/>
-      <c r="BB51" s="193"/>
-      <c r="BC51" s="193"/>
-      <c r="BD51" s="193"/>
-      <c r="BE51" s="193"/>
-      <c r="BF51" s="193"/>
-      <c r="BG51" s="193"/>
-      <c r="BH51" s="193"/>
-    </row>
-    <row r="52" spans="1:60" s="210" customFormat="1" ht="19.2" customHeight="1">
-      <c r="A52" s="185"/>
-      <c r="B52" s="186"/>
-      <c r="C52" s="203" t="s">
-        <v>279</v>
-      </c>
-      <c r="D52" s="204" t="s">
-        <v>127</v>
-      </c>
-      <c r="E52" s="204"/>
-      <c r="F52" s="204" t="s">
-        <v>280</v>
-      </c>
-      <c r="G52" s="204" t="s">
-        <v>24</v>
-      </c>
-      <c r="H52" s="204" t="s">
-        <v>281</v>
-      </c>
-      <c r="I52" s="205">
-        <v>41703</v>
-      </c>
-      <c r="J52" s="206">
-        <v>44824</v>
-      </c>
-      <c r="K52" s="206">
-        <v>46147</v>
-      </c>
-      <c r="L52" s="205">
-        <v>24000</v>
-      </c>
-      <c r="M52" s="205">
-        <v>0</v>
-      </c>
-      <c r="N52" s="205">
-        <v>200</v>
-      </c>
-      <c r="O52" s="205">
-        <f>P52-L52-M52-N52</f>
-        <v>1700</v>
-      </c>
-      <c r="P52" s="207">
-        <v>25900</v>
-      </c>
-      <c r="Q52" s="205" t="s">
-        <v>35</v>
-      </c>
-      <c r="R52" s="205"/>
-      <c r="S52" s="205" t="s">
-        <v>420</v>
-      </c>
-      <c r="T52" s="218" t="s">
-        <v>325</v>
-      </c>
-      <c r="U52" s="192"/>
-      <c r="V52" s="193"/>
-      <c r="W52" s="193"/>
-      <c r="X52" s="193"/>
-      <c r="Y52" s="193"/>
-      <c r="Z52" s="193"/>
-      <c r="AA52" s="193"/>
-      <c r="AB52" s="193"/>
-      <c r="AC52" s="193"/>
-      <c r="AD52" s="193"/>
-      <c r="AE52" s="193"/>
-      <c r="AF52" s="193"/>
-      <c r="AG52" s="193"/>
-      <c r="AH52" s="193"/>
-      <c r="AI52" s="193"/>
-      <c r="AJ52" s="193"/>
-      <c r="AK52" s="193"/>
-      <c r="AL52" s="193"/>
-      <c r="AM52" s="193"/>
-      <c r="AN52" s="193"/>
-      <c r="AO52" s="193"/>
-      <c r="AP52" s="193"/>
-      <c r="AQ52" s="193"/>
-      <c r="AR52" s="193"/>
-      <c r="AS52" s="193"/>
-      <c r="AT52" s="193"/>
-      <c r="AU52" s="193"/>
-      <c r="AV52" s="193"/>
-      <c r="AW52" s="193"/>
-      <c r="AX52" s="193"/>
-      <c r="AY52" s="193"/>
-      <c r="AZ52" s="193"/>
-      <c r="BA52" s="193"/>
-      <c r="BB52" s="193"/>
-      <c r="BC52" s="193"/>
-      <c r="BD52" s="193"/>
-      <c r="BE52" s="193"/>
-      <c r="BF52" s="193"/>
-      <c r="BG52" s="193"/>
-      <c r="BH52" s="193"/>
-    </row>
-    <row r="53" spans="1:60" s="210" customFormat="1" ht="5.4" customHeight="1">
-      <c r="A53" s="185"/>
-      <c r="B53" s="186"/>
-      <c r="C53" s="187"/>
-      <c r="D53" s="188"/>
-      <c r="E53" s="188"/>
-      <c r="F53" s="188"/>
-      <c r="G53" s="188"/>
-      <c r="H53" s="188"/>
-      <c r="I53" s="189"/>
-      <c r="J53" s="190"/>
-      <c r="K53" s="190"/>
-      <c r="L53" s="189"/>
-      <c r="M53" s="189"/>
-      <c r="N53" s="189"/>
-      <c r="O53" s="189"/>
-      <c r="P53" s="191"/>
-      <c r="Q53" s="189"/>
-      <c r="R53" s="189"/>
-      <c r="S53" s="189"/>
-      <c r="T53" s="217"/>
-      <c r="U53" s="192"/>
-      <c r="V53" s="193"/>
-      <c r="W53" s="193"/>
-      <c r="X53" s="193"/>
-      <c r="Y53" s="193"/>
-      <c r="Z53" s="193"/>
-      <c r="AA53" s="193"/>
-      <c r="AB53" s="193"/>
-      <c r="AC53" s="193"/>
-      <c r="AD53" s="193"/>
-      <c r="AE53" s="193"/>
-      <c r="AF53" s="193"/>
-      <c r="AG53" s="193"/>
-      <c r="AH53" s="193"/>
-      <c r="AI53" s="193"/>
-      <c r="AJ53" s="193"/>
-      <c r="AK53" s="193"/>
-      <c r="AL53" s="193"/>
-      <c r="AM53" s="193"/>
-      <c r="AN53" s="193"/>
-      <c r="AO53" s="193"/>
-      <c r="AP53" s="193"/>
-      <c r="AQ53" s="193"/>
-      <c r="AR53" s="193"/>
-      <c r="AS53" s="193"/>
-      <c r="AT53" s="193"/>
-      <c r="AU53" s="193"/>
-      <c r="AV53" s="193"/>
-      <c r="AW53" s="193"/>
-      <c r="AX53" s="193"/>
-      <c r="AY53" s="193"/>
-      <c r="AZ53" s="193"/>
-      <c r="BA53" s="193"/>
-      <c r="BB53" s="193"/>
-      <c r="BC53" s="193"/>
-      <c r="BD53" s="193"/>
-      <c r="BE53" s="193"/>
-      <c r="BF53" s="193"/>
-      <c r="BG53" s="193"/>
-      <c r="BH53" s="193"/>
-    </row>
-    <row r="54" spans="1:60" s="210" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A54" s="185"/>
-      <c r="B54" s="186"/>
-      <c r="C54" s="187" t="s">
-        <v>413</v>
-      </c>
-      <c r="D54" s="188" t="s">
-        <v>123</v>
-      </c>
-      <c r="E54" s="188"/>
-      <c r="F54" s="188" t="s">
-        <v>414</v>
-      </c>
-      <c r="G54" s="188" t="s">
-        <v>28</v>
-      </c>
-      <c r="H54" s="188" t="s">
-        <v>415</v>
-      </c>
-      <c r="I54" s="189">
-        <v>22201</v>
-      </c>
-      <c r="J54" s="190">
-        <v>45980</v>
-      </c>
-      <c r="K54" s="190">
-        <v>46220</v>
-      </c>
-      <c r="L54" s="189">
-        <v>34989</v>
-      </c>
-      <c r="M54" s="189">
-        <v>0</v>
-      </c>
-      <c r="N54" s="189">
-        <v>200</v>
-      </c>
-      <c r="O54" s="189">
-        <f>P54-L54-M54-N54</f>
-        <v>4311</v>
-      </c>
-      <c r="P54" s="191">
-        <v>39500</v>
-      </c>
-      <c r="Q54" s="189" t="s">
-        <v>342</v>
-      </c>
-      <c r="R54" s="189"/>
-      <c r="S54" s="189"/>
-      <c r="T54" s="220" t="s">
-        <v>325</v>
-      </c>
-      <c r="U54" s="192"/>
-      <c r="V54" s="193"/>
-      <c r="W54" s="193"/>
-      <c r="X54" s="193"/>
-      <c r="Y54" s="193"/>
-      <c r="Z54" s="193"/>
-      <c r="AA54" s="193"/>
-      <c r="AB54" s="193"/>
-      <c r="AC54" s="193"/>
-      <c r="AD54" s="193"/>
-      <c r="AE54" s="193"/>
-      <c r="AF54" s="193"/>
-      <c r="AG54" s="193"/>
-      <c r="AH54" s="193"/>
-      <c r="AI54" s="193"/>
-      <c r="AJ54" s="193"/>
-      <c r="AK54" s="193"/>
-      <c r="AL54" s="193"/>
-      <c r="AM54" s="193"/>
-      <c r="AN54" s="193"/>
-      <c r="AO54" s="193"/>
-      <c r="AP54" s="193"/>
-      <c r="AQ54" s="193"/>
-      <c r="AR54" s="193"/>
-      <c r="AS54" s="193"/>
-      <c r="AT54" s="193"/>
-      <c r="AU54" s="193"/>
-      <c r="AV54" s="193"/>
-      <c r="AW54" s="193"/>
-      <c r="AX54" s="193"/>
-      <c r="AY54" s="193"/>
-      <c r="AZ54" s="193"/>
-      <c r="BA54" s="193"/>
-      <c r="BB54" s="193"/>
-      <c r="BC54" s="193"/>
-      <c r="BD54" s="193"/>
-      <c r="BE54" s="193"/>
-      <c r="BF54" s="193"/>
-      <c r="BG54" s="193"/>
-      <c r="BH54" s="193"/>
-    </row>
-    <row r="55" spans="1:60" s="210" customFormat="1" ht="4.5" customHeight="1">
-      <c r="B55" s="211"/>
-      <c r="C55" s="212"/>
-      <c r="D55" s="212"/>
-      <c r="E55" s="212"/>
-      <c r="F55" s="212"/>
-      <c r="G55" s="212"/>
-      <c r="H55" s="212"/>
-      <c r="I55" s="212"/>
-      <c r="J55" s="212"/>
-      <c r="K55" s="213"/>
-      <c r="L55" s="212"/>
-      <c r="M55" s="212"/>
-      <c r="N55" s="212"/>
-      <c r="O55" s="212"/>
-      <c r="P55" s="212"/>
-      <c r="Q55" s="212"/>
-      <c r="R55" s="213"/>
-      <c r="S55" s="212"/>
-      <c r="T55" s="214"/>
-      <c r="U55" s="215"/>
+    <row r="51" spans="1:60" s="210" customFormat="1" ht="4.5" customHeight="1">
+      <c r="B51" s="211"/>
+      <c r="C51" s="212"/>
+      <c r="D51" s="212"/>
+      <c r="E51" s="212"/>
+      <c r="F51" s="212"/>
+      <c r="G51" s="212"/>
+      <c r="H51" s="212"/>
+      <c r="I51" s="212"/>
+      <c r="J51" s="212"/>
+      <c r="K51" s="213"/>
+      <c r="L51" s="212"/>
+      <c r="M51" s="212"/>
+      <c r="N51" s="212"/>
+      <c r="O51" s="212"/>
+      <c r="P51" s="212"/>
+      <c r="Q51" s="212"/>
+      <c r="R51" s="213"/>
+      <c r="S51" s="212"/>
+      <c r="T51" s="214"/>
+      <c r="U51" s="215"/>
+    </row>
+    <row r="52" spans="1:60" s="104" customFormat="1" ht="15" customHeight="1">
+      <c r="C52" s="124"/>
+      <c r="D52" s="124"/>
+      <c r="E52" s="124"/>
+      <c r="F52" s="124"/>
+      <c r="G52" s="124"/>
+      <c r="H52" s="124"/>
+      <c r="I52" s="124"/>
+      <c r="J52" s="124"/>
+      <c r="K52" s="125"/>
+      <c r="L52" s="124"/>
+      <c r="M52" s="124"/>
+      <c r="N52" s="124"/>
+      <c r="O52" s="124"/>
+      <c r="P52" s="124"/>
+      <c r="Q52" s="124"/>
+      <c r="R52" s="125"/>
+      <c r="S52" s="124"/>
+      <c r="T52" s="42"/>
+      <c r="U52" s="105"/>
+    </row>
+    <row r="53" spans="1:60" s="104" customFormat="1" ht="15" customHeight="1">
+      <c r="C53" s="124"/>
+      <c r="D53" s="124"/>
+      <c r="E53" s="124"/>
+      <c r="F53" s="124"/>
+      <c r="G53" s="124"/>
+      <c r="H53" s="124"/>
+      <c r="I53" s="124"/>
+      <c r="J53" s="124"/>
+      <c r="K53" s="125"/>
+      <c r="L53" s="124"/>
+      <c r="M53" s="124"/>
+      <c r="N53" s="124"/>
+      <c r="O53" s="124"/>
+      <c r="P53" s="124"/>
+      <c r="Q53" s="124"/>
+      <c r="R53" s="125"/>
+      <c r="S53" s="124"/>
+      <c r="T53" s="42"/>
+      <c r="U53" s="105"/>
+    </row>
+    <row r="54" spans="1:60" s="104" customFormat="1" ht="15" customHeight="1">
+      <c r="C54" s="124"/>
+      <c r="D54" s="124"/>
+      <c r="E54" s="124"/>
+      <c r="F54" s="124"/>
+      <c r="G54" s="124"/>
+      <c r="H54" s="124"/>
+      <c r="I54" s="124"/>
+      <c r="J54" s="124"/>
+      <c r="K54" s="125"/>
+      <c r="L54" s="124"/>
+      <c r="M54" s="124"/>
+      <c r="N54" s="124"/>
+      <c r="O54" s="124"/>
+      <c r="P54" s="124"/>
+      <c r="Q54" s="124"/>
+      <c r="R54" s="125"/>
+      <c r="S54" s="124"/>
+      <c r="T54" s="42"/>
+      <c r="U54" s="105"/>
+    </row>
+    <row r="55" spans="1:60" s="104" customFormat="1" ht="15" customHeight="1">
+      <c r="C55" s="124"/>
+      <c r="D55" s="124"/>
+      <c r="E55" s="124"/>
+      <c r="F55" s="124"/>
+      <c r="G55" s="124"/>
+      <c r="H55" s="124"/>
+      <c r="I55" s="124"/>
+      <c r="J55" s="124"/>
+      <c r="K55" s="125"/>
+      <c r="L55" s="124"/>
+      <c r="M55" s="124"/>
+      <c r="N55" s="124"/>
+      <c r="O55" s="124"/>
+      <c r="P55" s="124"/>
+      <c r="Q55" s="124"/>
+      <c r="R55" s="125"/>
+      <c r="S55" s="124"/>
+      <c r="T55" s="42"/>
+      <c r="U55" s="105"/>
     </row>
     <row r="56" spans="1:60" s="104" customFormat="1" ht="15" customHeight="1">
       <c r="C56" s="124"/>
@@ -18926,7 +18393,7 @@
       <c r="T288" s="42"/>
       <c r="U288" s="105"/>
     </row>
-    <row r="289" spans="3:21" s="104" customFormat="1" ht="15" customHeight="1">
+    <row r="289" spans="2:21" s="104" customFormat="1" ht="15" customHeight="1">
       <c r="C289" s="124"/>
       <c r="D289" s="124"/>
       <c r="E289" s="124"/>
@@ -18947,7 +18414,7 @@
       <c r="T289" s="42"/>
       <c r="U289" s="105"/>
     </row>
-    <row r="290" spans="3:21" s="104" customFormat="1" ht="15" customHeight="1">
+    <row r="290" spans="2:21" s="104" customFormat="1" ht="15" customHeight="1">
       <c r="C290" s="124"/>
       <c r="D290" s="124"/>
       <c r="E290" s="124"/>
@@ -18968,7 +18435,7 @@
       <c r="T290" s="42"/>
       <c r="U290" s="105"/>
     </row>
-    <row r="291" spans="3:21" s="104" customFormat="1" ht="15" customHeight="1">
+    <row r="291" spans="2:21" s="104" customFormat="1" ht="15" customHeight="1">
       <c r="C291" s="124"/>
       <c r="D291" s="124"/>
       <c r="E291" s="124"/>
@@ -18989,7 +18456,7 @@
       <c r="T291" s="42"/>
       <c r="U291" s="105"/>
     </row>
-    <row r="292" spans="3:21" s="104" customFormat="1" ht="15" customHeight="1">
+    <row r="292" spans="2:21" s="104" customFormat="1" ht="15" customHeight="1">
       <c r="C292" s="124"/>
       <c r="D292" s="124"/>
       <c r="E292" s="124"/>
@@ -19010,7 +18477,7 @@
       <c r="T292" s="42"/>
       <c r="U292" s="105"/>
     </row>
-    <row r="293" spans="3:21" s="104" customFormat="1" ht="15" customHeight="1">
+    <row r="293" spans="2:21" s="104" customFormat="1" ht="15" customHeight="1">
       <c r="C293" s="124"/>
       <c r="D293" s="124"/>
       <c r="E293" s="124"/>
@@ -19031,7 +18498,7 @@
       <c r="T293" s="42"/>
       <c r="U293" s="105"/>
     </row>
-    <row r="294" spans="3:21" s="104" customFormat="1" ht="15" customHeight="1">
+    <row r="294" spans="2:21" s="104" customFormat="1" ht="15" customHeight="1">
       <c r="C294" s="124"/>
       <c r="D294" s="124"/>
       <c r="E294" s="124"/>
@@ -19052,7 +18519,7 @@
       <c r="T294" s="42"/>
       <c r="U294" s="105"/>
     </row>
-    <row r="295" spans="3:21" s="104" customFormat="1" ht="15" customHeight="1">
+    <row r="295" spans="2:21" s="104" customFormat="1" ht="15" customHeight="1">
       <c r="C295" s="124"/>
       <c r="D295" s="124"/>
       <c r="E295" s="124"/>
@@ -19073,7 +18540,7 @@
       <c r="T295" s="42"/>
       <c r="U295" s="105"/>
     </row>
-    <row r="296" spans="3:21" s="104" customFormat="1" ht="15" customHeight="1">
+    <row r="296" spans="2:21" s="104" customFormat="1" ht="15" customHeight="1">
       <c r="C296" s="124"/>
       <c r="D296" s="124"/>
       <c r="E296" s="124"/>
@@ -19094,7 +18561,7 @@
       <c r="T296" s="42"/>
       <c r="U296" s="105"/>
     </row>
-    <row r="297" spans="3:21" s="104" customFormat="1" ht="15" customHeight="1">
+    <row r="297" spans="2:21" s="104" customFormat="1" ht="15" customHeight="1">
       <c r="C297" s="124"/>
       <c r="D297" s="124"/>
       <c r="E297" s="124"/>
@@ -19115,7 +18582,7 @@
       <c r="T297" s="42"/>
       <c r="U297" s="105"/>
     </row>
-    <row r="298" spans="3:21" s="104" customFormat="1" ht="15" customHeight="1">
+    <row r="298" spans="2:21" s="104" customFormat="1" ht="15" customHeight="1">
       <c r="C298" s="124"/>
       <c r="D298" s="124"/>
       <c r="E298" s="124"/>
@@ -19136,7 +18603,7 @@
       <c r="T298" s="42"/>
       <c r="U298" s="105"/>
     </row>
-    <row r="299" spans="3:21" s="104" customFormat="1" ht="15" customHeight="1">
+    <row r="299" spans="2:21" s="104" customFormat="1" ht="15" customHeight="1">
       <c r="C299" s="124"/>
       <c r="D299" s="124"/>
       <c r="E299" s="124"/>
@@ -19157,7 +18624,7 @@
       <c r="T299" s="42"/>
       <c r="U299" s="105"/>
     </row>
-    <row r="300" spans="3:21" s="104" customFormat="1" ht="15" customHeight="1">
+    <row r="300" spans="2:21" s="104" customFormat="1" ht="15" customHeight="1">
       <c r="C300" s="124"/>
       <c r="D300" s="124"/>
       <c r="E300" s="124"/>
@@ -19178,7 +18645,7 @@
       <c r="T300" s="42"/>
       <c r="U300" s="105"/>
     </row>
-    <row r="301" spans="3:21" s="104" customFormat="1" ht="15" customHeight="1">
+    <row r="301" spans="2:21" s="104" customFormat="1" ht="15" customHeight="1">
       <c r="C301" s="124"/>
       <c r="D301" s="124"/>
       <c r="E301" s="124"/>
@@ -19199,7 +18666,7 @@
       <c r="T301" s="42"/>
       <c r="U301" s="105"/>
     </row>
-    <row r="302" spans="3:21" s="104" customFormat="1" ht="15" customHeight="1">
+    <row r="302" spans="2:21" s="104" customFormat="1" ht="15" customHeight="1">
       <c r="C302" s="124"/>
       <c r="D302" s="124"/>
       <c r="E302" s="124"/>
@@ -19220,7 +18687,7 @@
       <c r="T302" s="42"/>
       <c r="U302" s="105"/>
     </row>
-    <row r="303" spans="3:21" s="104" customFormat="1" ht="15" customHeight="1">
+    <row r="303" spans="2:21" s="104" customFormat="1" ht="15" customHeight="1">
       <c r="C303" s="124"/>
       <c r="D303" s="124"/>
       <c r="E303" s="124"/>
@@ -19241,7 +18708,8 @@
       <c r="T303" s="42"/>
       <c r="U303" s="105"/>
     </row>
-    <row r="304" spans="3:21" s="104" customFormat="1" ht="15" customHeight="1">
+    <row r="304" spans="2:21" ht="15" customHeight="1">
+      <c r="B304" s="104"/>
       <c r="C304" s="124"/>
       <c r="D304" s="124"/>
       <c r="E304" s="124"/>
@@ -19260,9 +18728,9 @@
       <c r="R304" s="125"/>
       <c r="S304" s="124"/>
       <c r="T304" s="42"/>
-      <c r="U304" s="105"/>
-    </row>
-    <row r="305" spans="2:21" s="104" customFormat="1" ht="15" customHeight="1">
+    </row>
+    <row r="305" spans="2:20" ht="15" customHeight="1">
+      <c r="B305" s="104"/>
       <c r="C305" s="124"/>
       <c r="D305" s="124"/>
       <c r="E305" s="124"/>
@@ -19281,9 +18749,9 @@
       <c r="R305" s="125"/>
       <c r="S305" s="124"/>
       <c r="T305" s="42"/>
-      <c r="U305" s="105"/>
-    </row>
-    <row r="306" spans="2:21" s="104" customFormat="1" ht="15" customHeight="1">
+    </row>
+    <row r="306" spans="2:20" ht="15" customHeight="1">
+      <c r="B306" s="104"/>
       <c r="C306" s="124"/>
       <c r="D306" s="124"/>
       <c r="E306" s="124"/>
@@ -19302,93 +18770,8 @@
       <c r="R306" s="125"/>
       <c r="S306" s="124"/>
       <c r="T306" s="42"/>
-      <c r="U306" s="105"/>
-    </row>
-    <row r="307" spans="2:21" s="104" customFormat="1" ht="15" customHeight="1">
-      <c r="C307" s="124"/>
-      <c r="D307" s="124"/>
-      <c r="E307" s="124"/>
-      <c r="F307" s="124"/>
-      <c r="G307" s="124"/>
-      <c r="H307" s="124"/>
-      <c r="I307" s="124"/>
-      <c r="J307" s="124"/>
-      <c r="K307" s="125"/>
-      <c r="L307" s="124"/>
-      <c r="M307" s="124"/>
-      <c r="N307" s="124"/>
-      <c r="O307" s="124"/>
-      <c r="P307" s="124"/>
-      <c r="Q307" s="124"/>
-      <c r="R307" s="125"/>
-      <c r="S307" s="124"/>
-      <c r="T307" s="42"/>
-      <c r="U307" s="105"/>
-    </row>
-    <row r="308" spans="2:21" ht="15" customHeight="1">
-      <c r="B308" s="104"/>
-      <c r="C308" s="124"/>
-      <c r="D308" s="124"/>
-      <c r="E308" s="124"/>
-      <c r="F308" s="124"/>
-      <c r="G308" s="124"/>
-      <c r="H308" s="124"/>
-      <c r="I308" s="124"/>
-      <c r="J308" s="124"/>
-      <c r="K308" s="125"/>
-      <c r="L308" s="124"/>
-      <c r="M308" s="124"/>
-      <c r="N308" s="124"/>
-      <c r="O308" s="124"/>
-      <c r="P308" s="124"/>
-      <c r="Q308" s="124"/>
-      <c r="R308" s="125"/>
-      <c r="S308" s="124"/>
-      <c r="T308" s="42"/>
-    </row>
-    <row r="309" spans="2:21" ht="15" customHeight="1">
-      <c r="B309" s="104"/>
-      <c r="C309" s="124"/>
-      <c r="D309" s="124"/>
-      <c r="E309" s="124"/>
-      <c r="F309" s="124"/>
-      <c r="G309" s="124"/>
-      <c r="H309" s="124"/>
-      <c r="I309" s="124"/>
-      <c r="J309" s="124"/>
-      <c r="K309" s="125"/>
-      <c r="L309" s="124"/>
-      <c r="M309" s="124"/>
-      <c r="N309" s="124"/>
-      <c r="O309" s="124"/>
-      <c r="P309" s="124"/>
-      <c r="Q309" s="124"/>
-      <c r="R309" s="125"/>
-      <c r="S309" s="124"/>
-      <c r="T309" s="42"/>
-    </row>
-    <row r="310" spans="2:21" ht="15" customHeight="1">
-      <c r="B310" s="104"/>
-      <c r="C310" s="124"/>
-      <c r="D310" s="124"/>
-      <c r="E310" s="124"/>
-      <c r="F310" s="124"/>
-      <c r="G310" s="124"/>
-      <c r="H310" s="124"/>
-      <c r="I310" s="124"/>
-      <c r="J310" s="124"/>
-      <c r="K310" s="125"/>
-      <c r="L310" s="124"/>
-      <c r="M310" s="124"/>
-      <c r="N310" s="124"/>
-      <c r="O310" s="124"/>
-      <c r="P310" s="124"/>
-      <c r="Q310" s="124"/>
-      <c r="R310" s="125"/>
-      <c r="S310" s="124"/>
-      <c r="T310" s="42"/>
-    </row>
-    <row r="1048549" ht="12.75" customHeight="1"/>
+    </row>
+    <row r="1048545" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="R3:S3"/>
@@ -19403,7 +18786,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN147"/>
+  <dimension ref="A1:AN146"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="1.109375" style="134" customWidth="1"/>
@@ -19464,7 +18847,7 @@
     <row r="3" spans="1:40" s="14" customFormat="1" ht="15" customHeight="1">
       <c r="B3" s="15"/>
       <c r="C3" s="16" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D3" s="16"/>
       <c r="E3" s="16"/>
@@ -19479,7 +18862,7 @@
       <c r="N3" s="17"/>
       <c r="O3" s="17"/>
       <c r="P3" s="145">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="Q3" s="19"/>
       <c r="R3" s="20"/>
@@ -19603,25 +18986,25 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="H6" s="37">
         <v>99</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J6" s="38">
         <v>45959</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L6" s="38" t="s">
         <v>27</v>
@@ -19633,11 +19016,11 @@
         <v>31600</v>
       </c>
       <c r="O6" s="132" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P6" s="40"/>
-      <c r="Q6" s="217" t="s">
-        <v>325</v>
+      <c r="Q6" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="R6" s="41"/>
       <c r="S6" s="148"/>
@@ -19680,7 +19063,7 @@
       <c r="N7" s="37"/>
       <c r="O7" s="37"/>
       <c r="P7" s="40"/>
-      <c r="Q7" s="217"/>
+      <c r="Q7" s="216"/>
       <c r="R7" s="41"/>
       <c r="S7" s="148"/>
       <c r="T7" s="43"/>
@@ -19705,21 +19088,21 @@
       <c r="AM7" s="43"/>
       <c r="AN7" s="43"/>
     </row>
-    <row r="8" spans="1:40" s="232" customFormat="1" ht="19.95" customHeight="1">
-      <c r="A8" s="229"/>
-      <c r="B8" s="230"/>
+    <row r="8" spans="1:40" s="230" customFormat="1" ht="19.95" customHeight="1">
+      <c r="A8" s="227"/>
+      <c r="B8" s="228"/>
       <c r="C8" s="28" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="28"/>
       <c r="E8" s="28" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="H8" s="37">
         <v>99</v>
@@ -19731,7 +19114,7 @@
         <v>46203</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="L8" s="38">
         <v>46289</v>
@@ -19743,41 +19126,41 @@
         <v>36500</v>
       </c>
       <c r="O8" s="37" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="P8" s="40"/>
-      <c r="Q8" s="217" t="s">
-        <v>325</v>
-      </c>
-      <c r="R8" s="231"/>
-      <c r="S8" s="229"/>
-      <c r="T8" s="229"/>
-      <c r="U8" s="229"/>
-      <c r="V8" s="229"/>
-      <c r="W8" s="229"/>
-      <c r="X8" s="229"/>
-      <c r="Y8" s="229"/>
-      <c r="Z8" s="229"/>
-      <c r="AA8" s="229"/>
-      <c r="AB8" s="229"/>
-      <c r="AC8" s="229"/>
-      <c r="AD8" s="229"/>
-      <c r="AE8" s="229"/>
-      <c r="AF8" s="229"/>
-      <c r="AG8" s="229"/>
-      <c r="AH8" s="229"/>
-      <c r="AI8" s="229"/>
-      <c r="AJ8" s="229"/>
-      <c r="AK8" s="229"/>
-      <c r="AL8" s="229"/>
-      <c r="AM8" s="229"/>
+      <c r="Q8" s="216" t="s">
+        <v>320</v>
+      </c>
+      <c r="R8" s="229"/>
+      <c r="S8" s="227"/>
+      <c r="T8" s="227"/>
+      <c r="U8" s="227"/>
+      <c r="V8" s="227"/>
+      <c r="W8" s="227"/>
+      <c r="X8" s="227"/>
+      <c r="Y8" s="227"/>
+      <c r="Z8" s="227"/>
+      <c r="AA8" s="227"/>
+      <c r="AB8" s="227"/>
+      <c r="AC8" s="227"/>
+      <c r="AD8" s="227"/>
+      <c r="AE8" s="227"/>
+      <c r="AF8" s="227"/>
+      <c r="AG8" s="227"/>
+      <c r="AH8" s="227"/>
+      <c r="AI8" s="227"/>
+      <c r="AJ8" s="227"/>
+      <c r="AK8" s="227"/>
+      <c r="AL8" s="227"/>
+      <c r="AM8" s="227"/>
     </row>
     <row r="9" spans="1:40" ht="10.199999999999999" customHeight="1">
       <c r="B9" s="149"/>
       <c r="C9" s="45"/>
       <c r="D9" s="45"/>
       <c r="E9" s="45"/>
-      <c r="Q9" s="238"/>
+      <c r="Q9" s="236"/>
       <c r="R9" s="150"/>
     </row>
     <row r="10" spans="1:40" s="45" customFormat="1" ht="19.8" customHeight="1">
@@ -19788,25 +19171,25 @@
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="H10" s="37">
         <v>99</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J10" s="38">
         <v>46052</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="L10" s="38" t="s">
         <v>27</v>
@@ -19818,11 +19201,11 @@
         <v>32900</v>
       </c>
       <c r="O10" s="37" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="P10" s="40"/>
-      <c r="Q10" s="217" t="s">
-        <v>325</v>
+      <c r="Q10" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="R10" s="41"/>
       <c r="S10" s="148"/>
@@ -19862,7 +19245,7 @@
       <c r="N11" s="152"/>
       <c r="O11" s="136"/>
       <c r="P11" s="136"/>
-      <c r="Q11" s="222"/>
+      <c r="Q11" s="221"/>
       <c r="R11" s="150"/>
       <c r="S11" s="134"/>
       <c r="T11" s="134"/>
@@ -19895,13 +19278,13 @@
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="F12" s="226" t="s">
-        <v>403</v>
+        <v>154</v>
+      </c>
+      <c r="F12" s="225" t="s">
+        <v>380</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H12" s="37">
         <v>1471</v>
@@ -19913,7 +19296,7 @@
         <v>45897</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="L12" s="38" t="s">
         <v>27</v>
@@ -19925,13 +19308,13 @@
         <v>31900</v>
       </c>
       <c r="O12" s="132" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P12" s="40" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q12" s="217" t="s">
-        <v>325</v>
+        <v>158</v>
+      </c>
+      <c r="Q12" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="R12" s="41"/>
       <c r="S12" s="148"/>
@@ -19959,46 +19342,46 @@
     <row r="13" spans="1:40" s="45" customFormat="1" ht="19.5" customHeight="1">
       <c r="A13" s="34"/>
       <c r="B13" s="35"/>
-      <c r="C13" s="240" t="s">
+      <c r="C13" s="237" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="240"/>
-      <c r="E13" s="241" t="s">
-        <v>156</v>
-      </c>
-      <c r="F13" s="246" t="s">
-        <v>423</v>
-      </c>
-      <c r="G13" s="240" t="s">
-        <v>421</v>
-      </c>
-      <c r="H13" s="242">
+      <c r="D13" s="237"/>
+      <c r="E13" s="238" t="s">
+        <v>154</v>
+      </c>
+      <c r="F13" s="242" t="s">
+        <v>395</v>
+      </c>
+      <c r="G13" s="237" t="s">
+        <v>393</v>
+      </c>
+      <c r="H13" s="239">
         <v>99</v>
       </c>
-      <c r="I13" s="240" t="s">
+      <c r="I13" s="237" t="s">
         <v>28</v>
       </c>
-      <c r="J13" s="243">
+      <c r="J13" s="240">
         <v>46225</v>
       </c>
-      <c r="K13" s="240" t="s">
-        <v>422</v>
-      </c>
-      <c r="L13" s="243">
+      <c r="K13" s="237" t="s">
+        <v>394</v>
+      </c>
+      <c r="L13" s="240">
         <v>46318</v>
       </c>
-      <c r="M13" s="242">
+      <c r="M13" s="239">
         <v>31694</v>
       </c>
-      <c r="N13" s="242">
+      <c r="N13" s="239">
         <v>33900</v>
       </c>
-      <c r="O13" s="242" t="s">
-        <v>338</v>
-      </c>
-      <c r="P13" s="244"/>
-      <c r="Q13" s="247" t="s">
-        <v>325</v>
+      <c r="O13" s="239" t="s">
+        <v>333</v>
+      </c>
+      <c r="P13" s="241"/>
+      <c r="Q13" s="243" t="s">
+        <v>320</v>
       </c>
       <c r="R13" s="41"/>
       <c r="S13" s="148"/>
@@ -20040,7 +19423,7 @@
       <c r="N14" s="37"/>
       <c r="O14" s="37"/>
       <c r="P14" s="40"/>
-      <c r="Q14" s="220"/>
+      <c r="Q14" s="219"/>
       <c r="R14" s="41"/>
       <c r="S14" s="148"/>
       <c r="T14" s="43"/>
@@ -20072,13 +19455,13 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="36" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="H15" s="37">
         <v>99</v>
@@ -20090,7 +19473,7 @@
         <v>46169</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="L15" s="38">
         <v>46262</v>
@@ -20102,13 +19485,13 @@
         <v>38900</v>
       </c>
       <c r="O15" s="37" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="P15" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="Q15" s="217" t="s">
-        <v>325</v>
+      <c r="Q15" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="R15" s="41"/>
       <c r="S15" s="148"/>
@@ -20142,25 +19525,25 @@
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="36" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="H16" s="37">
         <v>199</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="J16" s="38">
         <v>46169</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="L16" s="38">
         <v>46262</v>
@@ -20172,11 +19555,11 @@
         <v>38900</v>
       </c>
       <c r="O16" s="132" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="P16" s="40"/>
-      <c r="Q16" s="217" t="s">
-        <v>325</v>
+      <c r="Q16" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="R16" s="47"/>
       <c r="S16" s="148"/>
@@ -20215,7 +19598,7 @@
       <c r="N17" s="136"/>
       <c r="O17" s="136"/>
       <c r="P17" s="136"/>
-      <c r="Q17" s="222"/>
+      <c r="Q17" s="221"/>
       <c r="R17" s="150"/>
       <c r="S17" s="134"/>
       <c r="T17" s="134"/>
@@ -20243,47 +19626,47 @@
     <row r="18" spans="1:40" s="45" customFormat="1" ht="19.5" customHeight="1">
       <c r="A18" s="34"/>
       <c r="B18" s="35"/>
-      <c r="C18" s="233" t="s">
+      <c r="C18" s="231" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="233"/>
-      <c r="E18" s="234" t="s">
+      <c r="D18" s="231"/>
+      <c r="E18" s="232" t="s">
+        <v>160</v>
+      </c>
+      <c r="F18" s="231" t="s">
+        <v>161</v>
+      </c>
+      <c r="G18" s="231" t="s">
         <v>162</v>
       </c>
-      <c r="F18" s="233" t="s">
+      <c r="H18" s="233">
+        <v>350</v>
+      </c>
+      <c r="I18" s="231" t="s">
         <v>163</v>
       </c>
-      <c r="G18" s="233" t="s">
+      <c r="J18" s="234">
+        <v>45959</v>
+      </c>
+      <c r="K18" s="231" t="s">
         <v>164</v>
       </c>
-      <c r="H18" s="235">
-        <v>350</v>
-      </c>
-      <c r="I18" s="233" t="s">
-        <v>165</v>
-      </c>
-      <c r="J18" s="236">
-        <v>45959</v>
-      </c>
-      <c r="K18" s="233" t="s">
-        <v>166</v>
-      </c>
-      <c r="L18" s="236" t="s">
+      <c r="L18" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="M18" s="235">
+      <c r="M18" s="233">
         <v>36823</v>
       </c>
-      <c r="N18" s="235">
+      <c r="N18" s="233">
         <v>37900</v>
       </c>
-      <c r="O18" s="235" t="s">
-        <v>338</v>
-      </c>
-      <c r="P18" s="237" t="s">
+      <c r="O18" s="233" t="s">
+        <v>333</v>
+      </c>
+      <c r="P18" s="235" t="s">
         <v>22</v>
       </c>
-      <c r="Q18" s="221" t="s">
+      <c r="Q18" s="220" t="s">
         <v>36</v>
       </c>
       <c r="R18" s="41"/>
@@ -20317,25 +19700,25 @@
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="36" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H19" s="37">
         <v>599</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J19" s="38">
         <v>46111</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L19" s="38" t="s">
         <v>27</v>
@@ -20347,11 +19730,11 @@
         <v>36900</v>
       </c>
       <c r="O19" s="132" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P19" s="40"/>
-      <c r="Q19" s="220" t="s">
-        <v>325</v>
+      <c r="Q19" s="219" t="s">
+        <v>320</v>
       </c>
       <c r="R19" s="41"/>
       <c r="S19" s="148"/>
@@ -20377,50 +19760,24 @@
       <c r="AM19" s="43"/>
       <c r="AN19" s="45"/>
     </row>
-    <row r="20" spans="1:40" s="134" customFormat="1" ht="19.5" customHeight="1">
+    <row r="20" spans="1:40" s="45" customFormat="1" ht="4.5" customHeight="1">
       <c r="A20" s="34"/>
       <c r="B20" s="35"/>
-      <c r="C20" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="C20" s="1"/>
       <c r="D20" s="1"/>
-      <c r="E20" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="H20" s="37">
-        <v>1900</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J20" s="38">
-        <v>46111</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="L20" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="M20" s="37">
-        <v>35657</v>
-      </c>
-      <c r="N20" s="37">
-        <v>36500</v>
-      </c>
-      <c r="O20" s="37" t="s">
-        <v>35</v>
-      </c>
+      <c r="E20" s="36"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="38"/>
+      <c r="M20" s="37"/>
+      <c r="N20" s="37"/>
+      <c r="O20" s="37"/>
       <c r="P20" s="40"/>
-      <c r="Q20" s="217" t="s">
-        <v>325</v>
-      </c>
+      <c r="Q20" s="219"/>
       <c r="R20" s="41"/>
       <c r="S20" s="148"/>
       <c r="T20" s="43"/>
@@ -20443,27 +19800,54 @@
       <c r="AK20" s="43"/>
       <c r="AL20" s="43"/>
       <c r="AM20" s="43"/>
-      <c r="AN20" s="45"/>
-    </row>
-    <row r="21" spans="1:40" s="45" customFormat="1" ht="4.5" customHeight="1">
+    </row>
+    <row r="21" spans="1:40" s="134" customFormat="1" ht="19.5" customHeight="1">
       <c r="A21" s="34"/>
       <c r="B21" s="35"/>
-      <c r="C21" s="1"/>
+      <c r="C21" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="D21" s="1"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="37"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="37"/>
-      <c r="P21" s="40"/>
-      <c r="Q21" s="220"/>
-      <c r="R21" s="41"/>
+      <c r="E21" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="H21" s="37">
+        <v>11115</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="J21" s="38">
+        <v>45894</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="L21" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="M21" s="37">
+        <v>43584</v>
+      </c>
+      <c r="N21" s="37">
+        <v>39500</v>
+      </c>
+      <c r="O21" s="132" t="s">
+        <v>299</v>
+      </c>
+      <c r="P21" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q21" s="216" t="s">
+        <v>320</v>
+      </c>
+      <c r="R21" s="47"/>
       <c r="S21" s="148"/>
       <c r="T21" s="43"/>
       <c r="U21" s="43"/>
@@ -20485,6 +19869,7 @@
       <c r="AK21" s="43"/>
       <c r="AL21" s="43"/>
       <c r="AM21" s="43"/>
+      <c r="AN21" s="45"/>
     </row>
     <row r="22" spans="1:40" s="134" customFormat="1" ht="19.5" customHeight="1">
       <c r="A22" s="34"/>
@@ -20494,45 +19879,43 @@
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="36" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H22" s="37">
-        <v>11115</v>
+        <v>11900</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="J22" s="38">
-        <v>45894</v>
+        <v>45989</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L22" s="38" t="s">
         <v>27</v>
       </c>
       <c r="M22" s="37">
-        <v>43584</v>
+        <v>39783</v>
       </c>
       <c r="N22" s="37">
-        <v>39500</v>
-      </c>
-      <c r="O22" s="132" t="s">
-        <v>304</v>
-      </c>
-      <c r="P22" s="40" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q22" s="217" t="s">
-        <v>325</v>
-      </c>
-      <c r="R22" s="47"/>
+        <v>38900</v>
+      </c>
+      <c r="O22" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="P22" s="40"/>
+      <c r="Q22" s="216" t="s">
+        <v>320</v>
+      </c>
+      <c r="R22" s="41"/>
       <c r="S22" s="148"/>
       <c r="T22" s="43"/>
       <c r="U22" s="43"/>
@@ -20564,41 +19947,43 @@
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="36" t="s">
-        <v>167</v>
+        <v>369</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>172</v>
+        <v>370</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>173</v>
+        <v>371</v>
       </c>
       <c r="H23" s="37">
-        <v>11900</v>
+        <v>99</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>174</v>
+        <v>125</v>
       </c>
       <c r="J23" s="38">
-        <v>45989</v>
+        <v>46197</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="L23" s="38" t="s">
-        <v>27</v>
+        <v>372</v>
+      </c>
+      <c r="L23" s="38">
+        <v>46290</v>
       </c>
       <c r="M23" s="37">
-        <v>39783</v>
+        <v>40206</v>
       </c>
       <c r="N23" s="37">
-        <v>38900</v>
+        <v>41900</v>
       </c>
       <c r="O23" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="P23" s="40"/>
-      <c r="Q23" s="217" t="s">
-        <v>325</v>
+        <v>333</v>
+      </c>
+      <c r="P23" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q23" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="R23" s="41"/>
       <c r="S23" s="148"/>
@@ -20632,43 +20017,41 @@
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="36" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="H24" s="37">
         <v>99</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>125</v>
+        <v>326</v>
       </c>
       <c r="J24" s="38">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="L24" s="38">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="M24" s="37">
-        <v>40206</v>
+        <v>40457</v>
       </c>
       <c r="N24" s="37">
         <v>41900</v>
       </c>
       <c r="O24" s="37" t="s">
-        <v>338</v>
-      </c>
-      <c r="P24" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q24" s="217" t="s">
-        <v>325</v>
+        <v>375</v>
+      </c>
+      <c r="P24" s="40"/>
+      <c r="Q24" s="216" t="s">
+        <v>320</v>
       </c>
       <c r="R24" s="41"/>
       <c r="S24" s="148"/>
@@ -20694,52 +20077,24 @@
       <c r="AM24" s="43"/>
       <c r="AN24" s="45"/>
     </row>
-    <row r="25" spans="1:40" s="134" customFormat="1" ht="19.5" customHeight="1">
+    <row r="25" spans="1:40" s="134" customFormat="1" ht="10.8" customHeight="1">
       <c r="A25" s="34"/>
       <c r="B25" s="35"/>
-      <c r="C25" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="C25" s="1"/>
       <c r="D25" s="1"/>
-      <c r="E25" s="36" t="s">
-        <v>387</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="H25" s="37">
-        <v>99</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="J25" s="38">
-        <v>46196</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="L25" s="38">
-        <v>46289</v>
-      </c>
-      <c r="M25" s="37">
-        <v>40457</v>
-      </c>
-      <c r="N25" s="37">
-        <v>41900</v>
-      </c>
-      <c r="O25" s="37" t="s">
-        <v>338</v>
-      </c>
-      <c r="P25" s="40" t="s">
-        <v>398</v>
-      </c>
-      <c r="Q25" s="217" t="s">
-        <v>325</v>
-      </c>
+      <c r="E25" s="36"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="133"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="38"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="40"/>
+      <c r="Q25" s="216"/>
       <c r="R25" s="41"/>
       <c r="S25" s="148"/>
       <c r="T25" s="43"/>
@@ -20764,24 +20119,52 @@
       <c r="AM25" s="43"/>
       <c r="AN25" s="45"/>
     </row>
-    <row r="26" spans="1:40" s="134" customFormat="1" ht="10.8" customHeight="1">
+    <row r="26" spans="1:40" s="134" customFormat="1" ht="19.5" customHeight="1">
       <c r="A26" s="34"/>
       <c r="B26" s="35"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="133"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="38"/>
-      <c r="M26" s="37"/>
-      <c r="N26" s="37"/>
-      <c r="O26" s="37"/>
-      <c r="P26" s="40"/>
-      <c r="Q26" s="217"/>
+      <c r="C26" s="237" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="237"/>
+      <c r="E26" s="238" t="s">
+        <v>392</v>
+      </c>
+      <c r="F26" s="237" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="237" t="s">
+        <v>389</v>
+      </c>
+      <c r="H26" s="239">
+        <v>99</v>
+      </c>
+      <c r="I26" s="237" t="s">
+        <v>390</v>
+      </c>
+      <c r="J26" s="240">
+        <v>46217</v>
+      </c>
+      <c r="K26" s="237" t="s">
+        <v>391</v>
+      </c>
+      <c r="L26" s="240">
+        <v>46310</v>
+      </c>
+      <c r="M26" s="239">
+        <v>28793</v>
+      </c>
+      <c r="N26" s="239">
+        <v>0</v>
+      </c>
+      <c r="O26" s="239" t="s">
+        <v>333</v>
+      </c>
+      <c r="P26" s="241" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q26" s="220" t="s">
+        <v>320</v>
+      </c>
       <c r="R26" s="41"/>
       <c r="S26" s="148"/>
       <c r="T26" s="43"/>
@@ -20806,52 +20189,24 @@
       <c r="AM26" s="43"/>
       <c r="AN26" s="45"/>
     </row>
-    <row r="27" spans="1:40" s="134" customFormat="1" ht="19.5" customHeight="1">
+    <row r="27" spans="1:40" s="134" customFormat="1" ht="10.199999999999999" customHeight="1">
       <c r="A27" s="34"/>
       <c r="B27" s="35"/>
-      <c r="C27" s="240" t="s">
-        <v>16</v>
-      </c>
-      <c r="D27" s="240"/>
-      <c r="E27" s="241" t="s">
-        <v>419</v>
-      </c>
-      <c r="F27" s="240" t="s">
-        <v>23</v>
-      </c>
-      <c r="G27" s="240" t="s">
-        <v>416</v>
-      </c>
-      <c r="H27" s="242">
-        <v>99</v>
-      </c>
-      <c r="I27" s="240" t="s">
-        <v>417</v>
-      </c>
-      <c r="J27" s="243">
-        <v>46217</v>
-      </c>
-      <c r="K27" s="240" t="s">
-        <v>418</v>
-      </c>
-      <c r="L27" s="243">
-        <v>46310</v>
-      </c>
-      <c r="M27" s="242">
-        <v>28793</v>
-      </c>
-      <c r="N27" s="242">
-        <v>0</v>
-      </c>
-      <c r="O27" s="242" t="s">
-        <v>338</v>
-      </c>
-      <c r="P27" s="244" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q27" s="221" t="s">
-        <v>325</v>
-      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="133"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="38"/>
+      <c r="M27" s="37"/>
+      <c r="N27" s="37"/>
+      <c r="O27" s="37"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="216"/>
       <c r="R27" s="41"/>
       <c r="S27" s="148"/>
       <c r="T27" s="43"/>
@@ -20876,25 +20231,51 @@
       <c r="AM27" s="43"/>
       <c r="AN27" s="45"/>
     </row>
-    <row r="28" spans="1:40" s="134" customFormat="1" ht="10.199999999999999" customHeight="1">
+    <row r="28" spans="1:40" s="134" customFormat="1" ht="19.5" customHeight="1">
       <c r="A28" s="34"/>
       <c r="B28" s="35"/>
-      <c r="C28" s="1"/>
+      <c r="C28" s="1" t="s">
+        <v>258</v>
+      </c>
       <c r="D28" s="1"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="133"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="38"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="37"/>
-      <c r="N28" s="37"/>
-      <c r="O28" s="37"/>
+      <c r="E28" s="36" t="s">
+        <v>269</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="H28" s="37">
+        <v>99</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="J28" s="38">
+        <v>46142</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="L28" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="M28" s="37">
+        <v>53852</v>
+      </c>
+      <c r="N28" s="37">
+        <v>54300</v>
+      </c>
+      <c r="O28" s="37" t="s">
+        <v>333</v>
+      </c>
       <c r="P28" s="40"/>
-      <c r="Q28" s="217"/>
-      <c r="R28" s="41"/>
+      <c r="Q28" s="216" t="s">
+        <v>320</v>
+      </c>
+      <c r="R28" s="47"/>
       <c r="S28" s="148"/>
       <c r="T28" s="43"/>
       <c r="U28" s="43"/>
@@ -20918,92 +20299,38 @@
       <c r="AM28" s="43"/>
       <c r="AN28" s="45"/>
     </row>
-    <row r="29" spans="1:40" s="134" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A29" s="34"/>
-      <c r="B29" s="35"/>
-      <c r="C29" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="36" t="s">
-        <v>274</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="H29" s="37">
-        <v>99</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="J29" s="38">
-        <v>46142</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="L29" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="M29" s="37">
-        <v>53852</v>
-      </c>
-      <c r="N29" s="37">
-        <v>54300</v>
-      </c>
-      <c r="O29" s="37" t="s">
-        <v>338</v>
-      </c>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="217" t="s">
-        <v>325</v>
-      </c>
-      <c r="R29" s="47"/>
-      <c r="S29" s="148"/>
-      <c r="T29" s="43"/>
-      <c r="U29" s="43"/>
-      <c r="V29" s="43"/>
-      <c r="W29" s="43"/>
-      <c r="X29" s="43"/>
-      <c r="Y29" s="43"/>
-      <c r="Z29" s="43"/>
-      <c r="AA29" s="43"/>
-      <c r="AB29" s="43"/>
-      <c r="AC29" s="43"/>
-      <c r="AD29" s="43"/>
-      <c r="AE29" s="43"/>
-      <c r="AF29" s="43"/>
-      <c r="AG29" s="43"/>
-      <c r="AH29" s="43"/>
-      <c r="AI29" s="43"/>
-      <c r="AJ29" s="43"/>
-      <c r="AK29" s="43"/>
-      <c r="AL29" s="43"/>
-      <c r="AM29" s="43"/>
-      <c r="AN29" s="45"/>
-    </row>
-    <row r="30" spans="1:40" s="134" customFormat="1" ht="7.5" customHeight="1">
-      <c r="B30" s="153"/>
-      <c r="C30" s="154"/>
-      <c r="D30" s="154"/>
-      <c r="E30" s="155"/>
-      <c r="F30" s="155"/>
-      <c r="G30" s="155"/>
-      <c r="H30" s="155"/>
-      <c r="I30" s="155"/>
-      <c r="J30" s="156"/>
-      <c r="K30" s="155"/>
-      <c r="L30" s="156"/>
-      <c r="M30" s="155"/>
-      <c r="N30" s="155"/>
-      <c r="O30" s="155"/>
-      <c r="P30" s="155"/>
-      <c r="Q30" s="223"/>
-      <c r="R30" s="157"/>
+    <row r="29" spans="1:40" s="134" customFormat="1" ht="7.5" customHeight="1">
+      <c r="B29" s="153"/>
+      <c r="C29" s="154"/>
+      <c r="D29" s="154"/>
+      <c r="E29" s="155"/>
+      <c r="F29" s="155"/>
+      <c r="G29" s="155"/>
+      <c r="H29" s="155"/>
+      <c r="I29" s="155"/>
+      <c r="J29" s="156"/>
+      <c r="K29" s="155"/>
+      <c r="L29" s="156"/>
+      <c r="M29" s="155"/>
+      <c r="N29" s="155"/>
+      <c r="O29" s="155"/>
+      <c r="P29" s="155"/>
+      <c r="Q29" s="222"/>
+      <c r="R29" s="157"/>
+    </row>
+    <row r="30" spans="1:40" s="134" customFormat="1">
+      <c r="E30" s="138"/>
+      <c r="F30" s="138"/>
+      <c r="G30" s="138"/>
+      <c r="H30" s="138"/>
+      <c r="I30" s="138"/>
+      <c r="J30" s="139"/>
+      <c r="K30" s="138"/>
+      <c r="L30" s="139"/>
+      <c r="M30" s="138"/>
+      <c r="N30" s="138"/>
+      <c r="O30" s="138"/>
+      <c r="P30" s="138"/>
     </row>
     <row r="31" spans="1:40" s="134" customFormat="1">
       <c r="E31" s="138"/>
@@ -22503,7 +21830,9 @@
       <c r="O137" s="138"/>
       <c r="P137" s="138"/>
     </row>
-    <row r="138" spans="3:40" s="134" customFormat="1">
+    <row r="138" spans="3:40">
+      <c r="C138" s="134"/>
+      <c r="D138" s="134"/>
       <c r="E138" s="138"/>
       <c r="F138" s="138"/>
       <c r="G138" s="138"/>
@@ -22516,6 +21845,9 @@
       <c r="N138" s="138"/>
       <c r="O138" s="138"/>
       <c r="P138" s="138"/>
+      <c r="Q138" s="134"/>
+      <c r="R138" s="134"/>
+      <c r="AN138" s="134"/>
     </row>
     <row r="139" spans="3:40">
       <c r="C139" s="134"/>
@@ -22668,25 +22000,6 @@
       <c r="Q146" s="134"/>
       <c r="R146" s="134"/>
       <c r="AN146" s="134"/>
-    </row>
-    <row r="147" spans="3:40">
-      <c r="C147" s="134"/>
-      <c r="D147" s="134"/>
-      <c r="E147" s="138"/>
-      <c r="F147" s="138"/>
-      <c r="G147" s="138"/>
-      <c r="H147" s="138"/>
-      <c r="I147" s="138"/>
-      <c r="J147" s="139"/>
-      <c r="K147" s="138"/>
-      <c r="L147" s="139"/>
-      <c r="M147" s="138"/>
-      <c r="N147" s="138"/>
-      <c r="O147" s="138"/>
-      <c r="P147" s="138"/>
-      <c r="Q147" s="134"/>
-      <c r="R147" s="134"/>
-      <c r="AN147" s="134"/>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -22747,7 +22060,7 @@
     <row r="2" spans="1:60" s="158" customFormat="1" ht="15" customHeight="1">
       <c r="B2" s="159"/>
       <c r="C2" s="160" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D2" s="160"/>
       <c r="E2" s="160"/>
@@ -22764,10 +22077,10 @@
       <c r="P2" s="160"/>
       <c r="Q2" s="160"/>
       <c r="R2" s="160"/>
-      <c r="S2" s="251">
+      <c r="S2" s="247">
         <v>46188</v>
       </c>
-      <c r="T2" s="251"/>
+      <c r="T2" s="247"/>
       <c r="U2" s="161"/>
     </row>
     <row r="3" spans="1:60" s="28" customFormat="1" ht="16.5" customHeight="1">
@@ -22870,22 +22183,22 @@
       <c r="B4" s="37"/>
       <c r="C4" s="1"/>
       <c r="D4" s="36" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>29</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J4" s="37">
         <v>17624</v>
@@ -22961,22 +22274,22 @@
       <c r="B5" s="37"/>
       <c r="C5" s="1"/>
       <c r="D5" s="36" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>29</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J5" s="37">
         <v>20719</v>
@@ -23114,20 +22427,20 @@
       <c r="B7" s="37"/>
       <c r="C7" s="1"/>
       <c r="D7" s="36" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>185</v>
       </c>
       <c r="J7" s="37">
         <v>12059</v>
@@ -23203,7 +22516,7 @@
       <c r="B8" s="37"/>
       <c r="C8" s="1"/>
       <c r="D8" s="36" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>123</v>
@@ -23212,13 +22525,13 @@
         <v>23</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J8" s="37">
         <v>14150</v>
@@ -23245,8 +22558,8 @@
       <c r="Q8" s="39">
         <v>19390</v>
       </c>
-      <c r="R8" s="248" t="s">
-        <v>399</v>
+      <c r="R8" s="244" t="s">
+        <v>376</v>
       </c>
       <c r="S8" s="37"/>
       <c r="T8" s="37"/>
@@ -23296,20 +22609,20 @@
       <c r="B9" s="37"/>
       <c r="C9" s="1"/>
       <c r="D9" s="36" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J9" s="37">
         <v>99</v>
@@ -23385,7 +22698,7 @@
       <c r="B10" s="37"/>
       <c r="C10" s="1"/>
       <c r="D10" s="36" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>123</v>
@@ -23394,13 +22707,13 @@
         <v>23</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J10" s="37">
         <v>11854</v>
@@ -23538,7 +22851,7 @@
       <c r="B12" s="37"/>
       <c r="C12" s="1"/>
       <c r="D12" s="36" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>123</v>
@@ -23547,13 +22860,13 @@
         <v>62</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J12" s="37">
         <v>26754</v>
@@ -23580,8 +22893,8 @@
       <c r="Q12" s="39">
         <v>24990</v>
       </c>
-      <c r="R12" s="248" t="s">
-        <v>399</v>
+      <c r="R12" s="244" t="s">
+        <v>376</v>
       </c>
       <c r="S12" s="37"/>
       <c r="T12" s="37"/>
@@ -23702,13 +23015,13 @@
         <v>23</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>29</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J14" s="37">
         <v>17012</v>
@@ -23735,8 +23048,8 @@
       <c r="Q14" s="39">
         <v>18390</v>
       </c>
-      <c r="R14" s="248" t="s">
-        <v>399</v>
+      <c r="R14" s="244" t="s">
+        <v>376</v>
       </c>
       <c r="S14" s="37"/>
       <c r="T14" s="37"/>
@@ -29599,7 +28912,7 @@
     <row r="2" spans="1:40" s="158" customFormat="1" ht="16.5" customHeight="1">
       <c r="B2" s="159"/>
       <c r="C2" s="160" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D2" s="160"/>
       <c r="E2" s="160"/>
@@ -29641,16 +28954,16 @@
         <v>5</v>
       </c>
       <c r="J3" s="172" t="s">
+        <v>203</v>
+      </c>
+      <c r="K3" s="172" t="s">
+        <v>204</v>
+      </c>
+      <c r="L3" s="172" t="s">
         <v>205</v>
       </c>
-      <c r="K3" s="172" t="s">
+      <c r="M3" s="172" t="s">
         <v>206</v>
-      </c>
-      <c r="L3" s="172" t="s">
-        <v>207</v>
-      </c>
-      <c r="M3" s="172" t="s">
-        <v>208</v>
       </c>
       <c r="N3" s="172" t="s">
         <v>11</v>
@@ -29662,7 +28975,7 @@
         <v>13</v>
       </c>
       <c r="Q3" s="172" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="R3" s="174"/>
       <c r="S3" s="170"/>
@@ -29692,17 +29005,17 @@
       <c r="A4" s="34"/>
       <c r="B4" s="37"/>
       <c r="C4" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="36" t="s">
+        <v>209</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="H4" s="38">
         <v>43570</v>
@@ -29726,7 +29039,7 @@
       </c>
       <c r="O4" s="37"/>
       <c r="P4" s="40" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="Q4" s="40" t="s">
         <v>22</v>
@@ -29759,14 +29072,14 @@
       <c r="A5" s="34"/>
       <c r="B5" s="177"/>
       <c r="C5" s="178" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D5" s="178"/>
       <c r="E5" s="179" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F5" s="178" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G5" s="178" t="s">
         <v>29</v>
@@ -29792,10 +29105,10 @@
         <v>5785</v>
       </c>
       <c r="O5" s="181" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="P5" s="182" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="Q5" s="182" t="s">
         <v>22</v>
@@ -29828,14 +29141,14 @@
       <c r="A6" s="34"/>
       <c r="B6" s="37"/>
       <c r="C6" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="36" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>24</v>
@@ -29863,7 +29176,7 @@
       <c r="O6" s="37"/>
       <c r="P6" s="40"/>
       <c r="Q6" s="40" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="R6" s="175"/>
       <c r="S6" s="43"/>
@@ -29893,17 +29206,17 @@
       <c r="A7" s="34"/>
       <c r="B7" s="37"/>
       <c r="C7" s="178" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D7" s="178"/>
       <c r="E7" s="179" t="s">
+        <v>219</v>
+      </c>
+      <c r="F7" s="178" t="s">
+        <v>220</v>
+      </c>
+      <c r="G7" s="178" t="s">
         <v>221</v>
-      </c>
-      <c r="F7" s="178" t="s">
-        <v>222</v>
-      </c>
-      <c r="G7" s="178" t="s">
-        <v>223</v>
       </c>
       <c r="H7" s="180">
         <v>43404</v>
@@ -29926,7 +29239,7 @@
         <v>6198</v>
       </c>
       <c r="O7" s="181" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P7" s="182"/>
       <c r="Q7" s="182" t="s">
@@ -29960,14 +29273,14 @@
       <c r="A8" s="34"/>
       <c r="B8" s="37"/>
       <c r="C8" s="178" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D8" s="178"/>
       <c r="E8" s="179" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F8" s="178" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G8" s="178" t="s">
         <v>19</v>
@@ -29993,7 +29306,7 @@
         <v>8264</v>
       </c>
       <c r="O8" s="181" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P8" s="182"/>
       <c r="Q8" s="182" t="s">
@@ -30027,17 +29340,17 @@
       <c r="A9" s="34"/>
       <c r="B9" s="37"/>
       <c r="C9" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="36" t="s">
+        <v>225</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>229</v>
       </c>
       <c r="H9" s="38">
         <v>42431</v>
@@ -30064,7 +29377,7 @@
       <c r="O9" s="37"/>
       <c r="P9" s="40"/>
       <c r="Q9" s="40" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="R9" s="175"/>
       <c r="S9" s="43"/>
@@ -30136,14 +29449,14 @@
       <c r="A11" s="34"/>
       <c r="B11" s="37"/>
       <c r="C11" s="178" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D11" s="178"/>
       <c r="E11" s="179" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F11" s="178" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G11" s="178" t="s">
         <v>24</v>
@@ -30169,7 +29482,7 @@
         <v>5370</v>
       </c>
       <c r="O11" s="181" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P11" s="182"/>
       <c r="Q11" s="182" t="s">
@@ -30203,14 +29516,14 @@
       <c r="A12" s="34"/>
       <c r="B12" s="37"/>
       <c r="C12" s="178" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D12" s="178"/>
       <c r="E12" s="179" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F12" s="178" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G12" s="178" t="s">
         <v>24</v>
@@ -30236,10 +29549,10 @@
         <v>6600</v>
       </c>
       <c r="O12" s="181" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P12" s="182" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q12" s="182" t="s">
         <v>22</v>
@@ -30272,14 +29585,14 @@
       <c r="A13" s="34"/>
       <c r="B13" s="37"/>
       <c r="C13" s="178" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D13" s="178"/>
       <c r="E13" s="179" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F13" s="178" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G13" s="178" t="s">
         <v>24</v>
@@ -30305,7 +29618,7 @@
         <v>5370</v>
       </c>
       <c r="O13" s="181" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P13" s="182"/>
       <c r="Q13" s="182" t="s">
@@ -30339,14 +29652,14 @@
       <c r="A14" s="34"/>
       <c r="B14" s="37"/>
       <c r="C14" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="36" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>24</v>
@@ -30373,10 +29686,10 @@
       </c>
       <c r="O14" s="37"/>
       <c r="P14" s="40" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="Q14" s="40" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="R14" s="175"/>
       <c r="S14" s="43"/>
@@ -30406,17 +29719,17 @@
       <c r="A15" s="34"/>
       <c r="B15" s="37"/>
       <c r="C15" s="178" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D15" s="178"/>
       <c r="E15" s="179" t="s">
+        <v>235</v>
+      </c>
+      <c r="F15" s="178" t="s">
         <v>237</v>
       </c>
-      <c r="F15" s="178" t="s">
-        <v>239</v>
-      </c>
       <c r="G15" s="178" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H15" s="180">
         <v>43580</v>
@@ -30441,10 +29754,10 @@
         <v>5620</v>
       </c>
       <c r="O15" s="181" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P15" s="182" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="Q15" s="182" t="s">
         <v>22</v>
@@ -30477,14 +29790,14 @@
       <c r="A16" s="34"/>
       <c r="B16" s="37"/>
       <c r="C16" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="36" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>24</v>
@@ -30513,10 +29826,10 @@
       </c>
       <c r="O16" s="37"/>
       <c r="P16" s="40" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="Q16" s="40" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="R16" s="175"/>
       <c r="S16" s="43"/>
@@ -30588,17 +29901,17 @@
       <c r="A18" s="34"/>
       <c r="B18" s="37"/>
       <c r="C18" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>244</v>
       </c>
       <c r="H18" s="38">
         <v>43125</v>
@@ -30625,7 +29938,7 @@
       <c r="O18" s="37"/>
       <c r="P18" s="40"/>
       <c r="Q18" s="40" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="R18" s="175"/>
       <c r="S18" s="43"/>
